--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF44F889-2A27-4369-9DF6-F9F1B6BF9437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3396A5-7A5E-4097-BDDD-6BA28DC1E860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3010" yWindow="1390" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="1320" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="296">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3801,6 +3801,227 @@
   </si>
   <si>
     <t>["Prefabs/Characters/3/Spot/talents/spot_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芙蓉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hibisc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>罗德岛医疗干员芙蓉，将为伤员提供可靠的医疗援助。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请小心处理她与干员炎熔间的关系。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Hibisc/Hibisc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗德岛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1),(0,2),(0,3),(1,0),(1,1),(1,2),(1,3),(-1,0),(-1,1),(-1,2),(-1,3)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唯一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Hibisc/spine/ReferenceAssets/hibisc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Hibisc/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芙蓉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Hibisc/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芙蓉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Hibisc/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芙蓉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Hibisc/skills/hibisc_s1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Hibisc/talents/Hibisc_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Monsters/MC/Zombie/talents/zombie_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Monsters/MC/Skeleton/talents/skeleton_t1"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3950,7 +4171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -4045,6 +4266,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4326,7 +4553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF21"/>
+  <dimension ref="A1:BF22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.58203125" style="9" customWidth="1"/>
@@ -5716,68 +5943,70 @@
     </row>
     <row r="11" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>61</v>
+        <v>278</v>
       </c>
       <c r="B11" s="10">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>125</v>
+        <v>7</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>279</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>126</v>
+        <v>280</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>281</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>161</v>
+        <v>282</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>153</v>
+        <v>289</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="J11" s="10">
-        <v>2</v>
-      </c>
-      <c r="L11" s="16"/>
-      <c r="O11" s="10">
-        <v>0</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>1</v>
-      </c>
-      <c r="R11" s="10">
-        <v>1</v>
-      </c>
-      <c r="S11" s="10">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="K11" s="11">
+        <v>3</v>
+      </c>
+      <c r="L11" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="M11" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>285</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="U11" s="13">
         <v>0</v>
       </c>
       <c r="V11" s="13">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="W11" s="13">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="X11" s="11">
         <v>1</v>
       </c>
       <c r="Y11" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z11" s="13">
-        <v>5500</v>
+        <v>1220</v>
       </c>
       <c r="AA11" s="13">
-        <v>265</v>
+        <v>110</v>
       </c>
       <c r="AB11" s="13">
         <v>0</v>
@@ -5816,25 +6045,43 @@
         <v>0</v>
       </c>
       <c r="AP11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ11" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="BA11" s="11">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="11">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AQ11" s="10">
+        <v>15</v>
+      </c>
+      <c r="AR11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU11" s="14">
+        <v>70</v>
+      </c>
+      <c r="AV11" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="AW11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="14">
+        <v>50</v>
+      </c>
+      <c r="AY11" s="10">
+        <v>1</v>
       </c>
       <c r="BC11" s="4" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="BD11" s="5" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="BE11" s="4" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:58" x14ac:dyDescent="0.3">
@@ -5842,22 +6089,22 @@
         <v>61</v>
       </c>
       <c r="B12" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J12" s="10">
         <v>2</v>
@@ -5882,13 +6129,13 @@
         <v>65</v>
       </c>
       <c r="U12" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" s="13">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="W12" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X12" s="11">
         <v>1</v>
@@ -5897,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="Z12" s="13">
-        <v>4590</v>
+        <v>5500</v>
       </c>
       <c r="AA12" s="13">
-        <v>185</v>
+        <v>265</v>
       </c>
       <c r="AB12" s="13">
         <v>0</v>
@@ -5942,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="AZ12" s="13">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BA12" s="11">
         <v>1</v>
@@ -5954,10 +6201,10 @@
         <v>258</v>
       </c>
       <c r="BD12" s="5" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="BE12" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:58" x14ac:dyDescent="0.3">
@@ -5965,29 +6212,32 @@
         <v>61</v>
       </c>
       <c r="B13" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J13" s="10">
         <v>2</v>
       </c>
       <c r="L13" s="16"/>
       <c r="O13" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="Q13" s="10">
         <v>1</v>
@@ -6002,13 +6252,13 @@
         <v>65</v>
       </c>
       <c r="U13" s="13">
-        <v>1.4139999999999999</v>
+        <v>2.8279999999999998</v>
       </c>
       <c r="V13" s="13">
-        <v>1050</v>
+        <v>395</v>
       </c>
       <c r="W13" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X13" s="11">
         <v>1</v>
@@ -6017,13 +6267,13 @@
         <v>0</v>
       </c>
       <c r="Z13" s="13">
-        <v>12000</v>
+        <v>4590</v>
       </c>
       <c r="AA13" s="13">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="AB13" s="13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="13">
         <v>0</v>
@@ -6062,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="AZ13" s="13">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BA13" s="11">
         <v>1</v>
@@ -6074,7 +6324,10 @@
         <v>258</v>
       </c>
       <c r="BD13" s="5" t="s">
-        <v>258</v>
+        <v>295</v>
+      </c>
+      <c r="BE13" s="4" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:58" x14ac:dyDescent="0.3">
@@ -6082,22 +6335,22 @@
         <v>61</v>
       </c>
       <c r="B14" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J14" s="10">
         <v>2</v>
@@ -6106,9 +6359,6 @@
       <c r="O14" s="10">
         <v>1</v>
       </c>
-      <c r="P14" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="Q14" s="10">
         <v>1</v>
       </c>
@@ -6122,28 +6372,28 @@
         <v>65</v>
       </c>
       <c r="U14" s="13">
+        <v>1.4139999999999999</v>
+      </c>
+      <c r="V14" s="13">
+        <v>1050</v>
+      </c>
+      <c r="W14" s="13">
         <v>3</v>
       </c>
-      <c r="V14" s="13">
-        <v>200</v>
-      </c>
-      <c r="W14" s="13">
-        <v>5</v>
-      </c>
       <c r="X14" s="11">
         <v>1</v>
       </c>
       <c r="Y14" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="13">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="AA14" s="13">
-        <v>375</v>
+        <v>325</v>
       </c>
       <c r="AB14" s="13">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AC14" s="13">
         <v>0</v>
@@ -6182,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="AZ14" s="13">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BA14" s="11">
         <v>1</v>
@@ -6202,29 +6452,32 @@
         <v>61</v>
       </c>
       <c r="B15" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J15" s="10">
         <v>2</v>
       </c>
       <c r="L15" s="16"/>
       <c r="O15" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="Q15" s="10">
         <v>1</v>
@@ -6239,28 +6492,28 @@
         <v>65</v>
       </c>
       <c r="U15" s="13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" s="13">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="W15" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X15" s="11">
         <v>1</v>
       </c>
       <c r="Y15" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" s="13">
-        <v>1235</v>
+        <v>12500</v>
       </c>
       <c r="AA15" s="13">
-        <v>65</v>
+        <v>375</v>
       </c>
       <c r="AB15" s="13">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="AC15" s="13">
         <v>0</v>
@@ -6299,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="AZ15" s="13">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA15" s="11">
         <v>1</v>
@@ -6319,22 +6572,22 @@
         <v>61</v>
       </c>
       <c r="B16" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J16" s="10">
         <v>2</v>
@@ -6359,10 +6612,10 @@
         <v>0</v>
       </c>
       <c r="V16" s="13">
-        <v>430</v>
+        <v>290</v>
       </c>
       <c r="W16" s="13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X16" s="11">
         <v>1</v>
@@ -6371,10 +6624,10 @@
         <v>0</v>
       </c>
       <c r="Z16" s="13">
-        <v>3600</v>
+        <v>1235</v>
       </c>
       <c r="AA16" s="13">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AB16" s="13">
         <v>5</v>
@@ -6411,12 +6664,6 @@
       </c>
       <c r="AM16" s="11">
         <v>0</v>
-      </c>
-      <c r="AN16" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="AO16" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="AP16" s="11">
         <v>0</v>
@@ -6442,22 +6689,22 @@
         <v>61</v>
       </c>
       <c r="B17" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J17" s="10">
         <v>2</v>
@@ -6482,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="V17" s="13">
-        <v>670</v>
+        <v>430</v>
       </c>
       <c r="W17" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X17" s="11">
         <v>1</v>
@@ -6494,10 +6741,10 @@
         <v>0</v>
       </c>
       <c r="Z17" s="13">
-        <v>6900</v>
+        <v>3600</v>
       </c>
       <c r="AA17" s="13">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="AB17" s="13">
         <v>5</v>
@@ -6536,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AO17" s="11" t="s">
         <v>179</v>
@@ -6565,19 +6812,22 @@
         <v>61</v>
       </c>
       <c r="B18" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>142</v>
+        <v>72</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>139</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="J18" s="10">
         <v>2</v>
@@ -6587,40 +6837,40 @@
         <v>0</v>
       </c>
       <c r="Q18" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="12" t="s">
         <v>65</v>
       </c>
       <c r="U18" s="13">
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="V18" s="13">
-        <v>500</v>
+        <v>670</v>
       </c>
       <c r="W18" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X18" s="11">
         <v>1</v>
       </c>
       <c r="Y18" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="13">
-        <v>5000</v>
+        <v>6900</v>
       </c>
       <c r="AA18" s="13">
-        <v>500</v>
+        <v>235</v>
       </c>
       <c r="AB18" s="13">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="AC18" s="13">
         <v>0</v>
@@ -6655,14 +6905,20 @@
       <c r="AM18" s="11">
         <v>0</v>
       </c>
+      <c r="AN18" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="AO18" s="11" t="s">
+        <v>179</v>
+      </c>
       <c r="AP18" s="11">
         <v>0</v>
       </c>
       <c r="AZ18" s="13">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="BA18" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB18" s="11">
         <v>0</v>
@@ -6679,19 +6935,19 @@
         <v>61</v>
       </c>
       <c r="B19" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>142</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J19" s="10">
         <v>2</v>
@@ -6700,9 +6956,6 @@
       <c r="O19" s="10">
         <v>0</v>
       </c>
-      <c r="P19" s="19" t="s">
-        <v>145</v>
-      </c>
       <c r="Q19" s="10">
         <v>0</v>
       </c>
@@ -6716,96 +6969,72 @@
         <v>65</v>
       </c>
       <c r="U19" s="13">
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="V19" s="13">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="W19" s="13">
+        <v>3</v>
+      </c>
+      <c r="X19" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="13">
+        <v>5000</v>
+      </c>
+      <c r="AA19" s="13">
+        <v>500</v>
+      </c>
+      <c r="AB19" s="13">
+        <v>50</v>
+      </c>
+      <c r="AC19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AZ19" s="13">
+        <v>0.45</v>
+      </c>
+      <c r="BA19" s="11">
         <v>2</v>
       </c>
-      <c r="X19" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="13">
-        <v>100</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO19" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AP19" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AT19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AV19" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="AW19" s="10">
-        <v>0</v>
-      </c>
-      <c r="AX19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY19" s="10">
+      <c r="BB19" s="11">
         <v>0</v>
       </c>
       <c r="BC19" s="4" t="s">
@@ -6820,68 +7049,65 @@
         <v>61</v>
       </c>
       <c r="B20" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="J20" s="10">
         <v>2</v>
       </c>
       <c r="L20" s="16"/>
       <c r="O20" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20" s="19" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="Q20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T20" s="12" t="s">
         <v>65</v>
       </c>
       <c r="U20" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V20" s="13">
-        <v>650</v>
+        <v>100</v>
       </c>
       <c r="W20" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X20" s="11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="13">
-        <v>32500</v>
+        <v>100</v>
       </c>
       <c r="AA20" s="13">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="13">
         <v>0</v>
@@ -6890,42 +7116,66 @@
         <v>0</v>
       </c>
       <c r="AE20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="11">
         <v>0</v>
       </c>
       <c r="AG20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM20" s="11">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO20" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="AP20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="BA20" s="11">
-        <v>7</v>
-      </c>
-      <c r="BB20" s="11">
+        <v>1</v>
+      </c>
+      <c r="AQ20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="AW20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="10">
         <v>0</v>
       </c>
       <c r="BC20" s="4" t="s">
@@ -6937,53 +7187,71 @@
     </row>
     <row r="21" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>171</v>
+        <v>61</v>
       </c>
       <c r="B21" s="10">
-        <v>1</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>172</v>
+        <v>11</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>174</v>
+        <v>149</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>148</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>160</v>
       </c>
       <c r="J21" s="10">
         <v>2</v>
       </c>
       <c r="L21" s="16"/>
+      <c r="O21" s="10">
+        <v>2</v>
+      </c>
+      <c r="P21" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>1</v>
+      </c>
+      <c r="R21" s="10">
+        <v>1</v>
+      </c>
+      <c r="S21" s="10">
+        <v>2</v>
+      </c>
       <c r="T21" s="12" t="s">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="U21" s="13">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="V21" s="13">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="W21" s="13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21" s="11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y21" s="11">
         <v>1</v>
       </c>
       <c r="Z21" s="13">
-        <v>100</v>
+        <v>32500</v>
       </c>
       <c r="AA21" s="13">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="AB21" s="13">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AC21" s="13">
         <v>0</v>
@@ -6992,33 +7260,42 @@
         <v>0</v>
       </c>
       <c r="AE21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" s="11">
         <v>0</v>
       </c>
       <c r="AG21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AZ21" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="BA21" s="11">
+        <v>7</v>
+      </c>
+      <c r="BB21" s="11">
         <v>0</v>
       </c>
       <c r="BC21" s="4" t="s">
@@ -7027,7 +7304,100 @@
       <c r="BD21" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="BE21" s="4" t="s">
+    </row>
+    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B22" s="10">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="10">
+        <v>2</v>
+      </c>
+      <c r="L22" s="16"/>
+      <c r="T22" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="U22" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="V22" s="13">
+        <v>0</v>
+      </c>
+      <c r="W22" s="13">
+        <v>-1</v>
+      </c>
+      <c r="X22" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="13">
+        <v>100</v>
+      </c>
+      <c r="AA22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BC22" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BD22" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE22" s="4" t="s">
         <v>267</v>
       </c>
     </row>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3396A5-7A5E-4097-BDDD-6BA28DC1E860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D40879-A0F2-4B79-BFC9-E9753F5C07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1320" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="297">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4022,6 +4022,10 @@
   </si>
   <si>
     <t>["Prefabs/Monsters/MC/Skeleton/talents/skeleton_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/MC/Creeper/Spine/ReferenceAssets/creeper</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6446,6 +6450,9 @@
       <c r="BD14" s="5" t="s">
         <v>258</v>
       </c>
+      <c r="BE14" s="4" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="15" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D40879-A0F2-4B79-BFC9-E9753F5C07CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2266A-373B-4A22-9A0F-D4C9C4BBE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$BB$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$BC$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="299">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4026,6 +4026,14 @@
   </si>
   <si>
     <t>Prefabs/Monsters/MC/Creeper/Spine/ReferenceAssets/creeper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetPriority</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索敌优先级</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4557,7 +4565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BF22"/>
+  <dimension ref="A1:BG22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.58203125" style="9" customWidth="1"/>
@@ -4571,23 +4579,23 @@
     <col min="17" max="19" width="12.58203125" style="10" customWidth="1"/>
     <col min="20" max="20" width="12.58203125" style="12" customWidth="1"/>
     <col min="21" max="23" width="12.58203125" style="13" customWidth="1"/>
-    <col min="24" max="25" width="12.58203125" style="11" customWidth="1"/>
-    <col min="26" max="30" width="12.58203125" style="13" customWidth="1"/>
-    <col min="31" max="39" width="12.58203125" style="11" customWidth="1"/>
-    <col min="40" max="40" width="12.58203125" style="12" customWidth="1"/>
-    <col min="41" max="42" width="12.58203125" style="11" customWidth="1"/>
-    <col min="43" max="46" width="12.58203125" style="10" customWidth="1"/>
-    <col min="47" max="48" width="12.58203125" style="14" customWidth="1"/>
-    <col min="49" max="49" width="12.58203125" style="10" customWidth="1"/>
-    <col min="50" max="50" width="12.58203125" style="14" customWidth="1"/>
-    <col min="51" max="51" width="12.58203125" style="10" customWidth="1"/>
-    <col min="52" max="52" width="12.58203125" style="13" customWidth="1"/>
-    <col min="53" max="54" width="12.58203125" style="11" customWidth="1"/>
-    <col min="55" max="57" width="12.58203125" style="4" customWidth="1"/>
-    <col min="58" max="16384" width="8.6640625" style="7"/>
+    <col min="24" max="26" width="12.58203125" style="11" customWidth="1"/>
+    <col min="27" max="31" width="12.58203125" style="13" customWidth="1"/>
+    <col min="32" max="40" width="12.58203125" style="11" customWidth="1"/>
+    <col min="41" max="41" width="12.58203125" style="12" customWidth="1"/>
+    <col min="42" max="43" width="12.58203125" style="11" customWidth="1"/>
+    <col min="44" max="47" width="12.58203125" style="10" customWidth="1"/>
+    <col min="48" max="49" width="12.58203125" style="14" customWidth="1"/>
+    <col min="50" max="50" width="12.58203125" style="10" customWidth="1"/>
+    <col min="51" max="51" width="12.58203125" style="14" customWidth="1"/>
+    <col min="52" max="52" width="12.58203125" style="10" customWidth="1"/>
+    <col min="53" max="53" width="12.58203125" style="13" customWidth="1"/>
+    <col min="54" max="55" width="12.58203125" style="11" customWidth="1"/>
+    <col min="56" max="58" width="12.58203125" style="4" customWidth="1"/>
+    <col min="59" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -4649,9 +4657,10 @@
       <c r="BC1" s="6"/>
       <c r="BD1" s="6"/>
       <c r="BE1" s="6"/>
-      <c r="BF1" s="20"/>
+      <c r="BF1" s="6"/>
+      <c r="BG1" s="20"/>
     </row>
-    <row r="2" spans="1:58" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:59" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>4</v>
       </c>
@@ -4702,10 +4711,10 @@
       <c r="AN2" s="6"/>
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
-      <c r="AQ2" s="29" t="s">
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="29"/>
       <c r="AS2" s="29"/>
       <c r="AT2" s="29"/>
       <c r="AU2" s="29"/>
@@ -4713,19 +4722,20 @@
       <c r="AW2" s="29"/>
       <c r="AX2" s="29"/>
       <c r="AY2" s="29"/>
-      <c r="AZ2" s="6" t="s">
+      <c r="AZ2" s="29"/>
+      <c r="BA2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BA2" s="6"/>
       <c r="BB2" s="6"/>
-      <c r="BC2" s="1" t="s">
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
-      <c r="BF2" s="20"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="20"/>
     </row>
-    <row r="3" spans="1:58" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:59" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
         <v>73</v>
       </c>
@@ -4801,105 +4811,108 @@
       <c r="Y3" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="AA3" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="AA3" s="32" t="s">
+      <c r="AB3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AC3" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="AC3" s="32" t="s">
+      <c r="AD3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="AD3" s="32" t="s">
+      <c r="AE3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="AE3" s="32" t="s">
+      <c r="AF3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="AF3" s="32" t="s">
+      <c r="AG3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="AG3" s="33" t="s">
+      <c r="AH3" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AH3" s="33" t="s">
+      <c r="AI3" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AI3" s="33" t="s">
+      <c r="AJ3" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AK3" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AL3" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AM3" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AN3" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="AN3" s="32" t="s">
+      <c r="AO3" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="AO3" s="32" t="s">
+      <c r="AP3" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="AP3" s="33" t="s">
+      <c r="AQ3" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="AQ3" s="30" t="s">
+      <c r="AR3" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AR3" s="30" t="s">
+      <c r="AS3" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AS3" s="34" t="s">
+      <c r="AT3" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="AT3" s="30" t="s">
+      <c r="AU3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AU3" s="30" t="s">
+      <c r="AV3" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="AV3" s="31" t="s">
+      <c r="AW3" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="AW3" s="30" t="s">
+      <c r="AX3" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AX3" s="30" t="s">
+      <c r="AY3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="AY3" s="30" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="AZ3" s="32" t="s">
+      <c r="BA3" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="BA3" s="32" t="s">
+      <c r="BB3" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="BB3" s="32" t="s">
+      <c r="BC3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="BC3" s="2" t="s">
+      <c r="BD3" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BE3" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BF3" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="BF3" s="21"/>
+      <c r="BG3" s="21"/>
     </row>
-    <row r="4" spans="1:58" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:59" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
         <v>42</v>
       </c>
@@ -4976,104 +4989,107 @@
         <v>214</v>
       </c>
       <c r="Z4" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="AA4" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AB4" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AC4" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AD4" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AE4" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AF4" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AG4" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AH4" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AI4" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AK4" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AL4" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AM4" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AN4" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AO4" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AP4" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="AQ4" s="30" t="s">
+      <c r="AR4" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="AR4" s="30" t="s">
+      <c r="AS4" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AT4" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AU4" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AV4" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AW4" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AX4" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="AZ4" s="32" t="s">
+      <c r="BA4" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="BA4" s="32" t="s">
+      <c r="BB4" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="BB4" s="32" t="s">
+      <c r="BC4" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="BC4" s="3" t="s">
+      <c r="BD4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="BD4" s="3" t="s">
+      <c r="BE4" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="BE4" s="3" t="s">
+      <c r="BF4" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="BF4" s="21"/>
+      <c r="BG4" s="21"/>
     </row>
-    <row r="5" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>44</v>
       </c>
@@ -5139,26 +5155,26 @@
       <c r="Y5" s="24">
         <v>1</v>
       </c>
-      <c r="Z5" s="26">
+      <c r="Z5" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="26">
         <v>1743</v>
       </c>
-      <c r="AA5" s="26">
+      <c r="AB5" s="26">
         <v>122</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AC5" s="26">
         <v>20</v>
       </c>
-      <c r="AC5" s="26">
-        <v>0</v>
-      </c>
       <c r="AD5" s="26">
         <v>0</v>
       </c>
-      <c r="AE5" s="24">
-        <v>1</v>
+      <c r="AE5" s="26">
+        <v>0</v>
       </c>
       <c r="AF5" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" s="24">
         <v>0</v>
@@ -5181,56 +5197,59 @@
       <c r="AM5" s="24">
         <v>0</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="24">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="AO5" s="24" t="s">
+      <c r="AP5" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="AP5" s="24">
-        <v>1</v>
-      </c>
-      <c r="AQ5" s="23">
+      <c r="AQ5" s="24">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="23">
         <v>19</v>
       </c>
-      <c r="AR5" s="23">
-        <v>1</v>
-      </c>
       <c r="AS5" s="23">
         <v>1</v>
       </c>
       <c r="AT5" s="23">
         <v>1</v>
       </c>
-      <c r="AU5" s="27">
+      <c r="AU5" s="23">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="27">
         <v>70</v>
       </c>
-      <c r="AV5" s="28" t="s">
+      <c r="AW5" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="AW5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AX5" s="27">
+      <c r="AX5" s="23">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="27">
         <v>50</v>
       </c>
-      <c r="AY5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="24"/>
+      <c r="AZ5" s="23">
+        <v>1</v>
+      </c>
+      <c r="BA5" s="26"/>
       <c r="BB5" s="24"/>
-      <c r="BC5" s="4" t="s">
+      <c r="BC5" s="24"/>
+      <c r="BD5" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD5" s="5" t="s">
+      <c r="BE5" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="BE5" s="4" t="s">
+      <c r="BF5" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>46</v>
       </c>
@@ -5291,26 +5310,26 @@
       <c r="Y6" s="11">
         <v>1</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="Z6" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="13">
         <v>1678</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AB6" s="13">
         <v>135</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AC6" s="13">
         <v>20</v>
       </c>
-      <c r="AC6" s="13">
-        <v>0</v>
-      </c>
       <c r="AD6" s="13">
         <v>0</v>
       </c>
-      <c r="AE6" s="11">
-        <v>1</v>
+      <c r="AE6" s="13">
+        <v>0</v>
       </c>
       <c r="AF6" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="11">
         <v>0</v>
@@ -5333,47 +5352,50 @@
       <c r="AM6" s="11">
         <v>0</v>
       </c>
-      <c r="AP6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ6" s="10">
+      <c r="AN6" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="10">
         <v>25</v>
       </c>
-      <c r="AR6" s="10">
-        <v>1</v>
-      </c>
       <c r="AS6" s="10">
         <v>1</v>
       </c>
       <c r="AT6" s="10">
         <v>1</v>
       </c>
-      <c r="AU6" s="14">
+      <c r="AU6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="14">
         <v>70</v>
       </c>
-      <c r="AV6" s="15" t="s">
+      <c r="AW6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AW6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX6" s="14">
+      <c r="AX6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY6" s="14">
         <v>50</v>
       </c>
-      <c r="AY6" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC6" s="4" t="s">
+      <c r="AZ6" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD6" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="BD6" s="5" t="s">
+      <c r="BE6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="BE6" s="4" t="s">
+      <c r="BF6" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>50</v>
       </c>
@@ -5434,26 +5456,26 @@
       <c r="Y7" s="11">
         <v>0</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="Z7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="13">
         <v>1060</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>126</v>
       </c>
-      <c r="AB7" s="13">
-        <v>0</v>
-      </c>
       <c r="AC7" s="13">
         <v>0</v>
       </c>
       <c r="AD7" s="13">
         <v>0</v>
       </c>
-      <c r="AE7" s="11">
-        <v>1</v>
+      <c r="AE7" s="13">
+        <v>0</v>
       </c>
       <c r="AF7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" s="11">
         <v>0</v>
@@ -5476,47 +5498,50 @@
       <c r="AM7" s="11">
         <v>0</v>
       </c>
-      <c r="AP7" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ7" s="10">
+      <c r="AN7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="10">
         <v>11</v>
       </c>
-      <c r="AR7" s="10">
-        <v>1</v>
-      </c>
       <c r="AS7" s="10">
         <v>1</v>
       </c>
       <c r="AT7" s="10">
         <v>1</v>
       </c>
-      <c r="AU7" s="14">
+      <c r="AU7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="14">
         <v>70</v>
       </c>
-      <c r="AV7" s="15" t="s">
+      <c r="AW7" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AW7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX7" s="14">
+      <c r="AX7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY7" s="14">
         <v>50</v>
       </c>
-      <c r="AY7" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC7" s="4" t="s">
+      <c r="AZ7" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD7" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="BD7" s="5" t="s">
+      <c r="BE7" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="BE7" s="4" t="s">
+      <c r="BF7" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>50</v>
       </c>
@@ -5577,26 +5602,26 @@
       <c r="Y8" s="11">
         <v>1</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="Z8" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="13">
         <v>1100</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>90</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>15</v>
       </c>
-      <c r="AC8" s="13">
-        <v>0</v>
-      </c>
       <c r="AD8" s="13">
         <v>0</v>
       </c>
-      <c r="AE8" s="11">
-        <v>1</v>
+      <c r="AE8" s="13">
+        <v>0</v>
       </c>
       <c r="AF8" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" s="11">
         <v>0</v>
@@ -5619,47 +5644,50 @@
       <c r="AM8" s="11">
         <v>0</v>
       </c>
-      <c r="AP8" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ8" s="10">
+      <c r="AN8" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="10">
         <v>16</v>
       </c>
-      <c r="AR8" s="10">
-        <v>1</v>
-      </c>
       <c r="AS8" s="10">
         <v>1</v>
       </c>
       <c r="AT8" s="10">
         <v>1</v>
       </c>
-      <c r="AU8" s="14">
+      <c r="AU8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="14">
         <v>70</v>
       </c>
-      <c r="AV8" s="15" t="s">
+      <c r="AW8" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AW8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX8" s="14">
+      <c r="AX8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY8" s="14">
         <v>50</v>
       </c>
-      <c r="AY8" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC8" s="4" t="s">
+      <c r="AZ8" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD8" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="BD8" s="5" t="s">
+      <c r="BE8" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="BE8" s="4" t="s">
+      <c r="BF8" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>50</v>
       </c>
@@ -5720,27 +5748,27 @@
       <c r="Y9" s="11">
         <v>0</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="Z9" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="13">
         <v>1833</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>496</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10</v>
       </c>
-      <c r="AC9" s="13">
-        <v>0</v>
-      </c>
       <c r="AD9" s="13">
         <v>0</v>
       </c>
-      <c r="AE9" s="11">
+      <c r="AE9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="11">
         <v>3</v>
       </c>
-      <c r="AF9" s="11">
-        <v>0</v>
-      </c>
       <c r="AG9" s="11">
         <v>0</v>
       </c>
@@ -5762,47 +5790,50 @@
       <c r="AM9" s="11">
         <v>0</v>
       </c>
-      <c r="AP9" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="10">
+      <c r="AN9" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="10">
         <v>15</v>
       </c>
-      <c r="AR9" s="10">
-        <v>1</v>
-      </c>
       <c r="AS9" s="10">
         <v>1</v>
       </c>
       <c r="AT9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="14">
         <v>70</v>
       </c>
-      <c r="AV9" s="15" t="s">
+      <c r="AW9" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AW9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="14">
+      <c r="AX9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="14">
         <v>50</v>
       </c>
-      <c r="AY9" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC9" s="4" t="s">
+      <c r="AZ9" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD9" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="BD9" s="5" t="s">
+      <c r="BE9" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="BE9" s="4" t="s">
+      <c r="BF9" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>50</v>
       </c>
@@ -5863,26 +5894,26 @@
       <c r="Y10" s="11">
         <v>0</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="Z10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="13">
         <v>2745</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>155</v>
       </c>
-      <c r="AB10" s="13">
-        <v>0</v>
-      </c>
       <c r="AC10" s="13">
         <v>0</v>
       </c>
       <c r="AD10" s="13">
         <v>0</v>
       </c>
-      <c r="AE10" s="11">
-        <v>1</v>
+      <c r="AE10" s="13">
+        <v>0</v>
       </c>
       <c r="AF10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="11">
         <v>0</v>
@@ -5905,47 +5936,50 @@
       <c r="AM10" s="11">
         <v>0</v>
       </c>
-      <c r="AP10" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ10" s="10">
+      <c r="AN10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="10">
         <v>13</v>
       </c>
-      <c r="AR10" s="10">
-        <v>1</v>
-      </c>
       <c r="AS10" s="10">
         <v>1</v>
       </c>
       <c r="AT10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="14">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="14">
         <v>70</v>
       </c>
-      <c r="AV10" s="15" t="s">
+      <c r="AW10" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AW10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX10" s="14">
+      <c r="AX10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY10" s="14">
         <v>50</v>
       </c>
-      <c r="AY10" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC10" s="4" t="s">
+      <c r="AZ10" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD10" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="BD10" s="5" t="s">
+      <c r="BE10" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="BE10" s="4" t="s">
+      <c r="BF10" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>278</v>
       </c>
@@ -6006,26 +6040,26 @@
       <c r="Y11" s="11">
         <v>3</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="Z11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="13">
         <v>1220</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>110</v>
       </c>
-      <c r="AB11" s="13">
-        <v>0</v>
-      </c>
       <c r="AC11" s="13">
         <v>0</v>
       </c>
       <c r="AD11" s="13">
         <v>0</v>
       </c>
-      <c r="AE11" s="11">
-        <v>1</v>
+      <c r="AE11" s="13">
+        <v>0</v>
       </c>
       <c r="AF11" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" s="11">
         <v>0</v>
@@ -6048,47 +6082,50 @@
       <c r="AM11" s="11">
         <v>0</v>
       </c>
-      <c r="AP11" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ11" s="10">
+      <c r="AN11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="10">
         <v>15</v>
       </c>
-      <c r="AR11" s="10">
-        <v>1</v>
-      </c>
       <c r="AS11" s="10">
         <v>1</v>
       </c>
       <c r="AT11" s="10">
         <v>1</v>
       </c>
-      <c r="AU11" s="14">
+      <c r="AU11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="14">
         <v>70</v>
       </c>
-      <c r="AV11" s="15" t="s">
+      <c r="AW11" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="AW11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AX11" s="14">
+      <c r="AX11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY11" s="14">
         <v>50</v>
       </c>
-      <c r="AY11" s="10">
-        <v>1</v>
-      </c>
-      <c r="BC11" s="4" t="s">
+      <c r="AZ11" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="BD11" s="5" t="s">
+      <c r="BE11" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="BE11" s="4" t="s">
+      <c r="BF11" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
@@ -6147,26 +6184,26 @@
       <c r="Y12" s="11">
         <v>0</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="Z12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="13">
         <v>5500</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>265</v>
       </c>
-      <c r="AB12" s="13">
-        <v>0</v>
-      </c>
       <c r="AC12" s="13">
         <v>0</v>
       </c>
       <c r="AD12" s="13">
         <v>0</v>
       </c>
-      <c r="AE12" s="11">
-        <v>1</v>
+      <c r="AE12" s="13">
+        <v>0</v>
       </c>
       <c r="AF12" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="11">
         <v>0</v>
@@ -6189,29 +6226,32 @@
       <c r="AM12" s="11">
         <v>0</v>
       </c>
-      <c r="AP12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ12" s="13">
+      <c r="AN12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA12" s="13">
         <v>0.5</v>
       </c>
-      <c r="BA12" s="11">
-        <v>1</v>
-      </c>
       <c r="BB12" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC12" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD12" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD12" s="5" t="s">
+      <c r="BE12" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="BE12" s="4" t="s">
+      <c r="BF12" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="13" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>61</v>
       </c>
@@ -6270,26 +6310,26 @@
       <c r="Y13" s="11">
         <v>0</v>
       </c>
-      <c r="Z13" s="13">
+      <c r="Z13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="13">
         <v>4590</v>
       </c>
-      <c r="AA13" s="13">
+      <c r="AB13" s="13">
         <v>185</v>
       </c>
-      <c r="AB13" s="13">
-        <v>0</v>
-      </c>
       <c r="AC13" s="13">
         <v>0</v>
       </c>
       <c r="AD13" s="13">
         <v>0</v>
       </c>
-      <c r="AE13" s="11">
-        <v>1</v>
+      <c r="AE13" s="13">
+        <v>0</v>
       </c>
       <c r="AF13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" s="11">
         <v>0</v>
@@ -6312,29 +6352,32 @@
       <c r="AM13" s="11">
         <v>0</v>
       </c>
-      <c r="AP13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ13" s="13">
+      <c r="AN13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA13" s="13">
         <v>0.45</v>
       </c>
-      <c r="BA13" s="11">
-        <v>1</v>
-      </c>
       <c r="BB13" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC13" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD13" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD13" s="5" t="s">
+      <c r="BE13" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="BE13" s="4" t="s">
+      <c r="BF13" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="14" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>61</v>
       </c>
@@ -6390,26 +6433,26 @@
       <c r="Y14" s="11">
         <v>0</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="Z14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="13">
         <v>12000</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>325</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>10</v>
       </c>
-      <c r="AC14" s="13">
-        <v>0</v>
-      </c>
       <c r="AD14" s="13">
         <v>0</v>
       </c>
-      <c r="AE14" s="11">
-        <v>1</v>
+      <c r="AE14" s="13">
+        <v>0</v>
       </c>
       <c r="AF14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="11">
         <v>0</v>
@@ -6432,29 +6475,32 @@
       <c r="AM14" s="11">
         <v>0</v>
       </c>
-      <c r="AP14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ14" s="13">
+      <c r="AN14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA14" s="13">
         <v>0.4</v>
       </c>
-      <c r="BA14" s="11">
-        <v>1</v>
-      </c>
       <c r="BB14" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC14" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC14" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD14" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD14" s="5" t="s">
+      <c r="BE14" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="BE14" s="4" t="s">
+      <c r="BF14" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="15" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>61</v>
       </c>
@@ -6513,26 +6559,26 @@
       <c r="Y15" s="11">
         <v>1</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="Z15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="13">
         <v>12500</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>375</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>50</v>
       </c>
-      <c r="AC15" s="13">
-        <v>0</v>
-      </c>
       <c r="AD15" s="13">
         <v>0</v>
       </c>
-      <c r="AE15" s="11">
-        <v>1</v>
+      <c r="AE15" s="13">
+        <v>0</v>
       </c>
       <c r="AF15" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" s="11">
         <v>0</v>
@@ -6555,26 +6601,29 @@
       <c r="AM15" s="11">
         <v>0</v>
       </c>
-      <c r="AP15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ15" s="13">
+      <c r="AN15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA15" s="13">
         <v>0.25</v>
       </c>
-      <c r="BA15" s="11">
-        <v>1</v>
-      </c>
       <c r="BB15" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC15" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD15" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD15" s="5" t="s">
+      <c r="BE15" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="16" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>61</v>
       </c>
@@ -6630,26 +6679,26 @@
       <c r="Y16" s="11">
         <v>0</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="Z16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="13">
         <v>1235</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>65</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>5</v>
       </c>
-      <c r="AC16" s="13">
-        <v>0</v>
-      </c>
       <c r="AD16" s="13">
         <v>0</v>
       </c>
-      <c r="AE16" s="11">
-        <v>1</v>
+      <c r="AE16" s="13">
+        <v>0</v>
       </c>
       <c r="AF16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="11">
         <v>0</v>
@@ -6672,26 +6721,29 @@
       <c r="AM16" s="11">
         <v>0</v>
       </c>
-      <c r="AP16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="13">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="11">
-        <v>1</v>
+      <c r="AN16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="13">
+        <v>0</v>
       </c>
       <c r="BB16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC16" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD16" s="5" t="s">
+      <c r="BE16" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>61</v>
       </c>
@@ -6747,26 +6799,26 @@
       <c r="Y17" s="11">
         <v>0</v>
       </c>
-      <c r="Z17" s="13">
+      <c r="Z17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="13">
         <v>3600</v>
       </c>
-      <c r="AA17" s="13">
+      <c r="AB17" s="13">
         <v>150</v>
       </c>
-      <c r="AB17" s="13">
+      <c r="AC17" s="13">
         <v>5</v>
       </c>
-      <c r="AC17" s="13">
-        <v>0</v>
-      </c>
       <c r="AD17" s="13">
         <v>0</v>
       </c>
-      <c r="AE17" s="11">
-        <v>1</v>
+      <c r="AE17" s="13">
+        <v>0</v>
       </c>
       <c r="AF17" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" s="11">
         <v>0</v>
@@ -6789,32 +6841,35 @@
       <c r="AM17" s="11">
         <v>0</v>
       </c>
-      <c r="AN17" s="12" t="s">
+      <c r="AN17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="AO17" s="11" t="s">
+      <c r="AP17" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="AP17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ17" s="13">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="11">
-        <v>1</v>
+      <c r="AQ17" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA17" s="13">
+        <v>0</v>
       </c>
       <c r="BB17" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC17" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC17" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD17" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD17" s="5" t="s">
+      <c r="BE17" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>61</v>
       </c>
@@ -6870,26 +6925,26 @@
       <c r="Y18" s="11">
         <v>0</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="Z18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="13">
         <v>6900</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>235</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>5</v>
       </c>
-      <c r="AC18" s="13">
-        <v>0</v>
-      </c>
       <c r="AD18" s="13">
         <v>0</v>
       </c>
-      <c r="AE18" s="11">
-        <v>1</v>
+      <c r="AE18" s="13">
+        <v>0</v>
       </c>
       <c r="AF18" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="11">
         <v>0</v>
@@ -6912,32 +6967,35 @@
       <c r="AM18" s="11">
         <v>0</v>
       </c>
-      <c r="AN18" s="12" t="s">
+      <c r="AN18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="AO18" s="11" t="s">
+      <c r="AP18" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="AP18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ18" s="13">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="11">
-        <v>1</v>
+      <c r="AQ18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA18" s="13">
+        <v>0</v>
       </c>
       <c r="BB18" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC18" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD18" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD18" s="5" t="s">
+      <c r="BE18" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>61</v>
       </c>
@@ -6990,26 +7048,26 @@
       <c r="Y19" s="11">
         <v>1</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="Z19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="13">
         <v>5000</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AB19" s="13">
         <v>500</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AC19" s="13">
         <v>50</v>
       </c>
-      <c r="AC19" s="13">
-        <v>0</v>
-      </c>
       <c r="AD19" s="13">
         <v>0</v>
       </c>
-      <c r="AE19" s="11">
-        <v>1</v>
+      <c r="AE19" s="13">
+        <v>0</v>
       </c>
       <c r="AF19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG19" s="11">
         <v>0</v>
@@ -7032,26 +7090,29 @@
       <c r="AM19" s="11">
         <v>0</v>
       </c>
-      <c r="AP19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ19" s="13">
+      <c r="AN19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA19" s="13">
         <v>0.45</v>
       </c>
-      <c r="BA19" s="11">
+      <c r="BB19" s="11">
         <v>2</v>
       </c>
-      <c r="BB19" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC19" s="4" t="s">
+      <c r="BC19" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD19" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD19" s="5" t="s">
+      <c r="BE19" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>61</v>
       </c>
@@ -7107,12 +7168,12 @@
       <c r="Y20" s="11">
         <v>0</v>
       </c>
-      <c r="Z20" s="13">
+      <c r="Z20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="13">
         <v>100</v>
       </c>
-      <c r="AA20" s="13">
-        <v>0</v>
-      </c>
       <c r="AB20" s="13">
         <v>0</v>
       </c>
@@ -7122,7 +7183,7 @@
       <c r="AD20" s="13">
         <v>0</v>
       </c>
-      <c r="AE20" s="11">
+      <c r="AE20" s="13">
         <v>0</v>
       </c>
       <c r="AF20" s="11">
@@ -7149,17 +7210,17 @@
       <c r="AM20" s="11">
         <v>0</v>
       </c>
-      <c r="AN20" s="12" t="s">
+      <c r="AN20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="AO20" s="11" t="s">
+      <c r="AP20" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="AP20" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ20" s="10">
-        <v>0</v>
+      <c r="AQ20" s="11">
+        <v>1</v>
       </c>
       <c r="AR20" s="10">
         <v>0</v>
@@ -7170,29 +7231,32 @@
       <c r="AT20" s="10">
         <v>0</v>
       </c>
-      <c r="AU20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="15" t="s">
+      <c r="AU20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AW20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AX20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AY20" s="10">
-        <v>0</v>
-      </c>
-      <c r="BC20" s="4" t="s">
+      <c r="AX20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY20" s="14">
+        <v>0</v>
+      </c>
+      <c r="AZ20" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD20" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD20" s="5" t="s">
+      <c r="BE20" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>61</v>
       </c>
@@ -7251,29 +7315,29 @@
       <c r="Y21" s="11">
         <v>1</v>
       </c>
-      <c r="Z21" s="13">
+      <c r="Z21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="13">
         <v>32500</v>
       </c>
-      <c r="AA21" s="13">
+      <c r="AB21" s="13">
         <v>700</v>
       </c>
-      <c r="AB21" s="13">
+      <c r="AC21" s="13">
         <v>50</v>
       </c>
-      <c r="AC21" s="13">
-        <v>0</v>
-      </c>
       <c r="AD21" s="13">
         <v>0</v>
       </c>
-      <c r="AE21" s="11">
-        <v>1</v>
+      <c r="AE21" s="13">
+        <v>0</v>
       </c>
       <c r="AF21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG21" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="11">
         <v>1</v>
@@ -7293,26 +7357,29 @@
       <c r="AM21" s="11">
         <v>1</v>
       </c>
-      <c r="AP21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AZ21" s="13">
+      <c r="AN21" s="11">
+        <v>1</v>
+      </c>
+      <c r="AQ21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA21" s="13">
         <v>0.3</v>
       </c>
-      <c r="BA21" s="11">
+      <c r="BB21" s="11">
         <v>7</v>
       </c>
-      <c r="BB21" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC21" s="4" t="s">
+      <c r="BC21" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD21" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD21" s="5" t="s">
+      <c r="BE21" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>171</v>
       </c>
@@ -7353,12 +7420,12 @@
       <c r="Y22" s="11">
         <v>1</v>
       </c>
-      <c r="Z22" s="13">
+      <c r="Z22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="13">
         <v>100</v>
       </c>
-      <c r="AA22" s="13">
-        <v>0</v>
-      </c>
       <c r="AB22" s="13">
         <v>0</v>
       </c>
@@ -7368,7 +7435,7 @@
       <c r="AD22" s="13">
         <v>0</v>
       </c>
-      <c r="AE22" s="11">
+      <c r="AE22" s="13">
         <v>0</v>
       </c>
       <c r="AF22" s="11">
@@ -7395,21 +7462,24 @@
       <c r="AM22" s="11">
         <v>0</v>
       </c>
-      <c r="AP22" s="11">
-        <v>0</v>
-      </c>
-      <c r="BC22" s="4" t="s">
+      <c r="AN22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD22" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BD22" s="5" t="s">
+      <c r="BE22" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="BE22" s="4" t="s">
+      <c r="BF22" s="4" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BB4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BC4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2266A-373B-4A22-9A0F-D4C9C4BBE789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC74D292-D274-4BF7-AB05-F181D57150EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="301">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4034,6 +4034,14 @@
   </si>
   <si>
     <t>索敌优先级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Monsters/MC/AllTypeSlime/spine/ReferenceAssets/slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Monsters/MC/AllTypeSlime/talents/slime_t1"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6041,7 +6049,7 @@
         <v>3</v>
       </c>
       <c r="Z11" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA11" s="13">
         <v>1220</v>
@@ -6742,6 +6750,9 @@
       <c r="BE16" s="5" t="s">
         <v>258</v>
       </c>
+      <c r="BF16" s="4" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
@@ -6866,7 +6877,10 @@
         <v>258</v>
       </c>
       <c r="BE17" s="5" t="s">
-        <v>258</v>
+        <v>300</v>
+      </c>
+      <c r="BF17" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
@@ -6992,7 +7006,10 @@
         <v>258</v>
       </c>
       <c r="BE18" s="5" t="s">
-        <v>258</v>
+        <v>300</v>
+      </c>
+      <c r="BF18" s="4" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC74D292-D274-4BF7-AB05-F181D57150EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E90F15-412E-4853-B4E6-005821CFB2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="366">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4042,6 +4042,1626 @@
   </si>
   <si>
     <t>["Prefabs/Monsters/MC/AllTypeSlime/talents/slime_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/6/Eyjafjalla/talents/lavabubble_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/6/Eyjafjalla/talents/eyjafjalla_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Monsters/MC/Creeper/talents/creeper_t1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s1"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Adnach/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安德切尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Adnach/Adnach</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Adnach/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安德切尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安德切尔</t>
+  </si>
+  <si>
+    <t>Adnachiel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Wyvern/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>香草</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ansel/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安赛尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ardign/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡缇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Beagle/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>米格鲁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Catap/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>空爆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Falco/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翎羽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Fang/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Lava/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炎熔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Midn/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月见夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Orchid/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梓兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Popka/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>泡普卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Wyvern/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>半身像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>香草</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ansel/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安赛尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ardign/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡缇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Beagle/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>米格鲁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Catap/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>空爆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Falco/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翎羽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Fang/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Lava/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炎熔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Midn/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月见夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Orchid/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梓兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Popka/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>泡普卡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Wyvern/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>香草</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ansel/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安赛尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Ansel/Ansel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Ardign/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>卡缇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Ardign/Ardign</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Beagle/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>米格鲁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Beagle/Beagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Catap/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>空爆</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Catap/Catap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Falco/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>翎羽</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Falco/Falco</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Fang/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>芬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Fang/Fang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Lava/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炎熔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Lava/Lava</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Midn/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月见夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Midn/Midn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Orchid/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>梓兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Orchid/Orchid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Popka/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>泡普卡</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Popka/Popka</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Wyvern/Wyvern</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安赛尔</t>
+  </si>
+  <si>
+    <t>卡缇</t>
+  </si>
+  <si>
+    <t>米格鲁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翎羽</t>
+  </si>
+  <si>
+    <t>空爆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炎熔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月见夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梓兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡普卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香草</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4053,7 +5673,7 @@
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4101,6 +5721,19 @@
       <name val="Times New Roman"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -4573,7 +6206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG22"/>
+  <dimension ref="A1:BG34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.58203125" style="9" customWidth="1"/>
@@ -5248,10 +6881,10 @@
       <c r="BB5" s="24"/>
       <c r="BC5" s="24"/>
       <c r="BD5" s="4" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="BE5" s="5" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="BF5" s="4" t="s">
         <v>259</v>
@@ -6133,1365 +7766,1788 @@
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B12" s="10">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>125</v>
+        <v>8</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>309</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>126</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E12" s="35"/>
       <c r="F12" s="9" t="s">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>153</v>
+        <v>306</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>308</v>
       </c>
       <c r="J12" s="10">
-        <v>2</v>
-      </c>
-      <c r="L12" s="16"/>
-      <c r="O12" s="10">
-        <v>0</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>1</v>
-      </c>
-      <c r="R12" s="10">
-        <v>1</v>
-      </c>
-      <c r="S12" s="10">
-        <v>1</v>
-      </c>
-      <c r="T12" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U12" s="13">
-        <v>0</v>
-      </c>
-      <c r="V12" s="13">
-        <v>400</v>
-      </c>
-      <c r="W12" s="13">
-        <v>2</v>
-      </c>
-      <c r="X12" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>5500</v>
-      </c>
-      <c r="AB12" s="13">
-        <v>265</v>
-      </c>
-      <c r="AC12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA12" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="BB12" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC12" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE12" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="BF12" s="4" t="s">
-        <v>265</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K12" s="11">
+        <v>3</v>
+      </c>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="AW12" s="15"/>
+      <c r="BE12" s="5"/>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B13" s="10">
-        <v>2</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>129</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="E13" s="35"/>
       <c r="F13" s="9" t="s">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>154</v>
+        <v>334</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>323</v>
       </c>
       <c r="J13" s="10">
-        <v>2</v>
-      </c>
-      <c r="L13" s="16"/>
-      <c r="O13" s="10">
-        <v>0</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>1</v>
-      </c>
-      <c r="R13" s="10">
-        <v>1</v>
-      </c>
-      <c r="S13" s="10">
-        <v>1</v>
-      </c>
-      <c r="T13" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="13">
-        <v>2.8279999999999998</v>
-      </c>
-      <c r="V13" s="13">
-        <v>395</v>
-      </c>
-      <c r="W13" s="13">
-        <v>5</v>
-      </c>
-      <c r="X13" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="13">
-        <v>4590</v>
-      </c>
-      <c r="AB13" s="13">
-        <v>185</v>
-      </c>
-      <c r="AC13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA13" s="13">
-        <v>0.45</v>
-      </c>
-      <c r="BB13" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC13" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD13" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE13" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="BF13" s="4" t="s">
-        <v>266</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K13" s="11">
+        <v>3</v>
+      </c>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="AW13" s="15"/>
+      <c r="BE13" s="5"/>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B14" s="10">
+        <v>10</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="E14" s="35"/>
+      <c r="F14" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11">
         <v>3</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="J14" s="10">
-        <v>2</v>
-      </c>
-      <c r="L14" s="16"/>
-      <c r="O14" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>1</v>
-      </c>
-      <c r="R14" s="10">
-        <v>1</v>
-      </c>
-      <c r="S14" s="10">
-        <v>1</v>
-      </c>
-      <c r="T14" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U14" s="13">
-        <v>1.4139999999999999</v>
-      </c>
-      <c r="V14" s="13">
-        <v>1050</v>
-      </c>
-      <c r="W14" s="13">
-        <v>3</v>
-      </c>
-      <c r="X14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>12000</v>
-      </c>
-      <c r="AB14" s="13">
-        <v>325</v>
-      </c>
-      <c r="AC14" s="13">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA14" s="13">
-        <v>0.4</v>
-      </c>
-      <c r="BB14" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC14" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD14" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE14" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="BF14" s="4" t="s">
-        <v>296</v>
-      </c>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="AW14" s="15"/>
+      <c r="BE14" s="5"/>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B15" s="10">
-        <v>4</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>132</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="E15" s="35"/>
       <c r="F15" s="9" t="s">
-        <v>164</v>
+        <v>339</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>156</v>
+        <v>338</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J15" s="10">
-        <v>2</v>
-      </c>
-      <c r="L15" s="16"/>
-      <c r="O15" s="10">
-        <v>1</v>
-      </c>
-      <c r="P15" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>1</v>
-      </c>
-      <c r="R15" s="10">
-        <v>1</v>
-      </c>
-      <c r="S15" s="10">
-        <v>1</v>
-      </c>
-      <c r="T15" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U15" s="13">
+        <v>1</v>
+      </c>
+      <c r="K15" s="11">
         <v>3</v>
       </c>
-      <c r="V15" s="13">
-        <v>200</v>
-      </c>
-      <c r="W15" s="13">
-        <v>5</v>
-      </c>
-      <c r="X15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>12500</v>
-      </c>
-      <c r="AB15" s="13">
-        <v>375</v>
-      </c>
-      <c r="AC15" s="13">
-        <v>50</v>
-      </c>
-      <c r="AD15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA15" s="13">
-        <v>0.25</v>
-      </c>
-      <c r="BB15" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC15" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD15" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE15" s="5" t="s">
-        <v>258</v>
-      </c>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="AW15" s="15"/>
+      <c r="BE15" s="5"/>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B16" s="10">
-        <v>6</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>135</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="E16" s="35"/>
       <c r="F16" s="9" t="s">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>157</v>
+        <v>340</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>326</v>
       </c>
       <c r="J16" s="10">
-        <v>2</v>
-      </c>
-      <c r="L16" s="16"/>
-      <c r="O16" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>1</v>
-      </c>
-      <c r="R16" s="10">
-        <v>1</v>
-      </c>
-      <c r="S16" s="10">
-        <v>1</v>
-      </c>
-      <c r="T16" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U16" s="13">
-        <v>0</v>
-      </c>
-      <c r="V16" s="13">
-        <v>290</v>
-      </c>
-      <c r="W16" s="13">
-        <v>2</v>
-      </c>
-      <c r="X16" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>1235</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>65</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>5</v>
-      </c>
-      <c r="AD16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB16" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC16" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD16" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE16" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="BF16" s="4" t="s">
-        <v>299</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K16" s="11">
+        <v>3</v>
+      </c>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="AW16" s="15"/>
+      <c r="BE16" s="5"/>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B17" s="10">
-        <v>7</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>137</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="E17" s="35"/>
       <c r="F17" s="9" t="s">
-        <v>166</v>
+        <v>343</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>158</v>
+        <v>342</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>327</v>
       </c>
       <c r="J17" s="10">
-        <v>2</v>
-      </c>
-      <c r="L17" s="16"/>
-      <c r="O17" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>1</v>
-      </c>
-      <c r="R17" s="10">
-        <v>1</v>
-      </c>
-      <c r="S17" s="10">
-        <v>1</v>
-      </c>
-      <c r="T17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U17" s="13">
-        <v>0</v>
-      </c>
-      <c r="V17" s="13">
-        <v>430</v>
-      </c>
-      <c r="W17" s="13">
-        <v>4</v>
-      </c>
-      <c r="X17" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>3600</v>
-      </c>
-      <c r="AB17" s="13">
-        <v>150</v>
-      </c>
-      <c r="AC17" s="13">
-        <v>5</v>
-      </c>
-      <c r="AD17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="AP17" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB17" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC17" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD17" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE17" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="BF17" s="4" t="s">
-        <v>299</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K17" s="11">
+        <v>3</v>
+      </c>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="AW17" s="15"/>
+      <c r="BE17" s="5"/>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B18" s="10">
-        <v>8</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>139</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="E18" s="35"/>
       <c r="F18" s="9" t="s">
-        <v>167</v>
+        <v>345</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>159</v>
+        <v>344</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>328</v>
       </c>
       <c r="J18" s="10">
-        <v>2</v>
-      </c>
-      <c r="L18" s="16"/>
-      <c r="O18" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>1</v>
-      </c>
-      <c r="R18" s="10">
-        <v>1</v>
-      </c>
-      <c r="S18" s="10">
-        <v>1</v>
-      </c>
-      <c r="T18" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U18" s="13">
-        <v>0</v>
-      </c>
-      <c r="V18" s="13">
-        <v>670</v>
-      </c>
-      <c r="W18" s="13">
-        <v>5</v>
-      </c>
-      <c r="X18" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>6900</v>
-      </c>
-      <c r="AB18" s="13">
-        <v>235</v>
-      </c>
-      <c r="AC18" s="13">
-        <v>5</v>
-      </c>
-      <c r="AD18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="AP18" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ18" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA18" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB18" s="11">
-        <v>1</v>
-      </c>
-      <c r="BC18" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD18" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE18" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="BF18" s="4" t="s">
-        <v>299</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K18" s="11">
+        <v>3</v>
+      </c>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="AW18" s="15"/>
+      <c r="BE18" s="5"/>
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B19" s="10">
-        <v>9</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>142</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="E19" s="35"/>
       <c r="F19" s="9" t="s">
-        <v>168</v>
+        <v>347</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>329</v>
       </c>
       <c r="J19" s="10">
-        <v>2</v>
-      </c>
-      <c r="L19" s="16"/>
-      <c r="O19" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="10">
-        <v>0</v>
-      </c>
-      <c r="R19" s="10">
-        <v>0</v>
-      </c>
-      <c r="S19" s="10">
-        <v>0</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U19" s="13">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="V19" s="13">
-        <v>500</v>
-      </c>
-      <c r="W19" s="13">
+        <v>1</v>
+      </c>
+      <c r="K19" s="11">
         <v>3</v>
       </c>
-      <c r="X19" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>5000</v>
-      </c>
-      <c r="AB19" s="13">
-        <v>500</v>
-      </c>
-      <c r="AC19" s="13">
-        <v>50</v>
-      </c>
-      <c r="AD19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA19" s="13">
-        <v>0.45</v>
-      </c>
-      <c r="BB19" s="11">
-        <v>2</v>
-      </c>
-      <c r="BC19" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD19" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE19" s="5" t="s">
-        <v>258</v>
-      </c>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="AW19" s="15"/>
+      <c r="BE19" s="5"/>
     </row>
     <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B20" s="10">
-        <v>10</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>143</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="35"/>
       <c r="F20" s="9" t="s">
-        <v>169</v>
+        <v>349</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>330</v>
       </c>
       <c r="J20" s="10">
-        <v>2</v>
-      </c>
-      <c r="L20" s="16"/>
-      <c r="O20" s="10">
-        <v>0</v>
-      </c>
-      <c r="P20" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q20" s="10">
-        <v>0</v>
-      </c>
-      <c r="R20" s="10">
-        <v>0</v>
-      </c>
-      <c r="S20" s="10">
-        <v>0</v>
-      </c>
-      <c r="T20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U20" s="13">
-        <v>0</v>
-      </c>
-      <c r="V20" s="13">
-        <v>100</v>
-      </c>
-      <c r="W20" s="13">
-        <v>2</v>
-      </c>
-      <c r="X20" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>100</v>
-      </c>
-      <c r="AB20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="AP20" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ20" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AW20" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="AX20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AY20" s="14">
-        <v>0</v>
-      </c>
-      <c r="AZ20" s="10">
-        <v>0</v>
-      </c>
-      <c r="BD20" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE20" s="5" t="s">
-        <v>258</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" s="11">
+        <v>3</v>
+      </c>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="AW20" s="15"/>
+      <c r="BE20" s="5"/>
     </row>
     <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>61</v>
+        <v>305</v>
       </c>
       <c r="B21" s="10">
-        <v>11</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>148</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="E21" s="35"/>
       <c r="F21" s="9" t="s">
-        <v>170</v>
+        <v>351</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>160</v>
+        <v>350</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>331</v>
       </c>
       <c r="J21" s="10">
-        <v>2</v>
-      </c>
-      <c r="L21" s="16"/>
-      <c r="O21" s="10">
-        <v>2</v>
-      </c>
-      <c r="P21" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q21" s="10">
-        <v>1</v>
-      </c>
-      <c r="R21" s="10">
-        <v>1</v>
-      </c>
-      <c r="S21" s="10">
-        <v>2</v>
-      </c>
-      <c r="T21" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="U21" s="13">
+        <v>1</v>
+      </c>
+      <c r="K21" s="11">
         <v>3</v>
       </c>
-      <c r="V21" s="13">
-        <v>650</v>
-      </c>
-      <c r="W21" s="13">
-        <v>5</v>
-      </c>
-      <c r="X21" s="11">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="13">
-        <v>32500</v>
-      </c>
-      <c r="AB21" s="13">
-        <v>700</v>
-      </c>
-      <c r="AC21" s="13">
-        <v>50</v>
-      </c>
-      <c r="AD21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AI21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AK21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AL21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AM21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AN21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AQ21" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA21" s="13">
-        <v>0.3</v>
-      </c>
-      <c r="BB21" s="11">
-        <v>7</v>
-      </c>
-      <c r="BC21" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD21" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BE21" s="5" t="s">
-        <v>258</v>
-      </c>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="AW21" s="15"/>
+      <c r="BE21" s="5"/>
     </row>
     <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B22" s="10">
+        <v>18</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="J22" s="10">
+        <v>1</v>
+      </c>
+      <c r="K22" s="11">
+        <v>3</v>
+      </c>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="AW22" s="15"/>
+      <c r="BE22" s="5"/>
+    </row>
+    <row r="23" spans="1:58" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B23" s="10">
+        <v>19</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="J23" s="10">
+        <v>1</v>
+      </c>
+      <c r="K23" s="11">
+        <v>3</v>
+      </c>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="AW23" s="15"/>
+      <c r="BE23" s="5"/>
+    </row>
+    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="10">
+        <v>2</v>
+      </c>
+      <c r="L24" s="16"/>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q24" s="10">
+        <v>1</v>
+      </c>
+      <c r="R24" s="10">
+        <v>1</v>
+      </c>
+      <c r="S24" s="10">
+        <v>1</v>
+      </c>
+      <c r="T24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U24" s="13">
+        <v>0</v>
+      </c>
+      <c r="V24" s="13">
+        <v>400</v>
+      </c>
+      <c r="W24" s="13">
+        <v>2</v>
+      </c>
+      <c r="X24" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="13">
+        <v>5500</v>
+      </c>
+      <c r="AB24" s="13">
+        <v>265</v>
+      </c>
+      <c r="AC24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA24" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="BB24" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD24" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE24" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="BF24" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="10">
+        <v>2</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="10">
+        <v>2</v>
+      </c>
+      <c r="L25" s="16"/>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q25" s="10">
+        <v>1</v>
+      </c>
+      <c r="R25" s="10">
+        <v>1</v>
+      </c>
+      <c r="S25" s="10">
+        <v>1</v>
+      </c>
+      <c r="T25" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U25" s="13">
+        <v>2.8279999999999998</v>
+      </c>
+      <c r="V25" s="13">
+        <v>395</v>
+      </c>
+      <c r="W25" s="13">
+        <v>5</v>
+      </c>
+      <c r="X25" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="13">
+        <v>4590</v>
+      </c>
+      <c r="AB25" s="13">
+        <v>185</v>
+      </c>
+      <c r="AC25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA25" s="13">
+        <v>0.45</v>
+      </c>
+      <c r="BB25" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD25" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE25" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="BF25" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="10">
+        <v>3</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J26" s="10">
+        <v>2</v>
+      </c>
+      <c r="L26" s="16"/>
+      <c r="O26" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="10">
+        <v>1</v>
+      </c>
+      <c r="R26" s="10">
+        <v>1</v>
+      </c>
+      <c r="S26" s="10">
+        <v>1</v>
+      </c>
+      <c r="T26" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U26" s="13">
+        <v>1.4139999999999999</v>
+      </c>
+      <c r="V26" s="13">
+        <v>1050</v>
+      </c>
+      <c r="W26" s="13">
+        <v>3</v>
+      </c>
+      <c r="X26" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="13">
+        <v>12000</v>
+      </c>
+      <c r="AB26" s="13">
+        <v>325</v>
+      </c>
+      <c r="AC26" s="13">
+        <v>10</v>
+      </c>
+      <c r="AD26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA26" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="BB26" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD26" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE26" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="BF26" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A27" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="10">
+        <v>4</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27" s="10">
+        <v>2</v>
+      </c>
+      <c r="L27" s="16"/>
+      <c r="O27" s="10">
+        <v>1</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q27" s="10">
+        <v>1</v>
+      </c>
+      <c r="R27" s="10">
+        <v>1</v>
+      </c>
+      <c r="S27" s="10">
+        <v>1</v>
+      </c>
+      <c r="T27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U27" s="13">
+        <v>3</v>
+      </c>
+      <c r="V27" s="13">
+        <v>200</v>
+      </c>
+      <c r="W27" s="13">
+        <v>5</v>
+      </c>
+      <c r="X27" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="13">
+        <v>12500</v>
+      </c>
+      <c r="AB27" s="13">
+        <v>375</v>
+      </c>
+      <c r="AC27" s="13">
+        <v>50</v>
+      </c>
+      <c r="AD27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA27" s="13">
+        <v>0.25</v>
+      </c>
+      <c r="BB27" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD27" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE27" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="10">
+        <v>6</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="10">
+        <v>2</v>
+      </c>
+      <c r="L28" s="16"/>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="10">
+        <v>1</v>
+      </c>
+      <c r="R28" s="10">
+        <v>1</v>
+      </c>
+      <c r="S28" s="10">
+        <v>1</v>
+      </c>
+      <c r="T28" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U28" s="13">
+        <v>0</v>
+      </c>
+      <c r="V28" s="13">
+        <v>290</v>
+      </c>
+      <c r="W28" s="13">
+        <v>2</v>
+      </c>
+      <c r="X28" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="13">
+        <v>1235</v>
+      </c>
+      <c r="AB28" s="13">
+        <v>65</v>
+      </c>
+      <c r="AC28" s="13">
+        <v>5</v>
+      </c>
+      <c r="AD28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA28" s="13">
+        <v>0</v>
+      </c>
+      <c r="BB28" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC28" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD28" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE28" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="BF28" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A29" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="10">
+        <v>7</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J29" s="10">
+        <v>2</v>
+      </c>
+      <c r="L29" s="16"/>
+      <c r="O29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="10">
+        <v>1</v>
+      </c>
+      <c r="R29" s="10">
+        <v>1</v>
+      </c>
+      <c r="S29" s="10">
+        <v>1</v>
+      </c>
+      <c r="T29" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U29" s="13">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13">
+        <v>430</v>
+      </c>
+      <c r="W29" s="13">
+        <v>4</v>
+      </c>
+      <c r="X29" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="13">
+        <v>3600</v>
+      </c>
+      <c r="AB29" s="13">
+        <v>150</v>
+      </c>
+      <c r="AC29" s="13">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP29" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="AQ29" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA29" s="13">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC29" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD29" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE29" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="BF29" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="10">
+        <v>8</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J30" s="10">
+        <v>2</v>
+      </c>
+      <c r="L30" s="16"/>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="10">
+        <v>1</v>
+      </c>
+      <c r="R30" s="10">
+        <v>1</v>
+      </c>
+      <c r="S30" s="10">
+        <v>1</v>
+      </c>
+      <c r="T30" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U30" s="13">
+        <v>0</v>
+      </c>
+      <c r="V30" s="13">
+        <v>670</v>
+      </c>
+      <c r="W30" s="13">
+        <v>5</v>
+      </c>
+      <c r="X30" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="13">
+        <v>6900</v>
+      </c>
+      <c r="AB30" s="13">
+        <v>235</v>
+      </c>
+      <c r="AC30" s="13">
+        <v>5</v>
+      </c>
+      <c r="AD30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="AP30" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="AQ30" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA30" s="13">
+        <v>0</v>
+      </c>
+      <c r="BB30" s="11">
+        <v>1</v>
+      </c>
+      <c r="BC30" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD30" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE30" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="BF30" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="10">
+        <v>9</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="J31" s="10">
+        <v>2</v>
+      </c>
+      <c r="L31" s="16"/>
+      <c r="O31" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="10">
+        <v>0</v>
+      </c>
+      <c r="R31" s="10">
+        <v>0</v>
+      </c>
+      <c r="S31" s="10">
+        <v>0</v>
+      </c>
+      <c r="T31" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U31" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="V31" s="13">
+        <v>500</v>
+      </c>
+      <c r="W31" s="13">
+        <v>3</v>
+      </c>
+      <c r="X31" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="13">
+        <v>5000</v>
+      </c>
+      <c r="AB31" s="13">
+        <v>500</v>
+      </c>
+      <c r="AC31" s="13">
+        <v>50</v>
+      </c>
+      <c r="AD31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA31" s="13">
+        <v>0.45</v>
+      </c>
+      <c r="BB31" s="11">
+        <v>2</v>
+      </c>
+      <c r="BC31" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD31" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE31" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A32" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="10">
+        <v>10</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" s="10">
+        <v>2</v>
+      </c>
+      <c r="L32" s="16"/>
+      <c r="O32" s="10">
+        <v>0</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q32" s="10">
+        <v>0</v>
+      </c>
+      <c r="R32" s="10">
+        <v>0</v>
+      </c>
+      <c r="S32" s="10">
+        <v>0</v>
+      </c>
+      <c r="T32" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U32" s="13">
+        <v>0</v>
+      </c>
+      <c r="V32" s="13">
+        <v>100</v>
+      </c>
+      <c r="W32" s="13">
+        <v>2</v>
+      </c>
+      <c r="X32" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="13">
+        <v>100</v>
+      </c>
+      <c r="AB32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="AP32" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="AQ32" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="AX32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BD32" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE32" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="10">
+        <v>11</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J33" s="10">
+        <v>2</v>
+      </c>
+      <c r="L33" s="16"/>
+      <c r="O33" s="10">
+        <v>2</v>
+      </c>
+      <c r="P33" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>1</v>
+      </c>
+      <c r="R33" s="10">
+        <v>1</v>
+      </c>
+      <c r="S33" s="10">
+        <v>2</v>
+      </c>
+      <c r="T33" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="U33" s="13">
+        <v>3</v>
+      </c>
+      <c r="V33" s="13">
+        <v>650</v>
+      </c>
+      <c r="W33" s="13">
+        <v>5</v>
+      </c>
+      <c r="X33" s="11">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="13">
+        <v>32500</v>
+      </c>
+      <c r="AB33" s="13">
+        <v>700</v>
+      </c>
+      <c r="AC33" s="13">
+        <v>50</v>
+      </c>
+      <c r="AD33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AQ33" s="11">
+        <v>0</v>
+      </c>
+      <c r="BA33" s="13">
+        <v>0.3</v>
+      </c>
+      <c r="BB33" s="11">
+        <v>7</v>
+      </c>
+      <c r="BC33" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD33" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BE33" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
+      <c r="A34" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="B22" s="10">
-        <v>1</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="B34" s="10">
+        <v>1</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E34" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F34" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J34" s="10">
         <v>2</v>
       </c>
-      <c r="L22" s="16"/>
-      <c r="T22" s="12" t="s">
+      <c r="L34" s="16"/>
+      <c r="T34" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="U22" s="13">
+      <c r="U34" s="13">
         <v>1.5</v>
       </c>
-      <c r="V22" s="13">
-        <v>0</v>
-      </c>
-      <c r="W22" s="13">
+      <c r="V34" s="13">
+        <v>0</v>
+      </c>
+      <c r="W34" s="13">
         <v>-1</v>
       </c>
-      <c r="X22" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="13">
+      <c r="X34" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="13">
         <v>100</v>
       </c>
-      <c r="AB22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD22" s="4" t="s">
+      <c r="AB34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="11">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE22" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="BF22" s="4" t="s">
+      <c r="BE34" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="BF34" s="4" t="s">
         <v>267</v>
       </c>
     </row>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E90F15-412E-4853-B4E6-005821CFB2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF57D3C1-49ED-4DAE-B7CF-7742CAF9E633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="439">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4057,10 +4057,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>["Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s1"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>c</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5662,6 +5658,265 @@
   </si>
   <si>
     <t>香草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ansel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cardigan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Beagle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Catapult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plume</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lava</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Midnight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orchid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Popukar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vanilla</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Adnach/skills/adnach_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Adnach/talents/adnach_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Adnach/spine/ReferenceAssets/adnach</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Ansel/skills/ansel_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Ansel/talents/ansel_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Ansel/spine/ReferenceAssets/ansel</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Ardign/skills/ardign_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Ardign/talents/ardign_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Ardign/spine/ReferenceAssets/ardign</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Beagle/skills/beagle_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Beagle/talents/beagle_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Beagle/spine/ReferenceAssets/beagle</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Catap/skills/catap_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Catap/talents/catap_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Catap/spine/ReferenceAssets/catap</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Falco/skills/falco_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Falco/talents/falco_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Falco/spine/ReferenceAssets/falco</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Fang/skills/fang_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Fang/talents/fang_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Fang/spine/ReferenceAssets/fang</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Lava/skills/lava_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Lava/talents/lava_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Lava/spine/ReferenceAssets/lava</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Midn/skills/midn_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Midn/talents/midn_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Midn/spine/ReferenceAssets/midn</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Orchid/skills/orchid_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Orchid/talents/orchid_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Orchid/spine/ReferenceAssets/orchid</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Popka/skills/popka_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Popka/talents/popka_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Popka/spine/ReferenceAssets/popka</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Wyvern/skills/wyvern_s1"]</t>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/3/Wyvern/talents/wyvern_t1"]</t>
+  </si>
+  <si>
+    <t>Prefabs/Characters/3/Wyvern/spine/ReferenceAssets/wyvern</t>
+  </si>
+  <si>
+    <t>——</t>
+  </si>
+  <si>
+    <t>——</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>先锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>辅助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狙击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速射手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>铁卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尖兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩散术师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>领主</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凝滞师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强攻手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1),(0,2),(0,3),(1,0),(1,1),(1,2),(1,3),(-1,0),(-1,1),(-1,2),(-1,3)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1),(0,2),(1,0),(1,1),(1,2),(-1,0),(-1,1),(-1,2)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1),(0,2),(0,3),(0,4),(1,0),(1,1),(1,2),(1,3),(1,4),(-1,0),(-1,1),(-1,2),(-1,3),(-1,4)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,-1),(0,0),(0,1),(0,2),(1,-1),(1,0),(1,1),(1,2),(-1,-1),(-1,0),(-1,1),(-1,2)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[(0,0),(0,1),(0,2),(0,3),(1,0),(1,1),(-1,0),(-1,1)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s1","Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s2"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6881,7 +7136,7 @@
       <c r="BB5" s="24"/>
       <c r="BC5" s="24"/>
       <c r="BD5" s="4" t="s">
-        <v>304</v>
+        <v>438</v>
       </c>
       <c r="BE5" s="5" t="s">
         <v>302</v>
@@ -7766,31 +8021,33 @@
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B12" s="10">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="35" t="s">
+        <v>413</v>
+      </c>
       <c r="F12" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>308</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -7798,34 +8055,145 @@
       <c r="K12" s="11">
         <v>3</v>
       </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="AW12" s="15"/>
-      <c r="BE12" s="5"/>
+      <c r="L12" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M12" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="T12" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="U12" s="13">
+        <v>0</v>
+      </c>
+      <c r="V12" s="13">
+        <v>100</v>
+      </c>
+      <c r="W12" s="13">
+        <v>1</v>
+      </c>
+      <c r="X12" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB12" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR12" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW12" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY12" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ12" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD12" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="BE12" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="BF12" s="4" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B13" s="10">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="E13" s="35"/>
+        <v>354</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F13" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J13" s="10">
         <v>1</v>
@@ -7833,34 +8201,145 @@
       <c r="K13" s="11">
         <v>3</v>
       </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="AW13" s="15"/>
-      <c r="BE13" s="5"/>
+      <c r="L13" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M13" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>422</v>
+      </c>
+      <c r="T13" s="12" t="s">
+        <v>431</v>
+      </c>
+      <c r="U13" s="13">
+        <v>0</v>
+      </c>
+      <c r="V13" s="13">
+        <v>100</v>
+      </c>
+      <c r="W13" s="13">
+        <v>1</v>
+      </c>
+      <c r="X13" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="11">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="11">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB13" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW13" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="BE13" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="BF13" s="4" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B14" s="10">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="E14" s="35"/>
+        <v>355</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F14" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J14" s="10">
         <v>1</v>
@@ -7868,34 +8347,145 @@
       <c r="K14" s="11">
         <v>3</v>
       </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="AW14" s="15"/>
-      <c r="BE14" s="5"/>
+      <c r="L14" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M14" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="N14" s="36" t="s">
+        <v>423</v>
+      </c>
+      <c r="T14" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="U14" s="13">
+        <v>0</v>
+      </c>
+      <c r="V14" s="13">
+        <v>100</v>
+      </c>
+      <c r="W14" s="13">
+        <v>1</v>
+      </c>
+      <c r="X14" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB14" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="11">
+        <v>3</v>
+      </c>
+      <c r="AG14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS14" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW14" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX14" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY14" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ14" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD14" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="BE14" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="BF14" s="4" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B15" s="10">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="E15" s="35"/>
+        <v>356</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F15" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J15" s="10">
         <v>1</v>
@@ -7903,34 +8493,145 @@
       <c r="K15" s="11">
         <v>3</v>
       </c>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="AW15" s="15"/>
-      <c r="BE15" s="5"/>
+      <c r="L15" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M15" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="N15" s="36" t="s">
+        <v>423</v>
+      </c>
+      <c r="T15" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="U15" s="13">
+        <v>0</v>
+      </c>
+      <c r="V15" s="13">
+        <v>100</v>
+      </c>
+      <c r="W15" s="13">
+        <v>1</v>
+      </c>
+      <c r="X15" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB15" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>3</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR15" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV15" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW15" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ15" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="BE15" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="BF15" s="4" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B16" s="10">
         <v>12</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>359</v>
-      </c>
-      <c r="E16" s="35"/>
+        <v>358</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F16" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J16" s="10">
         <v>1</v>
@@ -7938,34 +8639,145 @@
       <c r="K16" s="11">
         <v>3</v>
       </c>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="AW16" s="15"/>
-      <c r="BE16" s="5"/>
+      <c r="L16" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M16" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="N16" s="36" t="s">
+        <v>424</v>
+      </c>
+      <c r="T16" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="U16" s="13">
+        <v>0</v>
+      </c>
+      <c r="V16" s="13">
+        <v>100</v>
+      </c>
+      <c r="W16" s="13">
+        <v>1</v>
+      </c>
+      <c r="X16" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB16" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR16" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV16" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW16" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY16" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ16" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD16" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="BE16" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="BF16" s="4" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="17" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B17" s="10">
         <v>13</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="E17" s="35"/>
+        <v>357</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F17" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
@@ -7973,34 +8785,145 @@
       <c r="K17" s="11">
         <v>3</v>
       </c>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="AW17" s="15"/>
-      <c r="BE17" s="5"/>
+      <c r="L17" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M17" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="N17" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="T17" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="U17" s="13">
+        <v>0</v>
+      </c>
+      <c r="V17" s="13">
+        <v>100</v>
+      </c>
+      <c r="W17" s="13">
+        <v>1</v>
+      </c>
+      <c r="X17" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB17" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR17" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV17" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW17" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY17" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="BE17" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="BF17" s="4" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="18" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B18" s="10">
         <v>14</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="E18" s="35"/>
+        <v>359</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F18" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -8008,34 +8931,145 @@
       <c r="K18" s="11">
         <v>3</v>
       </c>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="AW18" s="15"/>
-      <c r="BE18" s="5"/>
+      <c r="L18" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M18" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="N18" s="36" t="s">
+        <v>426</v>
+      </c>
+      <c r="T18" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="U18" s="13">
+        <v>0</v>
+      </c>
+      <c r="V18" s="13">
+        <v>100</v>
+      </c>
+      <c r="W18" s="13">
+        <v>1</v>
+      </c>
+      <c r="X18" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB18" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="11">
+        <v>2</v>
+      </c>
+      <c r="AG18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW18" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY18" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="BE18" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF18" s="4" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="19" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B19" s="10">
         <v>15</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="E19" s="35"/>
+        <v>360</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F19" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
@@ -8043,34 +9077,145 @@
       <c r="K19" s="11">
         <v>3</v>
       </c>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="AW19" s="15"/>
-      <c r="BE19" s="5"/>
+      <c r="L19" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M19" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="N19" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="T19" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="U19" s="13">
+        <v>0</v>
+      </c>
+      <c r="V19" s="13">
+        <v>100</v>
+      </c>
+      <c r="W19" s="13">
+        <v>1</v>
+      </c>
+      <c r="X19" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB19" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV19" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW19" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY19" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ19" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD19" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="BE19" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="BF19" s="4" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="20" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B20" s="10">
         <v>16</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="E20" s="35"/>
+        <v>361</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F20" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -8078,34 +9223,145 @@
       <c r="K20" s="11">
         <v>3</v>
       </c>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="AW20" s="15"/>
-      <c r="BE20" s="5"/>
+      <c r="L20" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M20" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="N20" s="36" t="s">
+        <v>428</v>
+      </c>
+      <c r="T20" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="U20" s="13">
+        <v>0</v>
+      </c>
+      <c r="V20" s="13">
+        <v>100</v>
+      </c>
+      <c r="W20" s="13">
+        <v>1</v>
+      </c>
+      <c r="X20" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB20" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="11">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW20" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ20" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD20" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="BE20" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="BF20" s="4" t="s">
+        <v>402</v>
+      </c>
     </row>
     <row r="21" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B21" s="10">
         <v>17</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="E21" s="35"/>
+        <v>362</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F21" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J21" s="10">
         <v>1</v>
@@ -8113,34 +9369,145 @@
       <c r="K21" s="11">
         <v>3</v>
       </c>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="AW21" s="15"/>
-      <c r="BE21" s="5"/>
+      <c r="L21" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M21" s="36" t="s">
+        <v>416</v>
+      </c>
+      <c r="N21" s="36" t="s">
+        <v>429</v>
+      </c>
+      <c r="T21" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="U21" s="13">
+        <v>0</v>
+      </c>
+      <c r="V21" s="13">
+        <v>100</v>
+      </c>
+      <c r="W21" s="13">
+        <v>1</v>
+      </c>
+      <c r="X21" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="11">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB21" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="11">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AV21" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW21" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY21" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="BE21" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="BF21" s="4" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="22" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B22" s="10">
         <v>18</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="E22" s="35"/>
+        <v>363</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F22" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -8148,34 +9515,145 @@
       <c r="K22" s="11">
         <v>3</v>
       </c>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="AW22" s="15"/>
-      <c r="BE22" s="5"/>
+      <c r="L22" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M22" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="N22" s="36" t="s">
+        <v>430</v>
+      </c>
+      <c r="T22" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="U22" s="13">
+        <v>0</v>
+      </c>
+      <c r="V22" s="13">
+        <v>100</v>
+      </c>
+      <c r="W22" s="13">
+        <v>1</v>
+      </c>
+      <c r="X22" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB22" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="11">
+        <v>2</v>
+      </c>
+      <c r="AG22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR22" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW22" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD22" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="BE22" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="BF22" s="4" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="23" spans="1:58" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B23" s="10">
         <v>19</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="E23" s="35"/>
+        <v>364</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>412</v>
+      </c>
       <c r="F23" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J23" s="10">
         <v>1</v>
@@ -8183,11 +9661,117 @@
       <c r="K23" s="11">
         <v>3</v>
       </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="AW23" s="15"/>
-      <c r="BE23" s="5"/>
+      <c r="L23" s="36" t="s">
+        <v>412</v>
+      </c>
+      <c r="M23" s="36" t="s">
+        <v>414</v>
+      </c>
+      <c r="N23" s="36" t="s">
+        <v>426</v>
+      </c>
+      <c r="T23" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="U23" s="13">
+        <v>0</v>
+      </c>
+      <c r="V23" s="13">
+        <v>100</v>
+      </c>
+      <c r="W23" s="13">
+        <v>1</v>
+      </c>
+      <c r="X23" s="11">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="13">
+        <v>1000</v>
+      </c>
+      <c r="AB23" s="13">
+        <v>100</v>
+      </c>
+      <c r="AC23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="11">
+        <v>2</v>
+      </c>
+      <c r="AG23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AQ23" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR23" s="10">
+        <v>10</v>
+      </c>
+      <c r="AS23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AT23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AU23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV23" s="14">
+        <v>70</v>
+      </c>
+      <c r="AW23" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AY23" s="14">
+        <v>50</v>
+      </c>
+      <c r="AZ23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="BE23" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="BF23" s="4" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="24" spans="1:58" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF57D3C1-49ED-4DAE-B7CF-7742CAF9E633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEE6321-0170-45AA-92A6-790BD8D26E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="440">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5917,6 +5917,50 @@
   </si>
   <si>
     <t>["Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s1","Prefabs/Characters/6/Eyjafjalla/skills/eyjafjalla_s2"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Prefabs/Characters/3/Adnach/img/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>立绘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>安德切尔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>_1</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7195,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="13">
-        <v>1692</v>
+        <v>1602</v>
       </c>
       <c r="W6" s="13">
         <v>3</v>
@@ -7255,7 +7299,7 @@
         <v>1</v>
       </c>
       <c r="AR6" s="10">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS6" s="10">
         <v>1</v>
@@ -7267,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="AV6" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW6" s="15" t="s">
         <v>196</v>
@@ -7401,7 +7445,7 @@
         <v>1</v>
       </c>
       <c r="AR7" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS7" s="10">
         <v>1</v>
@@ -7413,7 +7457,7 @@
         <v>1</v>
       </c>
       <c r="AV7" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW7" s="15" t="s">
         <v>196</v>
@@ -7487,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="13">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="W8" s="13">
         <v>1.6</v>
@@ -7559,7 +7603,7 @@
         <v>1</v>
       </c>
       <c r="AV8" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW8" s="15" t="s">
         <v>196</v>
@@ -7705,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="AV9" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW9" s="15" t="s">
         <v>196</v>
@@ -7851,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="AV10" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW10" s="15" t="s">
         <v>196</v>
@@ -7997,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="AV11" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW11" s="15" t="s">
         <v>287</v>
@@ -8047,7 +8091,7 @@
         <v>307</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>307</v>
+        <v>439</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -8071,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="13">
-        <v>100</v>
+        <v>438</v>
       </c>
       <c r="W12" s="13">
         <v>1</v>
@@ -8086,10 +8130,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="13">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="AB12" s="13">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="AC12" s="13">
         <v>0</v>
@@ -8131,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="AR12" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS12" s="10">
         <v>1</v>
@@ -8143,7 +8187,7 @@
         <v>1</v>
       </c>
       <c r="AV12" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW12" s="15" t="s">
         <v>196</v>
@@ -8217,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="13">
-        <v>100</v>
+        <v>427</v>
       </c>
       <c r="W13" s="13">
-        <v>1</v>
+        <v>2.85</v>
       </c>
       <c r="X13" s="11">
         <v>1</v>
@@ -8232,10 +8276,10 @@
         <v>2</v>
       </c>
       <c r="AA13" s="13">
-        <v>1000</v>
+        <v>1135</v>
       </c>
       <c r="AB13" s="13">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="AC13" s="13">
         <v>0</v>
@@ -8277,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="AR13" s="10">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AS13" s="10">
         <v>1</v>
@@ -8289,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="AV13" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW13" s="15" t="s">
         <v>196</v>
@@ -8363,10 +8407,10 @@
         <v>0</v>
       </c>
       <c r="V14" s="13">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="W14" s="13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X14" s="11">
         <v>1</v>
@@ -8378,10 +8422,10 @@
         <v>0</v>
       </c>
       <c r="AA14" s="13">
-        <v>1000</v>
+        <v>2630</v>
       </c>
       <c r="AB14" s="13">
-        <v>100</v>
+        <v>475</v>
       </c>
       <c r="AC14" s="13">
         <v>0</v>
@@ -8423,7 +8467,7 @@
         <v>1</v>
       </c>
       <c r="AR14" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AS14" s="10">
         <v>1</v>
@@ -8435,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="AV14" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW14" s="15" t="s">
         <v>196</v>
@@ -8509,10 +8553,10 @@
         <v>0</v>
       </c>
       <c r="V15" s="13">
-        <v>100</v>
+        <v>295</v>
       </c>
       <c r="W15" s="13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X15" s="11">
         <v>1</v>
@@ -8524,10 +8568,10 @@
         <v>0</v>
       </c>
       <c r="AA15" s="13">
-        <v>1000</v>
+        <v>2035</v>
       </c>
       <c r="AB15" s="13">
-        <v>100</v>
+        <v>578</v>
       </c>
       <c r="AC15" s="13">
         <v>0</v>
@@ -8569,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="AR15" s="10">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AS15" s="10">
         <v>1</v>
@@ -8581,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="AV15" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW15" s="15" t="s">
         <v>196</v>
@@ -8655,10 +8699,10 @@
         <v>0</v>
       </c>
       <c r="V16" s="13">
-        <v>100</v>
+        <v>699</v>
       </c>
       <c r="W16" s="13">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="X16" s="11">
         <v>1</v>
@@ -8670,10 +8714,10 @@
         <v>0</v>
       </c>
       <c r="AA16" s="13">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="AB16" s="13">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AC16" s="13">
         <v>0</v>
@@ -8715,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AR16" s="10">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AS16" s="10">
         <v>1</v>
@@ -8727,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="AV16" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW16" s="15" t="s">
         <v>196</v>
@@ -8801,7 +8845,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="13">
-        <v>100</v>
+        <v>516</v>
       </c>
       <c r="W17" s="13">
         <v>1</v>
@@ -8816,10 +8860,10 @@
         <v>0</v>
       </c>
       <c r="AA17" s="13">
-        <v>1000</v>
+        <v>1226</v>
       </c>
       <c r="AB17" s="13">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c r="AC17" s="13">
         <v>0</v>
@@ -8861,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="AR17" s="10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS17" s="10">
         <v>1</v>
@@ -8873,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="AV17" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW17" s="15" t="s">
         <v>196</v>
@@ -8947,10 +8991,10 @@
         <v>0</v>
       </c>
       <c r="V18" s="13">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="W18" s="13">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X18" s="11">
         <v>1</v>
@@ -8962,10 +9006,10 @@
         <v>0</v>
       </c>
       <c r="AA18" s="13">
-        <v>1000</v>
+        <v>1325</v>
       </c>
       <c r="AB18" s="13">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="AC18" s="13">
         <v>0</v>
@@ -9007,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="AR18" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS18" s="10">
         <v>1</v>
@@ -9019,7 +9063,7 @@
         <v>0</v>
       </c>
       <c r="AV18" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW18" s="15" t="s">
         <v>196</v>
@@ -9093,10 +9137,10 @@
         <v>0</v>
       </c>
       <c r="V19" s="13">
-        <v>100</v>
+        <v>642</v>
       </c>
       <c r="W19" s="13">
-        <v>1</v>
+        <v>2.6850000000000001</v>
       </c>
       <c r="X19" s="11">
         <v>1</v>
@@ -9108,13 +9152,13 @@
         <v>0</v>
       </c>
       <c r="AA19" s="13">
-        <v>1000</v>
+        <v>1141</v>
       </c>
       <c r="AB19" s="13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AC19" s="13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD19" s="13">
         <v>0</v>
@@ -9153,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="AR19" s="10">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AS19" s="10">
         <v>1</v>
@@ -9165,7 +9209,7 @@
         <v>1</v>
       </c>
       <c r="AV19" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW19" s="15" t="s">
         <v>196</v>
@@ -9239,10 +9283,10 @@
         <v>0</v>
       </c>
       <c r="V20" s="13">
-        <v>100</v>
+        <v>569</v>
       </c>
       <c r="W20" s="13">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="X20" s="11">
         <v>1</v>
@@ -9254,13 +9298,13 @@
         <v>0</v>
       </c>
       <c r="AA20" s="13">
-        <v>1000</v>
+        <v>1653</v>
       </c>
       <c r="AB20" s="13">
-        <v>100</v>
+        <v>282</v>
       </c>
       <c r="AC20" s="13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD20" s="13">
         <v>0</v>
@@ -9299,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="AR20" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AS20" s="10">
         <v>1</v>
@@ -9311,7 +9355,7 @@
         <v>0</v>
       </c>
       <c r="AV20" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW20" s="15" t="s">
         <v>196</v>
@@ -9385,10 +9429,10 @@
         <v>0</v>
       </c>
       <c r="V21" s="13">
-        <v>100</v>
+        <v>437</v>
       </c>
       <c r="W21" s="13">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="X21" s="11">
         <v>1</v>
@@ -9400,13 +9444,13 @@
         <v>0</v>
       </c>
       <c r="AA21" s="13">
-        <v>1000</v>
+        <v>935</v>
       </c>
       <c r="AB21" s="13">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="AC21" s="13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD21" s="13">
         <v>0</v>
@@ -9457,7 +9501,7 @@
         <v>1</v>
       </c>
       <c r="AV21" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW21" s="15" t="s">
         <v>196</v>
@@ -9531,10 +9575,10 @@
         <v>0</v>
       </c>
       <c r="V22" s="13">
-        <v>100</v>
+        <v>568</v>
       </c>
       <c r="W22" s="13">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X22" s="11">
         <v>1</v>
@@ -9546,10 +9590,10 @@
         <v>0</v>
       </c>
       <c r="AA22" s="13">
-        <v>1000</v>
+        <v>1858</v>
       </c>
       <c r="AB22" s="13">
-        <v>100</v>
+        <v>245</v>
       </c>
       <c r="AC22" s="13">
         <v>0</v>
@@ -9591,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="AR22" s="10">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AS22" s="10">
         <v>1</v>
@@ -9603,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="AV22" s="14">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="AW22" s="15" t="s">
         <v>196</v>
@@ -9677,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="13">
-        <v>100</v>
+        <v>425</v>
       </c>
       <c r="W23" s="13">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X23" s="11">
         <v>1</v>
@@ -9692,10 +9736,10 @@
         <v>0</v>
       </c>
       <c r="AA23" s="13">
-        <v>1000</v>
+        <v>1270</v>
       </c>
       <c r="AB23" s="13">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="AC23" s="13">
         <v>0</v>
@@ -9737,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="AR23" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS23" s="10">
         <v>1</v>
@@ -9749,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="AV23" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AW23" s="15" t="s">
         <v>196</v>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEE6321-0170-45AA-92A6-790BD8D26E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECE7746-8601-4AA3-B3B4-AB24A49314A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$BC$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$BD$4</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="442">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5959,8 +5959,16 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>_1</t>
-    </r>
+      <t>_skin1</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>溅射半径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SplashRadius</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6505,7 +6513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BG34"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.58203125" style="9" customWidth="1"/>
@@ -6520,22 +6528,22 @@
     <col min="20" max="20" width="12.58203125" style="12" customWidth="1"/>
     <col min="21" max="23" width="12.58203125" style="13" customWidth="1"/>
     <col min="24" max="26" width="12.58203125" style="11" customWidth="1"/>
-    <col min="27" max="31" width="12.58203125" style="13" customWidth="1"/>
-    <col min="32" max="40" width="12.58203125" style="11" customWidth="1"/>
-    <col min="41" max="41" width="12.58203125" style="12" customWidth="1"/>
-    <col min="42" max="43" width="12.58203125" style="11" customWidth="1"/>
-    <col min="44" max="47" width="12.58203125" style="10" customWidth="1"/>
-    <col min="48" max="49" width="12.58203125" style="14" customWidth="1"/>
-    <col min="50" max="50" width="12.58203125" style="10" customWidth="1"/>
-    <col min="51" max="51" width="12.58203125" style="14" customWidth="1"/>
-    <col min="52" max="52" width="12.58203125" style="10" customWidth="1"/>
-    <col min="53" max="53" width="12.58203125" style="13" customWidth="1"/>
-    <col min="54" max="55" width="12.58203125" style="11" customWidth="1"/>
-    <col min="56" max="58" width="12.58203125" style="4" customWidth="1"/>
-    <col min="59" max="16384" width="8.6640625" style="7"/>
+    <col min="27" max="32" width="12.58203125" style="13" customWidth="1"/>
+    <col min="33" max="41" width="12.58203125" style="11" customWidth="1"/>
+    <col min="42" max="42" width="12.58203125" style="12" customWidth="1"/>
+    <col min="43" max="44" width="12.58203125" style="11" customWidth="1"/>
+    <col min="45" max="48" width="12.58203125" style="10" customWidth="1"/>
+    <col min="49" max="50" width="12.58203125" style="14" customWidth="1"/>
+    <col min="51" max="51" width="12.58203125" style="10" customWidth="1"/>
+    <col min="52" max="52" width="12.58203125" style="14" customWidth="1"/>
+    <col min="53" max="53" width="12.58203125" style="10" customWidth="1"/>
+    <col min="54" max="54" width="12.58203125" style="13" customWidth="1"/>
+    <col min="55" max="56" width="12.58203125" style="11" customWidth="1"/>
+    <col min="57" max="59" width="12.58203125" style="4" customWidth="1"/>
+    <col min="60" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -6598,9 +6606,10 @@
       <c r="BD1" s="6"/>
       <c r="BE1" s="6"/>
       <c r="BF1" s="6"/>
-      <c r="BG1" s="20"/>
+      <c r="BG1" s="6"/>
+      <c r="BH1" s="20"/>
     </row>
-    <row r="2" spans="1:59" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>4</v>
       </c>
@@ -6652,10 +6661,10 @@
       <c r="AO2" s="6"/>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
-      <c r="AR2" s="29" t="s">
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="AS2" s="29"/>
       <c r="AT2" s="29"/>
       <c r="AU2" s="29"/>
       <c r="AV2" s="29"/>
@@ -6663,19 +6672,20 @@
       <c r="AX2" s="29"/>
       <c r="AY2" s="29"/>
       <c r="AZ2" s="29"/>
-      <c r="BA2" s="6" t="s">
+      <c r="BA2" s="29"/>
+      <c r="BB2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="6"/>
       <c r="BC2" s="6"/>
-      <c r="BD2" s="1" t="s">
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
-      <c r="BG2" s="20"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="20"/>
     </row>
-    <row r="3" spans="1:59" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:60" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
         <v>73</v>
       </c>
@@ -6754,105 +6764,108 @@
       <c r="Z3" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="AA3" s="32" t="s">
+      <c r="AA3" s="33" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB3" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AC3" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AC3" s="32" t="s">
+      <c r="AD3" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="AD3" s="32" t="s">
+      <c r="AE3" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="AE3" s="32" t="s">
+      <c r="AF3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="AF3" s="32" t="s">
+      <c r="AG3" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="AG3" s="32" t="s">
+      <c r="AH3" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="AH3" s="33" t="s">
+      <c r="AI3" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AI3" s="33" t="s">
+      <c r="AJ3" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AK3" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AL3" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AM3" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AN3" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="AO3" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="AO3" s="32" t="s">
+      <c r="AP3" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="AP3" s="32" t="s">
+      <c r="AQ3" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="AQ3" s="33" t="s">
+      <c r="AR3" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="AR3" s="30" t="s">
+      <c r="AS3" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="30" t="s">
+      <c r="AT3" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AT3" s="34" t="s">
+      <c r="AU3" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="AU3" s="30" t="s">
+      <c r="AV3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AV3" s="30" t="s">
+      <c r="AW3" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="AW3" s="31" t="s">
+      <c r="AX3" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="AX3" s="30" t="s">
+      <c r="AY3" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="AY3" s="30" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="BA3" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="BA3" s="32" t="s">
+      <c r="BB3" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="BB3" s="32" t="s">
+      <c r="BC3" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="BC3" s="32" t="s">
+      <c r="BD3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="BD3" s="2" t="s">
+      <c r="BE3" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="BE3" s="2" t="s">
+      <c r="BF3" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BG3" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="BG3" s="21"/>
+      <c r="BH3" s="21"/>
     </row>
-    <row r="4" spans="1:59" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:60" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
         <v>42</v>
       </c>
@@ -6932,104 +6945,107 @@
         <v>297</v>
       </c>
       <c r="AA4" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="AB4" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AC4" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AD4" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AE4" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AF4" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AG4" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AH4" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AI4" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AK4" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AL4" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AM4" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AN4" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AO4" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AP4" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AR4" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="AR4" s="30" t="s">
+      <c r="AS4" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AT4" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AU4" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AV4" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AW4" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AX4" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BA4" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="BA4" s="32" t="s">
+      <c r="BB4" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="BB4" s="32" t="s">
+      <c r="BC4" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="BC4" s="32" t="s">
+      <c r="BD4" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="BD4" s="3" t="s">
+      <c r="BE4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="BE4" s="3" t="s">
+      <c r="BF4" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="BF4" s="3" t="s">
+      <c r="BG4" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="BG4" s="21"/>
+      <c r="BH4" s="21"/>
     </row>
-    <row r="5" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>44</v>
       </c>
@@ -7099,25 +7115,25 @@
         <v>0</v>
       </c>
       <c r="AA5" s="26">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="26">
         <v>1743</v>
       </c>
-      <c r="AB5" s="26">
+      <c r="AC5" s="26">
         <v>122</v>
       </c>
-      <c r="AC5" s="26">
+      <c r="AD5" s="26">
         <v>20</v>
       </c>
-      <c r="AD5" s="26">
-        <v>0</v>
-      </c>
       <c r="AE5" s="26">
         <v>0</v>
       </c>
-      <c r="AF5" s="24">
-        <v>1</v>
+      <c r="AF5" s="26">
+        <v>0</v>
       </c>
       <c r="AG5" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" s="24">
         <v>0</v>
@@ -7140,56 +7156,59 @@
       <c r="AN5" s="24">
         <v>0</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AO5" s="24">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="AP5" s="24" t="s">
+      <c r="AQ5" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="AQ5" s="24">
-        <v>1</v>
-      </c>
-      <c r="AR5" s="23">
+      <c r="AR5" s="24">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="23">
         <v>19</v>
       </c>
-      <c r="AS5" s="23">
-        <v>1</v>
-      </c>
       <c r="AT5" s="23">
         <v>1</v>
       </c>
       <c r="AU5" s="23">
         <v>1</v>
       </c>
-      <c r="AV5" s="27">
+      <c r="AV5" s="23">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="27">
         <v>70</v>
       </c>
-      <c r="AW5" s="28" t="s">
+      <c r="AX5" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="AX5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AY5" s="27">
+      <c r="AY5" s="23">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="27">
         <v>50</v>
       </c>
-      <c r="AZ5" s="23">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="24"/>
+      <c r="BA5" s="23">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="26"/>
       <c r="BC5" s="24"/>
-      <c r="BD5" s="4" t="s">
+      <c r="BD5" s="24"/>
+      <c r="BE5" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="BE5" s="5" t="s">
+      <c r="BF5" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="BF5" s="4" t="s">
+      <c r="BG5" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>46</v>
       </c>
@@ -7254,25 +7273,25 @@
         <v>0</v>
       </c>
       <c r="AA6" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="13">
         <v>1678</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AC6" s="13">
         <v>135</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AD6" s="13">
         <v>20</v>
       </c>
-      <c r="AD6" s="13">
-        <v>0</v>
-      </c>
       <c r="AE6" s="13">
         <v>0</v>
       </c>
-      <c r="AF6" s="11">
-        <v>1</v>
+      <c r="AF6" s="13">
+        <v>0</v>
       </c>
       <c r="AG6" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH6" s="11">
         <v>0</v>
@@ -7295,47 +7314,50 @@
       <c r="AN6" s="11">
         <v>0</v>
       </c>
-      <c r="AQ6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="10">
+      <c r="AO6" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="10">
         <v>23</v>
       </c>
-      <c r="AS6" s="10">
-        <v>1</v>
-      </c>
       <c r="AT6" s="10">
         <v>1</v>
       </c>
       <c r="AU6" s="10">
         <v>1</v>
       </c>
-      <c r="AV6" s="14">
+      <c r="AV6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="14">
         <v>66</v>
       </c>
-      <c r="AW6" s="15" t="s">
+      <c r="AX6" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY6" s="14">
+      <c r="AY6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="14">
         <v>50</v>
       </c>
-      <c r="AZ6" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD6" s="4" t="s">
+      <c r="BA6" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE6" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="BE6" s="5" t="s">
+      <c r="BF6" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="BF6" s="4" t="s">
+      <c r="BG6" s="4" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>50</v>
       </c>
@@ -7400,25 +7422,25 @@
         <v>0</v>
       </c>
       <c r="AA7" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="13">
         <v>1060</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>126</v>
       </c>
-      <c r="AC7" s="13">
-        <v>0</v>
-      </c>
       <c r="AD7" s="13">
         <v>0</v>
       </c>
       <c r="AE7" s="13">
         <v>0</v>
       </c>
-      <c r="AF7" s="11">
-        <v>1</v>
+      <c r="AF7" s="13">
+        <v>0</v>
       </c>
       <c r="AG7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" s="11">
         <v>0</v>
@@ -7441,47 +7463,50 @@
       <c r="AN7" s="11">
         <v>0</v>
       </c>
-      <c r="AQ7" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR7" s="10">
+      <c r="AO7" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="10">
         <v>9</v>
       </c>
-      <c r="AS7" s="10">
-        <v>1</v>
-      </c>
       <c r="AT7" s="10">
         <v>1</v>
       </c>
       <c r="AU7" s="10">
         <v>1</v>
       </c>
-      <c r="AV7" s="14">
+      <c r="AV7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="14">
         <v>66</v>
       </c>
-      <c r="AW7" s="15" t="s">
+      <c r="AX7" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY7" s="14">
+      <c r="AY7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="14">
         <v>50</v>
       </c>
-      <c r="AZ7" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD7" s="4" t="s">
+      <c r="BA7" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE7" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="BE7" s="5" t="s">
+      <c r="BF7" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="BF7" s="4" t="s">
+      <c r="BG7" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>50</v>
       </c>
@@ -7546,25 +7571,25 @@
         <v>0</v>
       </c>
       <c r="AA8" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="13">
         <v>1100</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>90</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>15</v>
       </c>
-      <c r="AD8" s="13">
-        <v>0</v>
-      </c>
       <c r="AE8" s="13">
         <v>0</v>
       </c>
-      <c r="AF8" s="11">
-        <v>1</v>
+      <c r="AF8" s="13">
+        <v>0</v>
       </c>
       <c r="AG8" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="11">
         <v>0</v>
@@ -7587,47 +7612,50 @@
       <c r="AN8" s="11">
         <v>0</v>
       </c>
-      <c r="AQ8" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR8" s="10">
+      <c r="AO8" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="10">
         <v>16</v>
       </c>
-      <c r="AS8" s="10">
-        <v>1</v>
-      </c>
       <c r="AT8" s="10">
         <v>1</v>
       </c>
       <c r="AU8" s="10">
         <v>1</v>
       </c>
-      <c r="AV8" s="14">
+      <c r="AV8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="14">
         <v>60</v>
       </c>
-      <c r="AW8" s="15" t="s">
+      <c r="AX8" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY8" s="14">
+      <c r="AY8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="14">
         <v>50</v>
       </c>
-      <c r="AZ8" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD8" s="4" t="s">
+      <c r="BA8" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE8" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="BE8" s="5" t="s">
+      <c r="BF8" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="BF8" s="4" t="s">
+      <c r="BG8" s="4" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>50</v>
       </c>
@@ -7692,26 +7720,26 @@
         <v>0</v>
       </c>
       <c r="AA9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="13">
         <v>1833</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>496</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10</v>
       </c>
-      <c r="AD9" s="13">
-        <v>0</v>
-      </c>
       <c r="AE9" s="13">
         <v>0</v>
       </c>
-      <c r="AF9" s="11">
+      <c r="AF9" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="11">
         <v>3</v>
       </c>
-      <c r="AG9" s="11">
-        <v>0</v>
-      </c>
       <c r="AH9" s="11">
         <v>0</v>
       </c>
@@ -7733,47 +7761,50 @@
       <c r="AN9" s="11">
         <v>0</v>
       </c>
-      <c r="AQ9" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR9" s="10">
+      <c r="AO9" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="10">
         <v>15</v>
       </c>
-      <c r="AS9" s="10">
-        <v>1</v>
-      </c>
       <c r="AT9" s="10">
         <v>1</v>
       </c>
       <c r="AU9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="14">
         <v>66</v>
       </c>
-      <c r="AW9" s="15" t="s">
+      <c r="AX9" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY9" s="14">
+      <c r="AY9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="14">
         <v>50</v>
       </c>
-      <c r="AZ9" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD9" s="4" t="s">
+      <c r="BA9" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE9" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="BE9" s="5" t="s">
+      <c r="BF9" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="BF9" s="4" t="s">
+      <c r="BG9" s="4" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>50</v>
       </c>
@@ -7838,25 +7869,25 @@
         <v>0</v>
       </c>
       <c r="AA10" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="13">
         <v>2745</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>155</v>
       </c>
-      <c r="AC10" s="13">
-        <v>0</v>
-      </c>
       <c r="AD10" s="13">
         <v>0</v>
       </c>
       <c r="AE10" s="13">
         <v>0</v>
       </c>
-      <c r="AF10" s="11">
-        <v>1</v>
+      <c r="AF10" s="13">
+        <v>0</v>
       </c>
       <c r="AG10" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" s="11">
         <v>0</v>
@@ -7879,47 +7910,50 @@
       <c r="AN10" s="11">
         <v>0</v>
       </c>
-      <c r="AQ10" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="10">
+      <c r="AO10" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="10">
         <v>13</v>
       </c>
-      <c r="AS10" s="10">
-        <v>1</v>
-      </c>
       <c r="AT10" s="10">
         <v>1</v>
       </c>
       <c r="AU10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="14">
         <v>60</v>
       </c>
-      <c r="AW10" s="15" t="s">
+      <c r="AX10" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY10" s="14">
+      <c r="AY10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="14">
         <v>50</v>
       </c>
-      <c r="AZ10" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD10" s="4" t="s">
+      <c r="BA10" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE10" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="BE10" s="5" t="s">
+      <c r="BF10" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="BF10" s="4" t="s">
+      <c r="BG10" s="4" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>278</v>
       </c>
@@ -7984,25 +8018,25 @@
         <v>2</v>
       </c>
       <c r="AA11" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="13">
         <v>1220</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>110</v>
       </c>
-      <c r="AC11" s="13">
-        <v>0</v>
-      </c>
       <c r="AD11" s="13">
         <v>0</v>
       </c>
       <c r="AE11" s="13">
         <v>0</v>
       </c>
-      <c r="AF11" s="11">
-        <v>1</v>
+      <c r="AF11" s="13">
+        <v>0</v>
       </c>
       <c r="AG11" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" s="11">
         <v>0</v>
@@ -8025,47 +8059,50 @@
       <c r="AN11" s="11">
         <v>0</v>
       </c>
-      <c r="AQ11" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR11" s="10">
+      <c r="AO11" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="10">
         <v>15</v>
       </c>
-      <c r="AS11" s="10">
-        <v>1</v>
-      </c>
       <c r="AT11" s="10">
         <v>1</v>
       </c>
       <c r="AU11" s="10">
         <v>1</v>
       </c>
-      <c r="AV11" s="14">
+      <c r="AV11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="14">
         <v>60</v>
       </c>
-      <c r="AW11" s="15" t="s">
+      <c r="AX11" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="AX11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY11" s="14">
+      <c r="AY11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="14">
         <v>50</v>
       </c>
-      <c r="AZ11" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="4" t="s">
+      <c r="BA11" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE11" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="BE11" s="5" t="s">
+      <c r="BF11" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="BF11" s="4" t="s">
+      <c r="BG11" s="4" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:59" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:60" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>304</v>
       </c>
@@ -8130,25 +8167,25 @@
         <v>0</v>
       </c>
       <c r="AA12" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="13">
         <v>1080</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>134</v>
       </c>
-      <c r="AC12" s="13">
-        <v>0</v>
-      </c>
       <c r="AD12" s="13">
         <v>0</v>
       </c>
       <c r="AE12" s="13">
         <v>0</v>
       </c>
-      <c r="AF12" s="11">
-        <v>1</v>
+      <c r="AF12" s="13">
+        <v>0</v>
       </c>
       <c r="AG12" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="11">
         <v>0</v>
@@ -8171,47 +8208,50 @@
       <c r="AN12" s="11">
         <v>0</v>
       </c>
-      <c r="AQ12" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR12" s="10">
+      <c r="AO12" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="10">
         <v>9</v>
       </c>
-      <c r="AS12" s="10">
-        <v>1</v>
-      </c>
       <c r="AT12" s="10">
         <v>1</v>
       </c>
       <c r="AU12" s="10">
         <v>1</v>
       </c>
-      <c r="AV12" s="14">
+      <c r="AV12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="14">
         <v>60</v>
       </c>
-      <c r="AW12" s="15" t="s">
+      <c r="AX12" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY12" s="14">
+      <c r="AY12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="14">
         <v>50</v>
       </c>
-      <c r="AZ12" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD12" s="4" t="s">
+      <c r="BA12" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE12" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="BE12" s="5" t="s">
+      <c r="BF12" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="BF12" s="4" t="s">
+      <c r="BG12" s="4" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>304</v>
       </c>
@@ -8276,25 +8316,25 @@
         <v>2</v>
       </c>
       <c r="AA13" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="13">
         <v>1135</v>
       </c>
-      <c r="AB13" s="13">
+      <c r="AC13" s="13">
         <v>109</v>
       </c>
-      <c r="AC13" s="13">
-        <v>0</v>
-      </c>
       <c r="AD13" s="13">
         <v>0</v>
       </c>
       <c r="AE13" s="13">
         <v>0</v>
       </c>
-      <c r="AF13" s="11">
-        <v>1</v>
+      <c r="AF13" s="13">
+        <v>0</v>
       </c>
       <c r="AG13" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13" s="11">
         <v>0</v>
@@ -8317,47 +8357,50 @@
       <c r="AN13" s="11">
         <v>0</v>
       </c>
-      <c r="AQ13" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR13" s="10">
+      <c r="AO13" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="10">
         <v>15</v>
       </c>
-      <c r="AS13" s="10">
-        <v>1</v>
-      </c>
       <c r="AT13" s="10">
         <v>1</v>
       </c>
       <c r="AU13" s="10">
         <v>1</v>
       </c>
-      <c r="AV13" s="14">
+      <c r="AV13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="14">
         <v>66</v>
       </c>
-      <c r="AW13" s="15" t="s">
+      <c r="AX13" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY13" s="14">
+      <c r="AY13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="14">
         <v>50</v>
       </c>
-      <c r="AZ13" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="4" t="s">
+      <c r="BA13" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE13" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="BE13" s="5" t="s">
+      <c r="BF13" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="BF13" s="4" t="s">
+      <c r="BG13" s="4" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
         <v>304</v>
       </c>
@@ -8422,26 +8465,26 @@
         <v>0</v>
       </c>
       <c r="AA14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="13">
         <v>2630</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>475</v>
       </c>
-      <c r="AC14" s="13">
-        <v>0</v>
-      </c>
       <c r="AD14" s="13">
         <v>0</v>
       </c>
       <c r="AE14" s="13">
         <v>0</v>
       </c>
-      <c r="AF14" s="11">
+      <c r="AF14" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="11">
         <v>3</v>
       </c>
-      <c r="AG14" s="11">
-        <v>0</v>
-      </c>
       <c r="AH14" s="11">
         <v>0</v>
       </c>
@@ -8463,47 +8506,50 @@
       <c r="AN14" s="11">
         <v>0</v>
       </c>
-      <c r="AQ14" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR14" s="10">
+      <c r="AO14" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="10">
         <v>16</v>
       </c>
-      <c r="AS14" s="10">
-        <v>1</v>
-      </c>
       <c r="AT14" s="10">
         <v>1</v>
       </c>
       <c r="AU14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="14">
         <v>60</v>
       </c>
-      <c r="AW14" s="15" t="s">
+      <c r="AX14" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX14" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY14" s="14">
+      <c r="AY14" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="14">
         <v>50</v>
       </c>
-      <c r="AZ14" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD14" s="4" t="s">
+      <c r="BA14" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE14" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="BE14" s="5" t="s">
+      <c r="BF14" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="BF14" s="4" t="s">
+      <c r="BG14" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>304</v>
       </c>
@@ -8568,26 +8614,26 @@
         <v>0</v>
       </c>
       <c r="AA15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="13">
         <v>2035</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>578</v>
       </c>
-      <c r="AC15" s="13">
-        <v>0</v>
-      </c>
       <c r="AD15" s="13">
         <v>0</v>
       </c>
       <c r="AE15" s="13">
         <v>0</v>
       </c>
-      <c r="AF15" s="11">
+      <c r="AF15" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="11">
         <v>3</v>
       </c>
-      <c r="AG15" s="11">
-        <v>0</v>
-      </c>
       <c r="AH15" s="11">
         <v>0</v>
       </c>
@@ -8609,47 +8655,50 @@
       <c r="AN15" s="11">
         <v>0</v>
       </c>
-      <c r="AQ15" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR15" s="10">
+      <c r="AO15" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="10">
         <v>16</v>
       </c>
-      <c r="AS15" s="10">
-        <v>1</v>
-      </c>
       <c r="AT15" s="10">
         <v>1</v>
       </c>
       <c r="AU15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="14">
         <v>60</v>
       </c>
-      <c r="AW15" s="15" t="s">
+      <c r="AX15" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX15" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY15" s="14">
+      <c r="AY15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="14">
         <v>50</v>
       </c>
-      <c r="AZ15" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD15" s="4" t="s">
+      <c r="BA15" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE15" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="BE15" s="5" t="s">
+      <c r="BF15" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="BF15" s="4" t="s">
+      <c r="BG15" s="4" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
         <v>304</v>
       </c>
@@ -8714,25 +8763,25 @@
         <v>0</v>
       </c>
       <c r="AA16" s="13">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="13">
         <v>1150</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>85</v>
       </c>
-      <c r="AC16" s="13">
-        <v>0</v>
-      </c>
       <c r="AD16" s="13">
         <v>0</v>
       </c>
       <c r="AE16" s="13">
         <v>0</v>
       </c>
-      <c r="AF16" s="11">
-        <v>1</v>
+      <c r="AF16" s="13">
+        <v>0</v>
       </c>
       <c r="AG16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" s="11">
         <v>0</v>
@@ -8755,47 +8804,50 @@
       <c r="AN16" s="11">
         <v>0</v>
       </c>
-      <c r="AQ16" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR16" s="10">
+      <c r="AO16" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="10">
         <v>21</v>
       </c>
-      <c r="AS16" s="10">
-        <v>1</v>
-      </c>
       <c r="AT16" s="10">
         <v>1</v>
       </c>
       <c r="AU16" s="10">
         <v>1</v>
       </c>
-      <c r="AV16" s="14">
+      <c r="AV16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW16" s="14">
         <v>60</v>
       </c>
-      <c r="AW16" s="15" t="s">
+      <c r="AX16" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY16" s="14">
+      <c r="AY16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="14">
         <v>50</v>
       </c>
-      <c r="AZ16" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD16" s="4" t="s">
+      <c r="BA16" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE16" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="BE16" s="5" t="s">
+      <c r="BF16" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="BF16" s="4" t="s">
+      <c r="BG16" s="4" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="17" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>304</v>
       </c>
@@ -8860,25 +8912,25 @@
         <v>0</v>
       </c>
       <c r="AA17" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="13">
         <v>1226</v>
       </c>
-      <c r="AB17" s="13">
+      <c r="AC17" s="13">
         <v>279</v>
       </c>
-      <c r="AC17" s="13">
-        <v>0</v>
-      </c>
       <c r="AD17" s="13">
         <v>0</v>
       </c>
       <c r="AE17" s="13">
         <v>0</v>
       </c>
-      <c r="AF17" s="11">
-        <v>1</v>
+      <c r="AF17" s="13">
+        <v>0</v>
       </c>
       <c r="AG17" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17" s="11">
         <v>0</v>
@@ -8901,47 +8953,50 @@
       <c r="AN17" s="11">
         <v>0</v>
       </c>
-      <c r="AQ17" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR17" s="10">
+      <c r="AO17" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS17" s="10">
         <v>8</v>
       </c>
-      <c r="AS17" s="10">
-        <v>1</v>
-      </c>
       <c r="AT17" s="10">
         <v>1</v>
       </c>
       <c r="AU17" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV17" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="14">
         <v>60</v>
       </c>
-      <c r="AW17" s="15" t="s">
+      <c r="AX17" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX17" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY17" s="14">
+      <c r="AY17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="14">
         <v>50</v>
       </c>
-      <c r="AZ17" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="4" t="s">
+      <c r="BA17" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE17" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="BE17" s="5" t="s">
+      <c r="BF17" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="BF17" s="4" t="s">
+      <c r="BG17" s="4" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="18" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>304</v>
       </c>
@@ -9006,26 +9061,26 @@
         <v>0</v>
       </c>
       <c r="AA18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="13">
         <v>1325</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>330</v>
       </c>
-      <c r="AC18" s="13">
-        <v>0</v>
-      </c>
       <c r="AD18" s="13">
         <v>0</v>
       </c>
       <c r="AE18" s="13">
         <v>0</v>
       </c>
-      <c r="AF18" s="11">
+      <c r="AF18" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="11">
         <v>2</v>
       </c>
-      <c r="AG18" s="11">
-        <v>0</v>
-      </c>
       <c r="AH18" s="11">
         <v>0</v>
       </c>
@@ -9047,47 +9102,50 @@
       <c r="AN18" s="11">
         <v>0</v>
       </c>
-      <c r="AQ18" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR18" s="10">
+      <c r="AO18" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="10">
         <v>9</v>
       </c>
-      <c r="AS18" s="10">
-        <v>1</v>
-      </c>
       <c r="AT18" s="10">
         <v>1</v>
       </c>
       <c r="AU18" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="14">
         <v>60</v>
       </c>
-      <c r="AW18" s="15" t="s">
+      <c r="AX18" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX18" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY18" s="14">
+      <c r="AY18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="14">
         <v>50</v>
       </c>
-      <c r="AZ18" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="4" t="s">
+      <c r="BA18" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE18" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="BE18" s="5" t="s">
+      <c r="BF18" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="BF18" s="4" t="s">
+      <c r="BG18" s="4" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="19" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
         <v>304</v>
       </c>
@@ -9152,25 +9210,25 @@
         <v>0</v>
       </c>
       <c r="AA19" s="13">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="AB19" s="13">
         <v>1141</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AC19" s="13">
         <v>95</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AD19" s="13">
         <v>15</v>
       </c>
-      <c r="AD19" s="13">
-        <v>0</v>
-      </c>
       <c r="AE19" s="13">
         <v>0</v>
       </c>
-      <c r="AF19" s="11">
-        <v>1</v>
+      <c r="AF19" s="13">
+        <v>0</v>
       </c>
       <c r="AG19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH19" s="11">
         <v>0</v>
@@ -9193,47 +9251,50 @@
       <c r="AN19" s="11">
         <v>0</v>
       </c>
-      <c r="AQ19" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR19" s="10">
+      <c r="AO19" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="10">
         <v>28</v>
       </c>
-      <c r="AS19" s="10">
-        <v>1</v>
-      </c>
       <c r="AT19" s="10">
         <v>1</v>
       </c>
       <c r="AU19" s="10">
         <v>1</v>
       </c>
-      <c r="AV19" s="14">
+      <c r="AV19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="14">
         <v>66</v>
       </c>
-      <c r="AW19" s="15" t="s">
+      <c r="AX19" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX19" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY19" s="14">
+      <c r="AY19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="14">
         <v>50</v>
       </c>
-      <c r="AZ19" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD19" s="4" t="s">
+      <c r="BA19" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE19" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="BE19" s="5" t="s">
+      <c r="BF19" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="BF19" s="4" t="s">
+      <c r="BG19" s="4" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="20" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>304</v>
       </c>
@@ -9298,26 +9359,26 @@
         <v>0</v>
       </c>
       <c r="AA20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="13">
         <v>1653</v>
       </c>
-      <c r="AB20" s="13">
+      <c r="AC20" s="13">
         <v>282</v>
       </c>
-      <c r="AC20" s="13">
+      <c r="AD20" s="13">
         <v>10</v>
       </c>
-      <c r="AD20" s="13">
-        <v>0</v>
-      </c>
       <c r="AE20" s="13">
         <v>0</v>
       </c>
-      <c r="AF20" s="11">
+      <c r="AF20" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="11">
         <v>2</v>
       </c>
-      <c r="AG20" s="11">
-        <v>0</v>
-      </c>
       <c r="AH20" s="11">
         <v>0</v>
       </c>
@@ -9339,47 +9400,50 @@
       <c r="AN20" s="11">
         <v>0</v>
       </c>
-      <c r="AQ20" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="10">
+      <c r="AO20" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="10">
         <v>14</v>
       </c>
-      <c r="AS20" s="10">
-        <v>1</v>
-      </c>
       <c r="AT20" s="10">
         <v>1</v>
       </c>
       <c r="AU20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="14">
         <v>66</v>
       </c>
-      <c r="AW20" s="15" t="s">
+      <c r="AX20" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX20" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY20" s="14">
+      <c r="AY20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="14">
         <v>50</v>
       </c>
-      <c r="AZ20" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD20" s="4" t="s">
+      <c r="BA20" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE20" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="BE20" s="5" t="s">
+      <c r="BF20" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="BF20" s="4" t="s">
+      <c r="BG20" s="4" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
         <v>304</v>
       </c>
@@ -9444,25 +9508,25 @@
         <v>0</v>
       </c>
       <c r="AA21" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="13">
         <v>935</v>
       </c>
-      <c r="AB21" s="13">
+      <c r="AC21" s="13">
         <v>83</v>
       </c>
-      <c r="AC21" s="13">
+      <c r="AD21" s="13">
         <v>15</v>
       </c>
-      <c r="AD21" s="13">
-        <v>0</v>
-      </c>
       <c r="AE21" s="13">
         <v>0</v>
       </c>
-      <c r="AF21" s="11">
-        <v>1</v>
+      <c r="AF21" s="13">
+        <v>0</v>
       </c>
       <c r="AG21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH21" s="11">
         <v>0</v>
@@ -9485,47 +9549,50 @@
       <c r="AN21" s="11">
         <v>0</v>
       </c>
-      <c r="AQ21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR21" s="10">
+      <c r="AO21" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="10">
         <v>10</v>
       </c>
-      <c r="AS21" s="10">
-        <v>1</v>
-      </c>
       <c r="AT21" s="10">
         <v>1</v>
       </c>
       <c r="AU21" s="10">
         <v>1</v>
       </c>
-      <c r="AV21" s="14">
+      <c r="AV21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AW21" s="14">
         <v>60</v>
       </c>
-      <c r="AW21" s="15" t="s">
+      <c r="AX21" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX21" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY21" s="14">
+      <c r="AY21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="14">
         <v>50</v>
       </c>
-      <c r="AZ21" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="4" t="s">
+      <c r="BA21" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE21" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="BE21" s="5" t="s">
+      <c r="BF21" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="BF21" s="4" t="s">
+      <c r="BG21" s="4" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="22" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>304</v>
       </c>
@@ -9590,26 +9657,26 @@
         <v>0</v>
       </c>
       <c r="AA22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="13">
         <v>1858</v>
       </c>
-      <c r="AB22" s="13">
+      <c r="AC22" s="13">
         <v>245</v>
       </c>
-      <c r="AC22" s="13">
-        <v>0</v>
-      </c>
       <c r="AD22" s="13">
         <v>0</v>
       </c>
       <c r="AE22" s="13">
         <v>0</v>
       </c>
-      <c r="AF22" s="11">
+      <c r="AF22" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="11">
         <v>2</v>
       </c>
-      <c r="AG22" s="11">
-        <v>0</v>
-      </c>
       <c r="AH22" s="11">
         <v>0</v>
       </c>
@@ -9631,47 +9698,50 @@
       <c r="AN22" s="11">
         <v>0</v>
       </c>
-      <c r="AQ22" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR22" s="10">
+      <c r="AO22" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="10">
         <v>17</v>
       </c>
-      <c r="AS22" s="10">
-        <v>1</v>
-      </c>
       <c r="AT22" s="10">
         <v>1</v>
       </c>
       <c r="AU22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV22" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="14">
         <v>66</v>
       </c>
-      <c r="AW22" s="15" t="s">
+      <c r="AX22" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX22" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY22" s="14">
+      <c r="AY22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="14">
         <v>50</v>
       </c>
-      <c r="AZ22" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD22" s="4" t="s">
+      <c r="BA22" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE22" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="BE22" s="5" t="s">
+      <c r="BF22" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="BF22" s="4" t="s">
+      <c r="BG22" s="4" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="23" spans="1:58" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
         <v>304</v>
       </c>
@@ -9736,26 +9806,26 @@
         <v>0</v>
       </c>
       <c r="AA23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="13">
         <v>1270</v>
       </c>
-      <c r="AB23" s="13">
+      <c r="AC23" s="13">
         <v>240</v>
       </c>
-      <c r="AC23" s="13">
-        <v>0</v>
-      </c>
       <c r="AD23" s="13">
         <v>0</v>
       </c>
       <c r="AE23" s="13">
         <v>0</v>
       </c>
-      <c r="AF23" s="11">
+      <c r="AF23" s="13">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="11">
         <v>2</v>
       </c>
-      <c r="AG23" s="11">
-        <v>0</v>
-      </c>
       <c r="AH23" s="11">
         <v>0</v>
       </c>
@@ -9777,47 +9847,50 @@
       <c r="AN23" s="11">
         <v>0</v>
       </c>
-      <c r="AQ23" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR23" s="10">
+      <c r="AO23" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="11">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="10">
         <v>9</v>
       </c>
-      <c r="AS23" s="10">
-        <v>1</v>
-      </c>
       <c r="AT23" s="10">
         <v>1</v>
       </c>
       <c r="AU23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV23" s="14">
+        <v>1</v>
+      </c>
+      <c r="AV23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="14">
         <v>60</v>
       </c>
-      <c r="AW23" s="15" t="s">
+      <c r="AX23" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="AX23" s="10">
-        <v>1</v>
-      </c>
-      <c r="AY23" s="14">
+      <c r="AY23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AZ23" s="14">
         <v>50</v>
       </c>
-      <c r="AZ23" s="10">
-        <v>1</v>
-      </c>
-      <c r="BD23" s="4" t="s">
+      <c r="BA23" s="10">
+        <v>1</v>
+      </c>
+      <c r="BE23" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="BE23" s="5" t="s">
+      <c r="BF23" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="BF23" s="4" t="s">
+      <c r="BG23" s="4" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="24" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>61</v>
       </c>
@@ -9880,25 +9953,25 @@
         <v>0</v>
       </c>
       <c r="AA24" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="13">
         <v>5500</v>
       </c>
-      <c r="AB24" s="13">
+      <c r="AC24" s="13">
         <v>265</v>
       </c>
-      <c r="AC24" s="13">
-        <v>0</v>
-      </c>
       <c r="AD24" s="13">
         <v>0</v>
       </c>
       <c r="AE24" s="13">
         <v>0</v>
       </c>
-      <c r="AF24" s="11">
-        <v>1</v>
+      <c r="AF24" s="13">
+        <v>0</v>
       </c>
       <c r="AG24" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" s="11">
         <v>0</v>
@@ -9921,29 +9994,32 @@
       <c r="AN24" s="11">
         <v>0</v>
       </c>
-      <c r="AQ24" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA24" s="13">
+      <c r="AO24" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="13">
         <v>0.5</v>
       </c>
-      <c r="BB24" s="11">
-        <v>1</v>
-      </c>
       <c r="BC24" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD24" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE24" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE24" s="5" t="s">
+      <c r="BF24" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="BF24" s="4" t="s">
+      <c r="BG24" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>61</v>
       </c>
@@ -10006,25 +10082,25 @@
         <v>0</v>
       </c>
       <c r="AA25" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="13">
         <v>4590</v>
       </c>
-      <c r="AB25" s="13">
+      <c r="AC25" s="13">
         <v>185</v>
       </c>
-      <c r="AC25" s="13">
-        <v>0</v>
-      </c>
       <c r="AD25" s="13">
         <v>0</v>
       </c>
       <c r="AE25" s="13">
         <v>0</v>
       </c>
-      <c r="AF25" s="11">
-        <v>1</v>
+      <c r="AF25" s="13">
+        <v>0</v>
       </c>
       <c r="AG25" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" s="11">
         <v>0</v>
@@ -10047,29 +10123,32 @@
       <c r="AN25" s="11">
         <v>0</v>
       </c>
-      <c r="AQ25" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA25" s="13">
+      <c r="AO25" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="13">
         <v>0.45</v>
       </c>
-      <c r="BB25" s="11">
-        <v>1</v>
-      </c>
       <c r="BC25" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD25" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE25" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE25" s="5" t="s">
+      <c r="BF25" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="BF25" s="4" t="s">
+      <c r="BG25" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>61</v>
       </c>
@@ -10129,25 +10208,25 @@
         <v>0</v>
       </c>
       <c r="AA26" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="13">
         <v>12000</v>
       </c>
-      <c r="AB26" s="13">
+      <c r="AC26" s="13">
         <v>325</v>
       </c>
-      <c r="AC26" s="13">
+      <c r="AD26" s="13">
         <v>10</v>
       </c>
-      <c r="AD26" s="13">
-        <v>0</v>
-      </c>
       <c r="AE26" s="13">
         <v>0</v>
       </c>
-      <c r="AF26" s="11">
-        <v>1</v>
+      <c r="AF26" s="13">
+        <v>0</v>
       </c>
       <c r="AG26" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" s="11">
         <v>0</v>
@@ -10170,29 +10249,32 @@
       <c r="AN26" s="11">
         <v>0</v>
       </c>
-      <c r="AQ26" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA26" s="13">
+      <c r="AO26" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB26" s="13">
         <v>0.4</v>
       </c>
-      <c r="BB26" s="11">
-        <v>1</v>
-      </c>
       <c r="BC26" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD26" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE26" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE26" s="5" t="s">
+      <c r="BF26" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="BF26" s="4" t="s">
+      <c r="BG26" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="27" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" s="9" t="s">
         <v>61</v>
       </c>
@@ -10255,25 +10337,25 @@
         <v>0</v>
       </c>
       <c r="AA27" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="13">
         <v>12500</v>
       </c>
-      <c r="AB27" s="13">
+      <c r="AC27" s="13">
         <v>375</v>
       </c>
-      <c r="AC27" s="13">
+      <c r="AD27" s="13">
         <v>50</v>
       </c>
-      <c r="AD27" s="13">
-        <v>0</v>
-      </c>
       <c r="AE27" s="13">
         <v>0</v>
       </c>
-      <c r="AF27" s="11">
-        <v>1</v>
+      <c r="AF27" s="13">
+        <v>0</v>
       </c>
       <c r="AG27" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="11">
         <v>0</v>
@@ -10296,26 +10378,29 @@
       <c r="AN27" s="11">
         <v>0</v>
       </c>
-      <c r="AQ27" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA27" s="13">
+      <c r="AO27" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="13">
         <v>0.25</v>
       </c>
-      <c r="BB27" s="11">
-        <v>1</v>
-      </c>
       <c r="BC27" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD27" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE27" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE27" s="5" t="s">
+      <c r="BF27" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="28" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>61</v>
       </c>
@@ -10375,25 +10460,25 @@
         <v>0</v>
       </c>
       <c r="AA28" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="13">
         <v>1235</v>
       </c>
-      <c r="AB28" s="13">
+      <c r="AC28" s="13">
         <v>65</v>
       </c>
-      <c r="AC28" s="13">
+      <c r="AD28" s="13">
         <v>5</v>
       </c>
-      <c r="AD28" s="13">
-        <v>0</v>
-      </c>
       <c r="AE28" s="13">
         <v>0</v>
       </c>
-      <c r="AF28" s="11">
-        <v>1</v>
+      <c r="AF28" s="13">
+        <v>0</v>
       </c>
       <c r="AG28" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" s="11">
         <v>0</v>
@@ -10416,29 +10501,32 @@
       <c r="AN28" s="11">
         <v>0</v>
       </c>
-      <c r="AQ28" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA28" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB28" s="11">
-        <v>1</v>
+      <c r="AO28" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB28" s="13">
+        <v>0</v>
       </c>
       <c r="BC28" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD28" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD28" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE28" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE28" s="5" t="s">
+      <c r="BF28" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="BF28" s="4" t="s">
+      <c r="BG28" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="29" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>61</v>
       </c>
@@ -10498,25 +10586,25 @@
         <v>0</v>
       </c>
       <c r="AA29" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="13">
         <v>3600</v>
       </c>
-      <c r="AB29" s="13">
+      <c r="AC29" s="13">
         <v>150</v>
       </c>
-      <c r="AC29" s="13">
+      <c r="AD29" s="13">
         <v>5</v>
       </c>
-      <c r="AD29" s="13">
-        <v>0</v>
-      </c>
       <c r="AE29" s="13">
         <v>0</v>
       </c>
-      <c r="AF29" s="11">
-        <v>1</v>
+      <c r="AF29" s="13">
+        <v>0</v>
       </c>
       <c r="AG29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" s="11">
         <v>0</v>
@@ -10539,35 +10627,38 @@
       <c r="AN29" s="11">
         <v>0</v>
       </c>
-      <c r="AO29" s="12" t="s">
+      <c r="AO29" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="AP29" s="11" t="s">
+      <c r="AQ29" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="AQ29" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA29" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB29" s="11">
-        <v>1</v>
+      <c r="AR29" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="13">
+        <v>0</v>
       </c>
       <c r="BC29" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD29" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD29" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE29" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE29" s="5" t="s">
+      <c r="BF29" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="BF29" s="4" t="s">
+      <c r="BG29" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="30" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>61</v>
       </c>
@@ -10627,25 +10718,25 @@
         <v>0</v>
       </c>
       <c r="AA30" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="13">
         <v>6900</v>
       </c>
-      <c r="AB30" s="13">
+      <c r="AC30" s="13">
         <v>235</v>
       </c>
-      <c r="AC30" s="13">
+      <c r="AD30" s="13">
         <v>5</v>
       </c>
-      <c r="AD30" s="13">
-        <v>0</v>
-      </c>
       <c r="AE30" s="13">
         <v>0</v>
       </c>
-      <c r="AF30" s="11">
-        <v>1</v>
+      <c r="AF30" s="13">
+        <v>0</v>
       </c>
       <c r="AG30" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" s="11">
         <v>0</v>
@@ -10668,35 +10759,38 @@
       <c r="AN30" s="11">
         <v>0</v>
       </c>
-      <c r="AO30" s="12" t="s">
+      <c r="AO30" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="AP30" s="11" t="s">
+      <c r="AQ30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="AQ30" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA30" s="13">
-        <v>0</v>
-      </c>
-      <c r="BB30" s="11">
-        <v>1</v>
+      <c r="AR30" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB30" s="13">
+        <v>0</v>
       </c>
       <c r="BC30" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD30" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD30" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE30" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE30" s="5" t="s">
+      <c r="BF30" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="BF30" s="4" t="s">
+      <c r="BG30" s="4" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="31" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>61</v>
       </c>
@@ -10753,25 +10847,25 @@
         <v>0</v>
       </c>
       <c r="AA31" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="13">
         <v>5000</v>
       </c>
-      <c r="AB31" s="13">
+      <c r="AC31" s="13">
         <v>500</v>
       </c>
-      <c r="AC31" s="13">
+      <c r="AD31" s="13">
         <v>50</v>
       </c>
-      <c r="AD31" s="13">
-        <v>0</v>
-      </c>
       <c r="AE31" s="13">
         <v>0</v>
       </c>
-      <c r="AF31" s="11">
-        <v>1</v>
+      <c r="AF31" s="13">
+        <v>0</v>
       </c>
       <c r="AG31" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" s="11">
         <v>0</v>
@@ -10794,26 +10888,29 @@
       <c r="AN31" s="11">
         <v>0</v>
       </c>
-      <c r="AQ31" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA31" s="13">
+      <c r="AO31" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB31" s="13">
         <v>0.45</v>
       </c>
-      <c r="BB31" s="11">
+      <c r="BC31" s="11">
         <v>2</v>
       </c>
-      <c r="BC31" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="4" t="s">
+      <c r="BD31" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE31" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE31" s="5" t="s">
+      <c r="BF31" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="32" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>61</v>
       </c>
@@ -10873,11 +10970,11 @@
         <v>0</v>
       </c>
       <c r="AA32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="13">
         <v>100</v>
       </c>
-      <c r="AB32" s="13">
-        <v>0</v>
-      </c>
       <c r="AC32" s="13">
         <v>0</v>
       </c>
@@ -10887,7 +10984,7 @@
       <c r="AE32" s="13">
         <v>0</v>
       </c>
-      <c r="AF32" s="11">
+      <c r="AF32" s="13">
         <v>0</v>
       </c>
       <c r="AG32" s="11">
@@ -10914,17 +11011,17 @@
       <c r="AN32" s="11">
         <v>0</v>
       </c>
-      <c r="AO32" s="12" t="s">
+      <c r="AO32" s="11">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="AP32" s="11" t="s">
+      <c r="AQ32" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="AQ32" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR32" s="10">
-        <v>0</v>
+      <c r="AR32" s="11">
+        <v>1</v>
       </c>
       <c r="AS32" s="10">
         <v>0</v>
@@ -10935,29 +11032,32 @@
       <c r="AU32" s="10">
         <v>0</v>
       </c>
-      <c r="AV32" s="14">
-        <v>0</v>
-      </c>
-      <c r="AW32" s="15" t="s">
+      <c r="AV32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="14">
+        <v>0</v>
+      </c>
+      <c r="AX32" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="AX32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AY32" s="14">
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="10">
-        <v>0</v>
-      </c>
-      <c r="BD32" s="4" t="s">
+      <c r="AY32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="14">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="10">
+        <v>0</v>
+      </c>
+      <c r="BE32" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE32" s="5" t="s">
+      <c r="BF32" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="33" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>61</v>
       </c>
@@ -11020,28 +11120,28 @@
         <v>0</v>
       </c>
       <c r="AA33" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="13">
         <v>32500</v>
       </c>
-      <c r="AB33" s="13">
+      <c r="AC33" s="13">
         <v>700</v>
       </c>
-      <c r="AC33" s="13">
+      <c r="AD33" s="13">
         <v>50</v>
       </c>
-      <c r="AD33" s="13">
-        <v>0</v>
-      </c>
       <c r="AE33" s="13">
         <v>0</v>
       </c>
-      <c r="AF33" s="11">
-        <v>1</v>
+      <c r="AF33" s="13">
+        <v>0</v>
       </c>
       <c r="AG33" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="11">
         <v>1</v>
@@ -11061,26 +11161,29 @@
       <c r="AN33" s="11">
         <v>1</v>
       </c>
-      <c r="AQ33" s="11">
-        <v>0</v>
-      </c>
-      <c r="BA33" s="13">
+      <c r="AO33" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="11">
+        <v>0</v>
+      </c>
+      <c r="BB33" s="13">
         <v>0.3</v>
       </c>
-      <c r="BB33" s="11">
+      <c r="BC33" s="11">
         <v>7</v>
       </c>
-      <c r="BC33" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD33" s="4" t="s">
+      <c r="BD33" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE33" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE33" s="5" t="s">
+      <c r="BF33" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="34" spans="1:58" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>171</v>
       </c>
@@ -11125,11 +11228,11 @@
         <v>0</v>
       </c>
       <c r="AA34" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="13">
         <v>100</v>
       </c>
-      <c r="AB34" s="13">
-        <v>0</v>
-      </c>
       <c r="AC34" s="13">
         <v>0</v>
       </c>
@@ -11139,7 +11242,7 @@
       <c r="AE34" s="13">
         <v>0</v>
       </c>
-      <c r="AF34" s="11">
+      <c r="AF34" s="13">
         <v>0</v>
       </c>
       <c r="AG34" s="11">
@@ -11166,21 +11269,24 @@
       <c r="AN34" s="11">
         <v>0</v>
       </c>
-      <c r="AQ34" s="11">
-        <v>0</v>
-      </c>
-      <c r="BD34" s="4" t="s">
+      <c r="AO34" s="11">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="11">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="BE34" s="5" t="s">
+      <c r="BF34" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="BF34" s="4" t="s">
+      <c r="BG34" s="4" t="s">
         <v>267</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BC4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:BD4" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FECE7746-8601-4AA3-B3B4-AB24A49314A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD12A0D-3D21-42E3-8FC9-2308F8D9CA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1720,19 +1720,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>中坚术士</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>斑点</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5969,6 +5956,10 @@
   </si>
   <si>
     <t>SplashRadius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中坚术师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6131,7 +6122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -6231,6 +6222,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6679,7 +6673,7 @@
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
       <c r="BE2" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
@@ -6714,7 +6708,7 @@
         <v>78</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K3" s="32" t="s">
         <v>79</v>
@@ -6762,10 +6756,10 @@
         <v>24</v>
       </c>
       <c r="Z3" s="33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA3" s="33" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AB3" s="32" t="s">
         <v>25</v>
@@ -6789,25 +6783,25 @@
         <v>28</v>
       </c>
       <c r="AI3" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ3" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AK3" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AL3" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AM3" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AN3" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="AO3" s="33" t="s">
         <v>185</v>
-      </c>
-      <c r="AO3" s="33" t="s">
-        <v>186</v>
       </c>
       <c r="AP3" s="32" t="s">
         <v>82</v>
@@ -6816,7 +6810,7 @@
         <v>83</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AS3" s="30" t="s">
         <v>29</v>
@@ -6825,7 +6819,7 @@
         <v>30</v>
       </c>
       <c r="AU3" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AV3" s="30" t="s">
         <v>31</v>
@@ -6834,7 +6828,7 @@
         <v>32</v>
       </c>
       <c r="AX3" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AY3" s="30" t="s">
         <v>33</v>
@@ -6855,13 +6849,13 @@
         <v>37</v>
       </c>
       <c r="BE3" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BG3" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="BH3" s="21"/>
     </row>
@@ -6879,169 +6873,169 @@
         <v>1</v>
       </c>
       <c r="E4" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="30" t="s">
         <v>198</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="G4" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="J4" s="30" t="s">
+      <c r="L4" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="T4" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="U4" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="V4" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="W4" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="X4" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="Y4" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z4" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA4" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="AB4" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC4" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD4" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="AE4" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="AF4" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="AG4" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="AH4" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="AI4" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="K4" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>203</v>
-      </c>
-      <c r="O4" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q4" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>208</v>
-      </c>
-      <c r="T4" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="U4" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="V4" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="W4" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="Y4" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z4" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="AA4" s="32" t="s">
-        <v>441</v>
-      </c>
-      <c r="AB4" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC4" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD4" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="AE4" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="AF4" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="AG4" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="AH4" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AK4" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AL4" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AM4" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AN4" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AO4" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AP4" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AR4" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="AS4" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="AR4" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AT4" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AU4" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AV4" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AW4" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AX4" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BA4" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BB4" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="BB4" s="32" t="s">
+      <c r="BC4" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="BC4" s="32" t="s">
+      <c r="BD4" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="BD4" s="32" t="s">
-        <v>243</v>
-      </c>
       <c r="BE4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="BF4" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="BF4" s="3" t="s">
+      <c r="BG4" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="BG4" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="BH4" s="21"/>
     </row>
@@ -7094,7 +7088,7 @@
       <c r="R5" s="23"/>
       <c r="S5" s="23"/>
       <c r="T5" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U5" s="26">
         <v>0</v>
@@ -7160,10 +7154,10 @@
         <v>0</v>
       </c>
       <c r="AP5" s="25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AQ5" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AR5" s="24">
         <v>1</v>
@@ -7184,7 +7178,7 @@
         <v>70</v>
       </c>
       <c r="AX5" s="28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY5" s="23">
         <v>1</v>
@@ -7199,13 +7193,13 @@
       <c r="BC5" s="24"/>
       <c r="BD5" s="24"/>
       <c r="BE5" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BG5" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.3">
@@ -7336,7 +7330,7 @@
         <v>66</v>
       </c>
       <c r="AX6" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY6" s="10">
         <v>1</v>
@@ -7348,13 +7342,13 @@
         <v>1</v>
       </c>
       <c r="BE6" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="BF6" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="BF6" s="5" t="s">
-        <v>275</v>
-      </c>
       <c r="BG6" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.3">
@@ -7392,7 +7386,7 @@
         <v>3</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>106</v>
@@ -7485,7 +7479,7 @@
         <v>66</v>
       </c>
       <c r="AX7" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY7" s="10">
         <v>1</v>
@@ -7497,13 +7491,13 @@
         <v>1</v>
       </c>
       <c r="BE7" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="BF7" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="BF7" s="5" t="s">
-        <v>269</v>
-      </c>
       <c r="BG7" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.3">
@@ -7541,16 +7535,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="12" t="s">
-        <v>113</v>
+      <c r="N8" s="37" t="s">
+        <v>441</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="U8" s="13">
         <v>0</v>
@@ -7634,7 +7628,7 @@
         <v>60</v>
       </c>
       <c r="AX8" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY8" s="10">
         <v>1</v>
@@ -7646,13 +7640,13 @@
         <v>1</v>
       </c>
       <c r="BE8" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BF8" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BG8" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.3">
@@ -7663,25 +7657,25 @@
         <v>5</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>58</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>56</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>118</v>
       </c>
       <c r="J9" s="10">
         <v>1</v>
@@ -7690,13 +7684,13 @@
         <v>3</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="N9" s="12" t="s">
         <v>119</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>120</v>
       </c>
       <c r="T9" s="12" t="s">
         <v>57</v>
@@ -7783,7 +7777,7 @@
         <v>66</v>
       </c>
       <c r="AX9" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY9" s="10">
         <v>1</v>
@@ -7795,13 +7789,13 @@
         <v>1</v>
       </c>
       <c r="BE9" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BF9" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="BG9" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.3">
@@ -7812,25 +7806,25 @@
         <v>6</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>59</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>63</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="J10" s="10">
         <v>1</v>
@@ -7839,13 +7833,13 @@
         <v>3</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M10" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="N10" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>124</v>
       </c>
       <c r="T10" s="12" t="s">
         <v>60</v>
@@ -7932,7 +7926,7 @@
         <v>60</v>
       </c>
       <c r="AX10" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY10" s="10">
         <v>1</v>
@@ -7944,42 +7938,42 @@
         <v>1</v>
       </c>
       <c r="BE10" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="BF10" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="BF10" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="BG10" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B11" s="10">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="F11" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>282</v>
-      </c>
       <c r="G11" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>291</v>
       </c>
       <c r="J11" s="10">
         <v>1</v>
@@ -7988,16 +7982,16 @@
         <v>3</v>
       </c>
       <c r="L11" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="M11" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="N11" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="N11" s="36" t="s">
+      <c r="T11" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="T11" s="12" t="s">
-        <v>286</v>
       </c>
       <c r="U11" s="13">
         <v>0</v>
@@ -8081,7 +8075,7 @@
         <v>60</v>
       </c>
       <c r="AX11" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AY11" s="10">
         <v>1</v>
@@ -8093,42 +8087,42 @@
         <v>1</v>
       </c>
       <c r="BE11" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="BF11" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="BF11" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="BG11" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:60" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B12" s="10">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>309</v>
-      </c>
       <c r="E12" s="35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>307</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -8137,16 +8131,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M12" s="36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N12" s="36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U12" s="13">
         <v>0</v>
@@ -8230,7 +8224,7 @@
         <v>60</v>
       </c>
       <c r="AX12" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY12" s="10">
         <v>1</v>
@@ -8242,42 +8236,42 @@
         <v>1</v>
       </c>
       <c r="BE12" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="BF12" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="BF12" s="5" t="s">
+      <c r="BG12" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="BG12" s="4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B13" s="10">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J13" s="10">
         <v>1</v>
@@ -8286,16 +8280,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M13" s="36" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U13" s="13">
         <v>0</v>
@@ -8379,7 +8373,7 @@
         <v>66</v>
       </c>
       <c r="AX13" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY13" s="10">
         <v>1</v>
@@ -8391,42 +8385,42 @@
         <v>1</v>
       </c>
       <c r="BE13" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="BF13" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="BF13" s="5" t="s">
+      <c r="BG13" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="BG13" s="4" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="14" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B14" s="10">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J14" s="10">
         <v>1</v>
@@ -8435,16 +8429,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M14" s="36" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U14" s="13">
         <v>0</v>
@@ -8528,7 +8522,7 @@
         <v>60</v>
       </c>
       <c r="AX14" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY14" s="10">
         <v>1</v>
@@ -8540,42 +8534,42 @@
         <v>1</v>
       </c>
       <c r="BE14" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="BF14" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="BF14" s="5" t="s">
+      <c r="BG14" s="4" t="s">
         <v>383</v>
-      </c>
-      <c r="BG14" s="4" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B15" s="10">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J15" s="10">
         <v>1</v>
@@ -8584,16 +8578,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U15" s="13">
         <v>0</v>
@@ -8677,7 +8671,7 @@
         <v>60</v>
       </c>
       <c r="AX15" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY15" s="10">
         <v>1</v>
@@ -8689,42 +8683,42 @@
         <v>1</v>
       </c>
       <c r="BE15" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="BF15" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="BF15" s="5" t="s">
+      <c r="BG15" s="4" t="s">
         <v>386</v>
-      </c>
-      <c r="BG15" s="4" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B16" s="10">
         <v>12</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J16" s="10">
         <v>1</v>
@@ -8733,16 +8727,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M16" s="36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N16" s="36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T16" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U16" s="13">
         <v>0</v>
@@ -8826,7 +8820,7 @@
         <v>60</v>
       </c>
       <c r="AX16" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY16" s="10">
         <v>1</v>
@@ -8838,42 +8832,42 @@
         <v>1</v>
       </c>
       <c r="BE16" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="BF16" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="BF16" s="5" t="s">
+      <c r="BG16" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="BG16" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B17" s="10">
         <v>13</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
@@ -8882,16 +8876,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M17" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N17" s="36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U17" s="13">
         <v>0</v>
@@ -8975,7 +8969,7 @@
         <v>60</v>
       </c>
       <c r="AX17" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY17" s="10">
         <v>1</v>
@@ -8987,42 +8981,42 @@
         <v>1</v>
       </c>
       <c r="BE17" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="BF17" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="BF17" s="5" t="s">
+      <c r="BG17" s="4" t="s">
         <v>392</v>
-      </c>
-      <c r="BG17" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B18" s="10">
         <v>14</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -9031,16 +9025,16 @@
         <v>3</v>
       </c>
       <c r="L18" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M18" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N18" s="36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U18" s="13">
         <v>0</v>
@@ -9124,7 +9118,7 @@
         <v>60</v>
       </c>
       <c r="AX18" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY18" s="10">
         <v>1</v>
@@ -9136,42 +9130,42 @@
         <v>1</v>
       </c>
       <c r="BE18" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="BF18" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="BF18" s="5" t="s">
+      <c r="BG18" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="BG18" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B19" s="10">
         <v>15</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
@@ -9180,16 +9174,16 @@
         <v>3</v>
       </c>
       <c r="L19" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M19" s="36" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N19" s="36" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U19" s="13">
         <v>0</v>
@@ -9273,7 +9267,7 @@
         <v>66</v>
       </c>
       <c r="AX19" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY19" s="10">
         <v>1</v>
@@ -9285,42 +9279,42 @@
         <v>1</v>
       </c>
       <c r="BE19" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="BF19" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="BF19" s="5" t="s">
+      <c r="BG19" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="BG19" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B20" s="10">
         <v>16</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -9329,16 +9323,16 @@
         <v>3</v>
       </c>
       <c r="L20" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M20" s="36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N20" s="36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="U20" s="13">
         <v>0</v>
@@ -9422,7 +9416,7 @@
         <v>66</v>
       </c>
       <c r="AX20" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY20" s="10">
         <v>1</v>
@@ -9434,42 +9428,42 @@
         <v>1</v>
       </c>
       <c r="BE20" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="BF20" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="BF20" s="5" t="s">
+      <c r="BG20" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="BG20" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B21" s="10">
         <v>17</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J21" s="10">
         <v>1</v>
@@ -9478,16 +9472,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M21" s="36" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N21" s="36" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U21" s="13">
         <v>0</v>
@@ -9571,7 +9565,7 @@
         <v>60</v>
       </c>
       <c r="AX21" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY21" s="10">
         <v>1</v>
@@ -9583,42 +9577,42 @@
         <v>1</v>
       </c>
       <c r="BE21" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="BF21" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="BF21" s="5" t="s">
+      <c r="BG21" s="4" t="s">
         <v>404</v>
-      </c>
-      <c r="BG21" s="4" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B22" s="10">
         <v>18</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -9627,16 +9621,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U22" s="13">
         <v>0</v>
@@ -9648,7 +9642,7 @@
         <v>1.2</v>
       </c>
       <c r="X22" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22" s="11">
         <v>0</v>
@@ -9720,7 +9714,7 @@
         <v>66</v>
       </c>
       <c r="AX22" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY22" s="10">
         <v>1</v>
@@ -9732,42 +9726,42 @@
         <v>1</v>
       </c>
       <c r="BE22" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="BF22" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="BF22" s="5" t="s">
+      <c r="BG22" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="BG22" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="23" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B23" s="10">
         <v>19</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J23" s="10">
         <v>1</v>
@@ -9776,16 +9770,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M23" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N23" s="36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U23" s="13">
         <v>0</v>
@@ -9869,7 +9863,7 @@
         <v>60</v>
       </c>
       <c r="AX23" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY23" s="10">
         <v>1</v>
@@ -9881,13 +9875,13 @@
         <v>1</v>
       </c>
       <c r="BE23" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="BF23" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="BF23" s="5" t="s">
+      <c r="BG23" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="BG23" s="4" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:59" x14ac:dyDescent="0.3">
@@ -9898,19 +9892,19 @@
         <v>1</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>62</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J24" s="10">
         <v>2</v>
@@ -9920,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q24" s="10">
         <v>1</v>
@@ -10010,13 +10004,13 @@
         <v>0</v>
       </c>
       <c r="BE24" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF24" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG24" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:59" x14ac:dyDescent="0.3">
@@ -10027,19 +10021,19 @@
         <v>2</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>66</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J25" s="10">
         <v>2</v>
@@ -10049,7 +10043,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q25" s="10">
         <v>1</v>
@@ -10139,13 +10133,13 @@
         <v>0</v>
       </c>
       <c r="BE25" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="BG25" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:59" x14ac:dyDescent="0.3">
@@ -10156,7 +10150,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>67</v>
@@ -10165,10 +10159,10 @@
         <v>68</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J26" s="10">
         <v>2</v>
@@ -10265,13 +10259,13 @@
         <v>0</v>
       </c>
       <c r="BE26" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF26" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BG26" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:59" x14ac:dyDescent="0.3">
@@ -10282,19 +10276,19 @@
         <v>4</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J27" s="10">
         <v>2</v>
@@ -10304,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q27" s="10">
         <v>1</v>
@@ -10394,10 +10388,10 @@
         <v>0</v>
       </c>
       <c r="BE27" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF27" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:59" x14ac:dyDescent="0.3">
@@ -10408,19 +10402,19 @@
         <v>6</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J28" s="10">
         <v>2</v>
@@ -10517,13 +10511,13 @@
         <v>0</v>
       </c>
       <c r="BE28" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF28" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BG28" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:59" x14ac:dyDescent="0.3">
@@ -10534,19 +10528,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J29" s="10">
         <v>2</v>
@@ -10631,10 +10625,10 @@
         <v>0</v>
       </c>
       <c r="AP29" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AQ29" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AR29" s="11">
         <v>0</v>
@@ -10649,13 +10643,13 @@
         <v>0</v>
       </c>
       <c r="BE29" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF29" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BG29" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:59" x14ac:dyDescent="0.3">
@@ -10666,19 +10660,19 @@
         <v>8</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>72</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J30" s="10">
         <v>2</v>
@@ -10763,10 +10757,10 @@
         <v>0</v>
       </c>
       <c r="AP30" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ30" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AR30" s="11">
         <v>0</v>
@@ -10781,13 +10775,13 @@
         <v>0</v>
       </c>
       <c r="BE30" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF30" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BG30" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:59" x14ac:dyDescent="0.3">
@@ -10798,16 +10792,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="E31" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>142</v>
-      </c>
       <c r="F31" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J31" s="10">
         <v>2</v>
@@ -10904,10 +10898,10 @@
         <v>0</v>
       </c>
       <c r="BE31" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF31" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:59" x14ac:dyDescent="0.3">
@@ -10918,16 +10912,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J32" s="10">
         <v>2</v>
@@ -10937,7 +10931,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q32" s="10">
         <v>0</v>
@@ -11015,10 +11009,10 @@
         <v>0</v>
       </c>
       <c r="AP32" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AQ32" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AR32" s="11">
         <v>1</v>
@@ -11039,7 +11033,7 @@
         <v>0</v>
       </c>
       <c r="AX32" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY32" s="10">
         <v>0</v>
@@ -11051,10 +11045,10 @@
         <v>0</v>
       </c>
       <c r="BE32" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF32" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:59" x14ac:dyDescent="0.3">
@@ -11065,19 +11059,19 @@
         <v>11</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>148</v>
-      </c>
       <c r="F33" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J33" s="10">
         <v>2</v>
@@ -11177,37 +11171,37 @@
         <v>0</v>
       </c>
       <c r="BE33" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF33" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="10">
+        <v>1</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="10">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="F34" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="J34" s="10">
         <v>2</v>
       </c>
       <c r="L34" s="16"/>
       <c r="T34" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U34" s="13">
         <v>1.5</v>
@@ -11276,13 +11270,13 @@
         <v>0</v>
       </c>
       <c r="BE34" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="BF34" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BG34" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AD12A0D-3D21-42E3-8FC9-2308F8D9CA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4F9535-0E9F-4D51-B86E-1179F629A337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3450" yWindow="340" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2084,57 +2084,6 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>骷髅是</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>“</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>我的世界</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>”</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>中擅长使用弓箭远程攻击的怪物。作为亡灵生物，它惧怕阳光，但它头顶的帽子似乎可以帮他解决这个问题。骷髅看似一具傀儡，但它们似乎拥有交流能力，可以将对手的信息告诉队友。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>苦力怕</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5960,6 +5909,59 @@
   </si>
   <si>
     <t>中坚术师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骷髅是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>我的世界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中擅长使用弓箭远程攻击的怪物。作为亡灵生物，它惧怕阳光，但它头顶的帽子似乎可以帮他解决这个问题。骷髅之间似乎拥有交流能力，可以将对手的信息告诉对方。</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6122,7 +6124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -6225,6 +6227,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6673,7 +6678,7 @@
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
       <c r="BE2" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
@@ -6708,7 +6713,7 @@
         <v>78</v>
       </c>
       <c r="J3" s="31" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K3" s="32" t="s">
         <v>79</v>
@@ -6756,10 +6761,10 @@
         <v>24</v>
       </c>
       <c r="Z3" s="33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AA3" s="33" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AB3" s="32" t="s">
         <v>25</v>
@@ -6783,25 +6788,25 @@
         <v>28</v>
       </c>
       <c r="AI3" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="AJ3" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AK3" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AL3" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AM3" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AN3" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="AO3" s="33" t="s">
         <v>184</v>
-      </c>
-      <c r="AO3" s="33" t="s">
-        <v>185</v>
       </c>
       <c r="AP3" s="32" t="s">
         <v>82</v>
@@ -6810,7 +6815,7 @@
         <v>83</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AS3" s="30" t="s">
         <v>29</v>
@@ -6819,7 +6824,7 @@
         <v>30</v>
       </c>
       <c r="AU3" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AV3" s="30" t="s">
         <v>31</v>
@@ -6828,7 +6833,7 @@
         <v>32</v>
       </c>
       <c r="AX3" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AY3" s="30" t="s">
         <v>33</v>
@@ -6849,13 +6854,13 @@
         <v>37</v>
       </c>
       <c r="BE3" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="BF3" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="BF3" s="2" t="s">
+      <c r="BG3" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="BH3" s="21"/>
     </row>
@@ -6873,169 +6878,169 @@
         <v>1</v>
       </c>
       <c r="E4" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F4" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="G4" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="K4" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="30" t="s">
-        <v>245</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>247</v>
-      </c>
-      <c r="J4" s="30" t="s">
+      <c r="L4" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="M4" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="R4" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="T4" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="U4" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="V4" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="W4" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="X4" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y4" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z4" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA4" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="AB4" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC4" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD4" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="AE4" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF4" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="AG4" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="AH4" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="AI4" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="K4" s="32" t="s">
-        <v>199</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="O4" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q4" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="R4" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="S4" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="T4" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="U4" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="V4" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="W4" s="32" t="s">
-        <v>211</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="Y4" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z4" s="32" t="s">
-        <v>296</v>
-      </c>
-      <c r="AA4" s="32" t="s">
-        <v>440</v>
-      </c>
-      <c r="AB4" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC4" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD4" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="AE4" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="AF4" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="AG4" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="AH4" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AK4" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AL4" s="32" t="s">
         <v>224</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AM4" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AN4" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AO4" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AP4" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AR4" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="AS4" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="AR4" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AT4" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AU4" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AV4" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AW4" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AX4" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AY4" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AZ4" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="BA4" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BB4" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="BB4" s="32" t="s">
+      <c r="BC4" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="BC4" s="32" t="s">
+      <c r="BD4" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="BD4" s="32" t="s">
-        <v>242</v>
-      </c>
       <c r="BE4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="BF4" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="BF4" s="3" t="s">
+      <c r="BG4" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="BG4" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="BH4" s="21"/>
     </row>
@@ -7088,7 +7093,7 @@
       <c r="R5" s="23"/>
       <c r="S5" s="23"/>
       <c r="T5" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="U5" s="26">
         <v>0</v>
@@ -7154,10 +7159,10 @@
         <v>0</v>
       </c>
       <c r="AP5" s="25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AQ5" s="24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR5" s="24">
         <v>1</v>
@@ -7178,7 +7183,7 @@
         <v>70</v>
       </c>
       <c r="AX5" s="28" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY5" s="23">
         <v>1</v>
@@ -7193,13 +7198,13 @@
       <c r="BC5" s="24"/>
       <c r="BD5" s="24"/>
       <c r="BE5" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BG5" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.3">
@@ -7330,7 +7335,7 @@
         <v>66</v>
       </c>
       <c r="AX6" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY6" s="10">
         <v>1</v>
@@ -7342,13 +7347,13 @@
         <v>1</v>
       </c>
       <c r="BE6" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="BF6" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="BF6" s="5" t="s">
-        <v>274</v>
-      </c>
       <c r="BG6" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.3">
@@ -7386,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>106</v>
@@ -7479,7 +7484,7 @@
         <v>66</v>
       </c>
       <c r="AX7" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY7" s="10">
         <v>1</v>
@@ -7491,13 +7496,13 @@
         <v>1</v>
       </c>
       <c r="BE7" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="BF7" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="BF7" s="5" t="s">
-        <v>268</v>
-      </c>
       <c r="BG7" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.3">
@@ -7535,16 +7540,16 @@
         <v>3</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>99</v>
       </c>
       <c r="N8" s="37" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U8" s="13">
         <v>0</v>
@@ -7628,7 +7633,7 @@
         <v>60</v>
       </c>
       <c r="AX8" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY8" s="10">
         <v>1</v>
@@ -7640,13 +7645,13 @@
         <v>1</v>
       </c>
       <c r="BE8" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BF8" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BG8" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.3">
@@ -7684,7 +7689,7 @@
         <v>3</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M9" s="12" t="s">
         <v>118</v>
@@ -7777,7 +7782,7 @@
         <v>66</v>
       </c>
       <c r="AX9" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY9" s="10">
         <v>1</v>
@@ -7789,13 +7794,13 @@
         <v>1</v>
       </c>
       <c r="BE9" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BF9" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BG9" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.3">
@@ -7818,13 +7823,13 @@
         <v>63</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>150</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>151</v>
       </c>
       <c r="J10" s="10">
         <v>1</v>
@@ -7833,7 +7838,7 @@
         <v>3</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>122</v>
@@ -7926,7 +7931,7 @@
         <v>60</v>
       </c>
       <c r="AX10" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY10" s="10">
         <v>1</v>
@@ -7938,42 +7943,42 @@
         <v>1</v>
       </c>
       <c r="BE10" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="BF10" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="BF10" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="BG10" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B11" s="10">
         <v>7</v>
       </c>
       <c r="C11" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="F11" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="G11" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="I11" s="9" t="s">
         <v>289</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="J11" s="10">
         <v>1</v>
@@ -7982,16 +7987,16 @@
         <v>3</v>
       </c>
       <c r="L11" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="M11" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="N11" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="N11" s="36" t="s">
+      <c r="T11" s="12" t="s">
         <v>284</v>
-      </c>
-      <c r="T11" s="12" t="s">
-        <v>285</v>
       </c>
       <c r="U11" s="13">
         <v>0</v>
@@ -8075,7 +8080,7 @@
         <v>60</v>
       </c>
       <c r="AX11" s="15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AY11" s="10">
         <v>1</v>
@@ -8087,42 +8092,42 @@
         <v>1</v>
       </c>
       <c r="BE11" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="BF11" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="BF11" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="BG11" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:60" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B12" s="10">
         <v>8</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>308</v>
-      </c>
       <c r="E12" s="35" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>306</v>
-      </c>
       <c r="I12" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -8131,16 +8136,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M12" s="36" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N12" s="36" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U12" s="13">
         <v>0</v>
@@ -8224,7 +8229,7 @@
         <v>60</v>
       </c>
       <c r="AX12" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY12" s="10">
         <v>1</v>
@@ -8236,42 +8241,42 @@
         <v>1</v>
       </c>
       <c r="BE12" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="BF12" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="BF12" s="5" t="s">
+      <c r="BG12" s="4" t="s">
         <v>376</v>
-      </c>
-      <c r="BG12" s="4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B13" s="10">
         <v>9</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J13" s="10">
         <v>1</v>
@@ -8280,16 +8285,16 @@
         <v>3</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M13" s="36" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N13" s="36" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U13" s="13">
         <v>0</v>
@@ -8373,7 +8378,7 @@
         <v>66</v>
       </c>
       <c r="AX13" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY13" s="10">
         <v>1</v>
@@ -8385,42 +8390,42 @@
         <v>1</v>
       </c>
       <c r="BE13" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="BF13" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="BF13" s="5" t="s">
+      <c r="BG13" s="4" t="s">
         <v>379</v>
-      </c>
-      <c r="BG13" s="4" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B14" s="10">
         <v>10</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J14" s="10">
         <v>1</v>
@@ -8429,16 +8434,16 @@
         <v>3</v>
       </c>
       <c r="L14" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M14" s="36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N14" s="36" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U14" s="13">
         <v>0</v>
@@ -8522,7 +8527,7 @@
         <v>60</v>
       </c>
       <c r="AX14" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY14" s="10">
         <v>1</v>
@@ -8534,42 +8539,42 @@
         <v>1</v>
       </c>
       <c r="BE14" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="BF14" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="BF14" s="5" t="s">
+      <c r="BG14" s="4" t="s">
         <v>382</v>
-      </c>
-      <c r="BG14" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B15" s="10">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="J15" s="10">
         <v>1</v>
@@ -8578,16 +8583,16 @@
         <v>3</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M15" s="36" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N15" s="36" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U15" s="13">
         <v>0</v>
@@ -8671,7 +8676,7 @@
         <v>60</v>
       </c>
       <c r="AX15" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY15" s="10">
         <v>1</v>
@@ -8683,42 +8688,42 @@
         <v>1</v>
       </c>
       <c r="BE15" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="BF15" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="BF15" s="5" t="s">
+      <c r="BG15" s="4" t="s">
         <v>385</v>
-      </c>
-      <c r="BG15" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B16" s="10">
         <v>12</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J16" s="10">
         <v>1</v>
@@ -8727,16 +8732,16 @@
         <v>3</v>
       </c>
       <c r="L16" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M16" s="36" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N16" s="36" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="T16" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U16" s="13">
         <v>0</v>
@@ -8820,7 +8825,7 @@
         <v>60</v>
       </c>
       <c r="AX16" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY16" s="10">
         <v>1</v>
@@ -8832,42 +8837,42 @@
         <v>1</v>
       </c>
       <c r="BE16" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="BF16" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="BF16" s="5" t="s">
+      <c r="BG16" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="BG16" s="4" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="17" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B17" s="10">
         <v>13</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J17" s="10">
         <v>1</v>
@@ -8876,16 +8881,16 @@
         <v>3</v>
       </c>
       <c r="L17" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M17" s="36" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N17" s="36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U17" s="13">
         <v>0</v>
@@ -8969,7 +8974,7 @@
         <v>60</v>
       </c>
       <c r="AX17" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY17" s="10">
         <v>1</v>
@@ -8981,42 +8986,42 @@
         <v>1</v>
       </c>
       <c r="BE17" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="BF17" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="BF17" s="5" t="s">
+      <c r="BG17" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="BG17" s="4" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B18" s="10">
         <v>14</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E18" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -9025,16 +9030,16 @@
         <v>3</v>
       </c>
       <c r="L18" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M18" s="36" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N18" s="36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U18" s="13">
         <v>0</v>
@@ -9118,7 +9123,7 @@
         <v>60</v>
       </c>
       <c r="AX18" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY18" s="10">
         <v>1</v>
@@ -9130,42 +9135,42 @@
         <v>1</v>
       </c>
       <c r="BE18" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="BF18" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="BF18" s="5" t="s">
+      <c r="BG18" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="BG18" s="4" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B19" s="10">
         <v>15</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E19" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
@@ -9174,16 +9179,16 @@
         <v>3</v>
       </c>
       <c r="L19" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M19" s="36" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N19" s="36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U19" s="13">
         <v>0</v>
@@ -9267,7 +9272,7 @@
         <v>66</v>
       </c>
       <c r="AX19" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY19" s="10">
         <v>1</v>
@@ -9279,42 +9284,42 @@
         <v>1</v>
       </c>
       <c r="BE19" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="BF19" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="BF19" s="5" t="s">
+      <c r="BG19" s="4" t="s">
         <v>397</v>
-      </c>
-      <c r="BG19" s="4" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B20" s="10">
         <v>16</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E20" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -9323,16 +9328,16 @@
         <v>3</v>
       </c>
       <c r="L20" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M20" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N20" s="36" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U20" s="13">
         <v>0</v>
@@ -9416,7 +9421,7 @@
         <v>66</v>
       </c>
       <c r="AX20" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY20" s="10">
         <v>1</v>
@@ -9428,42 +9433,42 @@
         <v>1</v>
       </c>
       <c r="BE20" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="BF20" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="BF20" s="5" t="s">
+      <c r="BG20" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="BG20" s="4" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="21" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B21" s="10">
         <v>17</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E21" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J21" s="10">
         <v>1</v>
@@ -9472,16 +9477,16 @@
         <v>3</v>
       </c>
       <c r="L21" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M21" s="36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N21" s="36" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U21" s="13">
         <v>0</v>
@@ -9565,7 +9570,7 @@
         <v>60</v>
       </c>
       <c r="AX21" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY21" s="10">
         <v>1</v>
@@ -9577,42 +9582,42 @@
         <v>1</v>
       </c>
       <c r="BE21" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="BF21" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="BF21" s="5" t="s">
+      <c r="BG21" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="BG21" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B22" s="10">
         <v>18</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -9621,16 +9626,16 @@
         <v>3</v>
       </c>
       <c r="L22" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M22" s="36" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N22" s="36" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U22" s="13">
         <v>0</v>
@@ -9714,7 +9719,7 @@
         <v>66</v>
       </c>
       <c r="AX22" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY22" s="10">
         <v>1</v>
@@ -9726,42 +9731,42 @@
         <v>1</v>
       </c>
       <c r="BE22" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="BF22" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="BF22" s="5" t="s">
+      <c r="BG22" s="4" t="s">
         <v>406</v>
-      </c>
-      <c r="BG22" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B23" s="10">
         <v>19</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E23" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J23" s="10">
         <v>1</v>
@@ -9770,16 +9775,16 @@
         <v>3</v>
       </c>
       <c r="L23" s="36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M23" s="36" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N23" s="36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U23" s="13">
         <v>0</v>
@@ -9863,7 +9868,7 @@
         <v>60</v>
       </c>
       <c r="AX23" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AY23" s="10">
         <v>1</v>
@@ -9875,13 +9880,13 @@
         <v>1</v>
       </c>
       <c r="BE23" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="BF23" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="BF23" s="5" t="s">
+      <c r="BG23" s="4" t="s">
         <v>409</v>
-      </c>
-      <c r="BG23" s="4" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="24" spans="1:59" x14ac:dyDescent="0.3">
@@ -9901,10 +9906,10 @@
         <v>125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J24" s="10">
         <v>2</v>
@@ -10004,16 +10009,16 @@
         <v>0</v>
       </c>
       <c r="BE24" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF24" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BG24" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
         <v>61</v>
       </c>
@@ -10026,14 +10031,14 @@
       <c r="D25" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>128</v>
+      <c r="E25" s="38" t="s">
+        <v>441</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J25" s="10">
         <v>2</v>
@@ -10058,7 +10063,7 @@
         <v>65</v>
       </c>
       <c r="U25" s="13">
-        <v>2.8279999999999998</v>
+        <v>2.8284280000000002</v>
       </c>
       <c r="V25" s="13">
         <v>395</v>
@@ -10133,13 +10138,13 @@
         <v>0</v>
       </c>
       <c r="BE25" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF25" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG25" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="1:59" x14ac:dyDescent="0.3">
@@ -10150,7 +10155,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>67</v>
@@ -10159,10 +10164,10 @@
         <v>68</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J26" s="10">
         <v>2</v>
@@ -10184,7 +10189,7 @@
         <v>65</v>
       </c>
       <c r="U26" s="13">
-        <v>1.4139999999999999</v>
+        <v>1.4142140000000001</v>
       </c>
       <c r="V26" s="13">
         <v>1050</v>
@@ -10259,13 +10264,13 @@
         <v>0</v>
       </c>
       <c r="BE26" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF26" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BG26" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:59" x14ac:dyDescent="0.3">
@@ -10276,19 +10281,19 @@
         <v>4</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>69</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J27" s="10">
         <v>2</v>
@@ -10298,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q27" s="10">
         <v>1</v>
@@ -10388,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="BE27" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF27" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:59" x14ac:dyDescent="0.3">
@@ -10402,19 +10407,19 @@
         <v>6</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J28" s="10">
         <v>2</v>
@@ -10511,13 +10516,13 @@
         <v>0</v>
       </c>
       <c r="BE28" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF28" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BG28" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="1:59" x14ac:dyDescent="0.3">
@@ -10528,19 +10533,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>71</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J29" s="10">
         <v>2</v>
@@ -10625,10 +10630,10 @@
         <v>0</v>
       </c>
       <c r="AP29" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AQ29" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AR29" s="11">
         <v>0</v>
@@ -10643,13 +10648,13 @@
         <v>0</v>
       </c>
       <c r="BE29" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF29" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BG29" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="1:59" x14ac:dyDescent="0.3">
@@ -10660,19 +10665,19 @@
         <v>8</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>72</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J30" s="10">
         <v>2</v>
@@ -10757,10 +10762,10 @@
         <v>0</v>
       </c>
       <c r="AP30" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AQ30" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AR30" s="11">
         <v>0</v>
@@ -10775,13 +10780,13 @@
         <v>0</v>
       </c>
       <c r="BE30" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF30" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BG30" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:59" x14ac:dyDescent="0.3">
@@ -10792,16 +10797,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="E31" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>141</v>
-      </c>
       <c r="F31" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J31" s="10">
         <v>2</v>
@@ -10898,10 +10903,10 @@
         <v>0</v>
       </c>
       <c r="BE31" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF31" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:59" x14ac:dyDescent="0.3">
@@ -10912,16 +10917,16 @@
         <v>10</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J32" s="10">
         <v>2</v>
@@ -10931,7 +10936,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Q32" s="10">
         <v>0</v>
@@ -11009,10 +11014,10 @@
         <v>0</v>
       </c>
       <c r="AP32" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AQ32" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR32" s="11">
         <v>1</v>
@@ -11033,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="AX32" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AY32" s="10">
         <v>0</v>
@@ -11045,10 +11050,10 @@
         <v>0</v>
       </c>
       <c r="BE32" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF32" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:59" x14ac:dyDescent="0.3">
@@ -11059,19 +11064,19 @@
         <v>11</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="F33" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J33" s="10">
         <v>2</v>
@@ -11171,37 +11176,37 @@
         <v>0</v>
       </c>
       <c r="BE33" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF33" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="10">
+        <v>1</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="10">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="E34" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="F34" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="J34" s="10">
         <v>2</v>
       </c>
       <c r="L34" s="16"/>
       <c r="T34" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U34" s="13">
         <v>1.5</v>
@@ -11270,13 +11275,13 @@
         <v>0</v>
       </c>
       <c r="BE34" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BF34" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BG34" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4F9535-0E9F-4D51-B86E-1179F629A337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B591D754-8391-4297-B9B2-9FA7CE2F8FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3450" yWindow="340" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9955,7 +9955,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="13">
-        <v>5500</v>
+        <v>5960</v>
       </c>
       <c r="AC24" s="13">
         <v>265</v>
@@ -10084,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="13">
-        <v>4590</v>
+        <v>5090</v>
       </c>
       <c r="AC25" s="13">
         <v>185</v>
@@ -10210,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="13">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="AC26" s="13">
         <v>325</v>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="AB27" s="13">
-        <v>12500</v>
+        <v>13000</v>
       </c>
       <c r="AC27" s="13">
         <v>375</v>

--- a/Assets/DataTools/EntityAttributes.xlsx
+++ b/Assets/DataTools/EntityAttributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\projects\TD\Assets\DataTools\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B591D754-8391-4297-B9B2-9FA7CE2F8FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEEC6D5-24B2-4555-97D2-EBF607C1CFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="340" windowWidth="19640" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="450">
   <si>
     <t>ChineseName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5962,6 +5962,38 @@
       </rPr>
       <t>中擅长使用弓箭远程攻击的怪物。作为亡灵生物，它惧怕阳光，但它头顶的帽子似乎可以帮他解决这个问题。骷髅之间似乎拥有交流能力，可以将对手的信息告诉对方。</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullets</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['witch']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['skeleton']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['eyjafjalla_default','eyjafjalla_s2']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['default_physics']</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>['default_magic']</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6056,7 +6088,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -6108,14 +6140,23 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="dotted">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
-      <top style="dotted">
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="dotted">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -6124,7 +6165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -6141,9 +6182,6 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6176,10 +6214,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6231,6 +6265,27 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6515,34 +6570,35 @@
   <dimension ref="A1:BH34"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="12.58203125" style="10" customWidth="1"/>
-    <col min="3" max="9" width="12.58203125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="12.58203125" style="10" customWidth="1"/>
-    <col min="11" max="11" width="12.58203125" style="11" customWidth="1"/>
-    <col min="12" max="14" width="12.58203125" style="12" customWidth="1"/>
-    <col min="15" max="15" width="12.58203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="12.58203125" style="9" customWidth="1"/>
-    <col min="17" max="19" width="12.58203125" style="10" customWidth="1"/>
-    <col min="20" max="20" width="12.58203125" style="12" customWidth="1"/>
-    <col min="21" max="23" width="12.58203125" style="13" customWidth="1"/>
-    <col min="24" max="26" width="12.58203125" style="11" customWidth="1"/>
-    <col min="27" max="32" width="12.58203125" style="13" customWidth="1"/>
-    <col min="33" max="41" width="12.58203125" style="11" customWidth="1"/>
-    <col min="42" max="42" width="12.58203125" style="12" customWidth="1"/>
-    <col min="43" max="44" width="12.58203125" style="11" customWidth="1"/>
-    <col min="45" max="48" width="12.58203125" style="10" customWidth="1"/>
-    <col min="49" max="50" width="12.58203125" style="14" customWidth="1"/>
-    <col min="51" max="51" width="12.58203125" style="10" customWidth="1"/>
-    <col min="52" max="52" width="12.58203125" style="14" customWidth="1"/>
-    <col min="53" max="53" width="12.58203125" style="10" customWidth="1"/>
-    <col min="54" max="54" width="12.58203125" style="13" customWidth="1"/>
-    <col min="55" max="56" width="12.58203125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="9" customWidth="1"/>
+    <col min="3" max="9" width="12.58203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.58203125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="12.58203125" style="10" customWidth="1"/>
+    <col min="12" max="14" width="12.58203125" style="11" customWidth="1"/>
+    <col min="15" max="15" width="12.58203125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="12.58203125" style="8" customWidth="1"/>
+    <col min="17" max="19" width="12.58203125" style="9" customWidth="1"/>
+    <col min="20" max="20" width="12.58203125" style="11" customWidth="1"/>
+    <col min="21" max="23" width="12.58203125" style="12" customWidth="1"/>
+    <col min="24" max="26" width="12.58203125" style="10" customWidth="1"/>
+    <col min="27" max="32" width="12.58203125" style="12" customWidth="1"/>
+    <col min="33" max="41" width="12.58203125" style="10" customWidth="1"/>
+    <col min="42" max="42" width="12.58203125" style="11" customWidth="1"/>
+    <col min="43" max="44" width="12.58203125" style="10" customWidth="1"/>
+    <col min="45" max="48" width="12.58203125" style="9" customWidth="1"/>
+    <col min="49" max="50" width="12.58203125" style="13" customWidth="1"/>
+    <col min="51" max="51" width="12.58203125" style="9" customWidth="1"/>
+    <col min="52" max="52" width="12.58203125" style="13" customWidth="1"/>
+    <col min="53" max="53" width="12.58203125" style="9" customWidth="1"/>
+    <col min="54" max="54" width="12.58203125" style="12" customWidth="1"/>
+    <col min="55" max="56" width="12.58203125" style="10" customWidth="1"/>
     <col min="57" max="59" width="12.58203125" style="4" customWidth="1"/>
-    <col min="60" max="16384" width="8.6640625" style="7"/>
+    <col min="60" max="60" width="8.6640625" style="4"/>
+    <col min="61" max="16384" width="8.6640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:60" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -6605,35 +6661,35 @@
       <c r="BD1" s="6"/>
       <c r="BE1" s="6"/>
       <c r="BF1" s="6"/>
-      <c r="BG1" s="6"/>
-      <c r="BH1" s="20"/>
+      <c r="BG1" s="38"/>
+      <c r="BH1" s="42"/>
     </row>
-    <row r="2" spans="1:60" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:60" s="43" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
       <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
       <c r="T2" s="6" t="s">
         <v>7</v>
       </c>
@@ -6661,196 +6717,196 @@
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
       <c r="AR2" s="6"/>
-      <c r="AS2" s="29" t="s">
+      <c r="AS2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="AT2" s="29"/>
-      <c r="AU2" s="29"/>
-      <c r="AV2" s="29"/>
-      <c r="AW2" s="29"/>
-      <c r="AX2" s="29"/>
-      <c r="AY2" s="29"/>
-      <c r="AZ2" s="29"/>
-      <c r="BA2" s="29"/>
+      <c r="AT2" s="26"/>
+      <c r="AU2" s="26"/>
+      <c r="AV2" s="26"/>
+      <c r="AW2" s="26"/>
+      <c r="AX2" s="26"/>
+      <c r="AY2" s="26"/>
+      <c r="AZ2" s="26"/>
+      <c r="BA2" s="26"/>
       <c r="BB2" s="6" t="s">
         <v>9</v>
       </c>
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
-      <c r="BE2" s="1" t="s">
+      <c r="BE2" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
-      <c r="BH2" s="20"/>
+      <c r="BF2" s="37"/>
+      <c r="BG2" s="37"/>
+      <c r="BH2" s="1"/>
     </row>
-    <row r="3" spans="1:60" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:60" s="44" customFormat="1" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="J3" s="31" t="s">
+      <c r="J3" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="30" t="s">
+      <c r="P3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="30" t="s">
+      <c r="Q3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="R3" s="30" t="s">
+      <c r="R3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="30" t="s">
+      <c r="S3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="32" t="s">
+      <c r="T3" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="32" t="s">
+      <c r="U3" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="32" t="s">
+      <c r="V3" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="W3" s="32" t="s">
+      <c r="W3" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="32" t="s">
+      <c r="Y3" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="33" t="s">
+      <c r="Z3" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="AA3" s="33" t="s">
+      <c r="AA3" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="AB3" s="32" t="s">
+      <c r="AB3" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="32" t="s">
+      <c r="AC3" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="32" t="s">
+      <c r="AD3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="32" t="s">
+      <c r="AE3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="AG3" s="32" t="s">
+      <c r="AG3" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="AH3" s="32" t="s">
+      <c r="AH3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="AI3" s="33" t="s">
+      <c r="AI3" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="AJ3" s="33" t="s">
+      <c r="AJ3" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="AK3" s="33" t="s">
+      <c r="AK3" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="AL3" s="33" t="s">
+      <c r="AL3" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="AM3" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="AN3" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="AO3" s="33" t="s">
+      <c r="AO3" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="AP3" s="32" t="s">
+      <c r="AP3" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="AQ3" s="32" t="s">
+      <c r="AQ3" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="AR3" s="33" t="s">
+      <c r="AR3" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="AS3" s="30" t="s">
+      <c r="AS3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="AT3" s="30" t="s">
+      <c r="AT3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="AU3" s="34" t="s">
+      <c r="AU3" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="AV3" s="30" t="s">
+      <c r="AV3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="AW3" s="30" t="s">
+      <c r="AW3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="AX3" s="31" t="s">
+      <c r="AX3" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="AY3" s="30" t="s">
+      <c r="AY3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="AZ3" s="30" t="s">
+      <c r="AZ3" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="BA3" s="30" t="s">
+      <c r="BA3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="BB3" s="32" t="s">
+      <c r="BB3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="BC3" s="32" t="s">
+      <c r="BC3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="BD3" s="32" t="s">
+      <c r="BD3" s="29" t="s">
         <v>37</v>
       </c>
       <c r="BE3" s="2" t="s">
@@ -6859,178 +6915,180 @@
       <c r="BF3" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="BG3" s="2" t="s">
+      <c r="BG3" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="BH3" s="21"/>
+      <c r="BH3" s="2" t="s">
+        <v>442</v>
+      </c>
     </row>
-    <row r="4" spans="1:60" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+    <row r="4" spans="1:60" s="44" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="C4" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="27" t="s">
         <v>245</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="Q4" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="R4" s="30" t="s">
+      <c r="R4" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="T4" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="U4" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="V4" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="W4" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="X4" s="32" t="s">
+      <c r="X4" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="Y4" s="32" t="s">
+      <c r="Y4" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="Z4" s="32" t="s">
+      <c r="Z4" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="29" t="s">
         <v>439</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AD4" s="29" t="s">
         <v>215</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AE4" s="29" t="s">
         <v>216</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AF4" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AG4" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AH4" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AJ4" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AK4" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AL4" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AM4" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AN4" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AO4" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AP4" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AQ4" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="AR4" s="32" t="s">
+      <c r="AR4" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AS4" s="27" t="s">
         <v>230</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AT4" s="27" t="s">
         <v>231</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AU4" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AV4" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AW4" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AX4" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AY4" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="AZ4" s="30" t="s">
+      <c r="AZ4" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="BA4" s="30" t="s">
+      <c r="BA4" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="BB4" s="32" t="s">
+      <c r="BB4" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="BC4" s="32" t="s">
+      <c r="BC4" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="BD4" s="32" t="s">
+      <c r="BD4" s="29" t="s">
         <v>241</v>
       </c>
       <c r="BE4" s="3" t="s">
@@ -7039,164 +7097,166 @@
       <c r="BF4" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="BG4" s="3" t="s">
+      <c r="BG4" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="BH4" s="21"/>
+      <c r="BH4" s="3" t="s">
+        <v>443</v>
+      </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:60" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="23">
-        <v>1</v>
-      </c>
-      <c r="C5" s="22" t="s">
+      <c r="B5" s="20">
+        <v>1</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="J5" s="23">
-        <v>1</v>
-      </c>
-      <c r="K5" s="24">
+      <c r="J5" s="20">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21">
         <v>6</v>
       </c>
-      <c r="L5" s="25" t="s">
+      <c r="L5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="N5" s="25" t="s">
+      <c r="N5" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="O5" s="23"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="25" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="22" t="s">
         <v>247</v>
       </c>
-      <c r="U5" s="26">
-        <v>0</v>
-      </c>
-      <c r="V5" s="26">
+      <c r="U5" s="23">
+        <v>0</v>
+      </c>
+      <c r="V5" s="23">
         <v>762</v>
       </c>
-      <c r="W5" s="26">
+      <c r="W5" s="23">
         <v>1.6</v>
       </c>
-      <c r="X5" s="24">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="26">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="26">
+      <c r="X5" s="21">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="23">
         <v>1743</v>
       </c>
-      <c r="AC5" s="26">
+      <c r="AC5" s="23">
         <v>122</v>
       </c>
-      <c r="AD5" s="26">
+      <c r="AD5" s="23">
         <v>20</v>
       </c>
-      <c r="AE5" s="26">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="26">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="24">
-        <v>1</v>
-      </c>
-      <c r="AH5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AL5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="24">
-        <v>0</v>
-      </c>
-      <c r="AP5" s="25" t="s">
+      <c r="AE5" s="23">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="23">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="21">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="21">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="AQ5" s="24" t="s">
+      <c r="AQ5" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="AR5" s="24">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="23">
+      <c r="AR5" s="21">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="20">
         <v>19</v>
       </c>
-      <c r="AT5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AU5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AV5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AW5" s="27">
+      <c r="AT5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AU5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="24">
         <v>70</v>
       </c>
-      <c r="AX5" s="28" t="s">
+      <c r="AX5" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="AY5" s="23">
-        <v>1</v>
-      </c>
-      <c r="AZ5" s="27">
+      <c r="AY5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AZ5" s="24">
         <v>50</v>
       </c>
-      <c r="BA5" s="23">
-        <v>1</v>
-      </c>
-      <c r="BB5" s="26"/>
-      <c r="BC5" s="24"/>
-      <c r="BD5" s="24"/>
+      <c r="BA5" s="20">
+        <v>1</v>
+      </c>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="21"/>
+      <c r="BD5" s="21"/>
       <c r="BE5" s="4" t="s">
         <v>436</v>
       </c>
@@ -7206,144 +7266,147 @@
       <c r="BG5" s="4" t="s">
         <v>257</v>
       </c>
+      <c r="BH5" s="5" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>2</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="11">
+      <c r="J6" s="9">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
         <v>6</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="T6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="U6" s="13">
-        <v>0</v>
-      </c>
-      <c r="V6" s="13">
+      <c r="U6" s="12">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12">
         <v>1602</v>
       </c>
-      <c r="W6" s="13">
+      <c r="W6" s="12">
         <v>3</v>
       </c>
-      <c r="X6" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="13">
+      <c r="X6" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="12">
         <v>1678</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AC6" s="12">
         <v>135</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AD6" s="12">
         <v>20</v>
       </c>
-      <c r="AE6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS6" s="10">
+      <c r="AE6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="9">
         <v>23</v>
       </c>
-      <c r="AT6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW6" s="14">
+      <c r="AT6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="13">
         <v>66</v>
       </c>
-      <c r="AX6" s="15" t="s">
+      <c r="AX6" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY6" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ6" s="14">
+      <c r="AY6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="13">
         <v>50</v>
       </c>
-      <c r="BA6" s="10">
+      <c r="BA6" s="9">
         <v>1</v>
       </c>
       <c r="BE6" s="4" t="s">
@@ -7355,144 +7418,147 @@
       <c r="BG6" s="4" t="s">
         <v>258</v>
       </c>
+      <c r="BH6" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="7" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>3</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="J7" s="10">
-        <v>1</v>
-      </c>
-      <c r="K7" s="11">
+      <c r="J7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10">
         <v>3</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="T7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="13">
-        <v>0</v>
-      </c>
-      <c r="V7" s="13">
+      <c r="U7" s="12">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12">
         <v>446</v>
       </c>
-      <c r="W7" s="13">
-        <v>1</v>
-      </c>
-      <c r="X7" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="13">
+      <c r="W7" s="12">
+        <v>1</v>
+      </c>
+      <c r="X7" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="12">
         <v>1060</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AC7" s="12">
         <v>126</v>
       </c>
-      <c r="AD7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS7" s="10">
+      <c r="AD7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS7" s="9">
         <v>9</v>
       </c>
-      <c r="AT7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW7" s="14">
+      <c r="AT7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="13">
         <v>66</v>
       </c>
-      <c r="AX7" s="15" t="s">
+      <c r="AX7" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY7" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ7" s="14">
+      <c r="AY7" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ7" s="13">
         <v>50</v>
       </c>
-      <c r="BA7" s="10">
+      <c r="BA7" s="9">
         <v>1</v>
       </c>
       <c r="BE7" s="4" t="s">
@@ -7504,144 +7570,147 @@
       <c r="BG7" s="4" t="s">
         <v>259</v>
       </c>
+      <c r="BH7" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="8" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>4</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="J8" s="10">
-        <v>1</v>
-      </c>
-      <c r="K8" s="11">
+      <c r="J8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10">
         <v>3</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="T8" s="12" t="s">
+      <c r="T8" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="U8" s="13">
-        <v>0</v>
-      </c>
-      <c r="V8" s="13">
+      <c r="U8" s="12">
+        <v>0</v>
+      </c>
+      <c r="V8" s="12">
         <v>543</v>
       </c>
-      <c r="W8" s="13">
+      <c r="W8" s="12">
         <v>1.6</v>
       </c>
-      <c r="X8" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="13">
+      <c r="X8" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="12">
         <v>1100</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AC8" s="12">
         <v>90</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AD8" s="12">
         <v>15</v>
       </c>
-      <c r="AE8" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS8" s="10">
+      <c r="AE8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="9">
         <v>16</v>
       </c>
-      <c r="AT8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW8" s="14">
+      <c r="AT8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="13">
         <v>60</v>
       </c>
-      <c r="AX8" s="15" t="s">
+      <c r="AX8" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY8" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ8" s="14">
+      <c r="AY8" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ8" s="13">
         <v>50</v>
       </c>
-      <c r="BA8" s="10">
+      <c r="BA8" s="9">
         <v>1</v>
       </c>
       <c r="BE8" s="4" t="s">
@@ -7653,144 +7722,147 @@
       <c r="BG8" s="4" t="s">
         <v>260</v>
       </c>
+      <c r="BH8" s="4" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="9" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>5</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="10">
-        <v>1</v>
-      </c>
-      <c r="K9" s="11">
+      <c r="J9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
         <v>3</v>
       </c>
-      <c r="L9" s="17" t="s">
+      <c r="L9" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N9" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="T9" s="12" t="s">
+      <c r="T9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="U9" s="13">
-        <v>0</v>
-      </c>
-      <c r="V9" s="13">
+      <c r="U9" s="12">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12">
         <v>350</v>
       </c>
-      <c r="W9" s="13">
+      <c r="W9" s="12">
         <v>1.2</v>
       </c>
-      <c r="X9" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="13">
+      <c r="X9" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="12">
         <v>1833</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AC9" s="12">
         <v>496</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AD9" s="12">
         <v>10</v>
       </c>
-      <c r="AE9" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="11">
+      <c r="AE9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="10">
         <v>3</v>
       </c>
-      <c r="AH9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="10">
+      <c r="AH9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="9">
         <v>15</v>
       </c>
-      <c r="AT9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="14">
+      <c r="AT9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="13">
         <v>66</v>
       </c>
-      <c r="AX9" s="15" t="s">
+      <c r="AX9" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ9" s="14">
+      <c r="AY9" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="13">
         <v>50</v>
       </c>
-      <c r="BA9" s="10">
+      <c r="BA9" s="9">
         <v>1</v>
       </c>
       <c r="BE9" s="4" t="s">
@@ -7802,144 +7874,147 @@
       <c r="BG9" s="4" t="s">
         <v>261</v>
       </c>
+      <c r="BH9" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="10" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="11">
+      <c r="J10" s="9">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
         <v>3</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="T10" s="12" t="s">
+      <c r="T10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="U10" s="13">
-        <v>0</v>
-      </c>
-      <c r="V10" s="13">
+      <c r="U10" s="12">
+        <v>0</v>
+      </c>
+      <c r="V10" s="12">
         <v>828</v>
       </c>
-      <c r="W10" s="13">
+      <c r="W10" s="12">
         <v>1.5</v>
       </c>
-      <c r="X10" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="13">
+      <c r="X10" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="12">
         <v>2745</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AC10" s="12">
         <v>155</v>
       </c>
-      <c r="AD10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS10" s="10">
+      <c r="AD10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="9">
         <v>13</v>
       </c>
-      <c r="AT10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="14">
+      <c r="AT10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="13">
         <v>60</v>
       </c>
-      <c r="AX10" s="15" t="s">
+      <c r="AX10" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ10" s="14">
+      <c r="AY10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="13">
         <v>50</v>
       </c>
-      <c r="BA10" s="10">
+      <c r="BA10" s="9">
         <v>1</v>
       </c>
       <c r="BE10" s="4" t="s">
@@ -7951,144 +8026,147 @@
       <c r="BG10" s="4" t="s">
         <v>262</v>
       </c>
+      <c r="BH10" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="11" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>7</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="J11" s="10">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11">
+      <c r="J11" s="9">
+        <v>1</v>
+      </c>
+      <c r="K11" s="10">
         <v>3</v>
       </c>
-      <c r="L11" s="36" t="s">
+      <c r="L11" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="M11" s="36" t="s">
+      <c r="M11" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="N11" s="36" t="s">
+      <c r="N11" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="T11" s="12" t="s">
+      <c r="T11" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="U11" s="13">
-        <v>0</v>
-      </c>
-      <c r="V11" s="13">
+      <c r="U11" s="12">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12">
         <v>408</v>
       </c>
-      <c r="W11" s="13">
+      <c r="W11" s="12">
         <v>2.85</v>
       </c>
-      <c r="X11" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="11">
+      <c r="X11" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="10">
         <v>3</v>
       </c>
-      <c r="Z11" s="11">
+      <c r="Z11" s="10">
         <v>2</v>
       </c>
-      <c r="AA11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="13">
+      <c r="AA11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="12">
         <v>1220</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AC11" s="12">
         <v>110</v>
       </c>
-      <c r="AD11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS11" s="10">
+      <c r="AD11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="9">
         <v>15</v>
       </c>
-      <c r="AT11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW11" s="14">
+      <c r="AT11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="13">
         <v>60</v>
       </c>
-      <c r="AX11" s="15" t="s">
+      <c r="AX11" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="AY11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ11" s="14">
+      <c r="AY11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="13">
         <v>50</v>
       </c>
-      <c r="BA11" s="10">
+      <c r="BA11" s="9">
         <v>1</v>
       </c>
       <c r="BE11" s="4" t="s">
@@ -8100,144 +8178,147 @@
       <c r="BG11" s="4" t="s">
         <v>286</v>
       </c>
+      <c r="BH11" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="12" spans="1:60" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>8</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="32" t="s">
         <v>411</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="J12" s="10">
-        <v>1</v>
-      </c>
-      <c r="K12" s="11">
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
         <v>3</v>
       </c>
-      <c r="L12" s="36" t="s">
+      <c r="L12" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M12" s="36" t="s">
+      <c r="M12" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="N12" s="36" t="s">
+      <c r="N12" s="33" t="s">
         <v>419</v>
       </c>
-      <c r="T12" s="12" t="s">
+      <c r="T12" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="U12" s="13">
-        <v>0</v>
-      </c>
-      <c r="V12" s="13">
+      <c r="U12" s="12">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
         <v>438</v>
       </c>
-      <c r="W12" s="13">
-        <v>1</v>
-      </c>
-      <c r="X12" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="13">
+      <c r="W12" s="12">
+        <v>1</v>
+      </c>
+      <c r="X12" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="12">
         <v>1080</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AC12" s="12">
         <v>134</v>
       </c>
-      <c r="AD12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="10">
+      <c r="AD12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="9">
         <v>9</v>
       </c>
-      <c r="AT12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW12" s="14">
+      <c r="AT12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW12" s="13">
         <v>60</v>
       </c>
-      <c r="AX12" s="15" t="s">
+      <c r="AX12" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ12" s="14">
+      <c r="AY12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ12" s="13">
         <v>50</v>
       </c>
-      <c r="BA12" s="10">
+      <c r="BA12" s="9">
         <v>1</v>
       </c>
       <c r="BE12" s="4" t="s">
@@ -8249,144 +8330,147 @@
       <c r="BG12" s="4" t="s">
         <v>376</v>
       </c>
+      <c r="BH12" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>9</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="18" t="s">
         <v>352</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="J13" s="10">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11">
+      <c r="J13" s="9">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10">
         <v>3</v>
       </c>
-      <c r="L13" s="36" t="s">
+      <c r="L13" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M13" s="36" t="s">
+      <c r="M13" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="N13" s="36" t="s">
+      <c r="N13" s="33" t="s">
         <v>420</v>
       </c>
-      <c r="T13" s="12" t="s">
+      <c r="T13" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="U13" s="13">
-        <v>0</v>
-      </c>
-      <c r="V13" s="13">
+      <c r="U13" s="12">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
         <v>427</v>
       </c>
-      <c r="W13" s="13">
+      <c r="W13" s="12">
         <v>2.85</v>
       </c>
-      <c r="X13" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="11">
+      <c r="X13" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="10">
         <v>3</v>
       </c>
-      <c r="Z13" s="11">
+      <c r="Z13" s="10">
         <v>2</v>
       </c>
-      <c r="AA13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="13">
+      <c r="AA13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="12">
         <v>1135</v>
       </c>
-      <c r="AC13" s="13">
+      <c r="AC13" s="12">
         <v>109</v>
       </c>
-      <c r="AD13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="10">
+      <c r="AD13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="9">
         <v>15</v>
       </c>
-      <c r="AT13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW13" s="14">
+      <c r="AT13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW13" s="13">
         <v>66</v>
       </c>
-      <c r="AX13" s="15" t="s">
+      <c r="AX13" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ13" s="14">
+      <c r="AY13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="13">
         <v>50</v>
       </c>
-      <c r="BA13" s="10">
+      <c r="BA13" s="9">
         <v>1</v>
       </c>
       <c r="BE13" s="4" t="s">
@@ -8398,144 +8482,147 @@
       <c r="BG13" s="4" t="s">
         <v>379</v>
       </c>
+      <c r="BH13" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="14" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>10</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="J14" s="10">
-        <v>1</v>
-      </c>
-      <c r="K14" s="11">
+      <c r="J14" s="9">
+        <v>1</v>
+      </c>
+      <c r="K14" s="10">
         <v>3</v>
       </c>
-      <c r="L14" s="36" t="s">
+      <c r="L14" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M14" s="36" t="s">
+      <c r="M14" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="N14" s="36" t="s">
+      <c r="N14" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="T14" s="12" t="s">
+      <c r="T14" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="U14" s="13">
-        <v>0</v>
-      </c>
-      <c r="V14" s="13">
+      <c r="U14" s="12">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12">
         <v>305</v>
       </c>
-      <c r="W14" s="13">
+      <c r="W14" s="12">
         <v>1.2</v>
       </c>
-      <c r="X14" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="13">
+      <c r="X14" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="12">
         <v>2630</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AC14" s="12">
         <v>475</v>
       </c>
-      <c r="AD14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="11">
+      <c r="AD14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="10">
         <v>3</v>
       </c>
-      <c r="AH14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS14" s="10">
+      <c r="AH14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="9">
         <v>16</v>
       </c>
-      <c r="AT14" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU14" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV14" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="14">
+      <c r="AT14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="13">
         <v>60</v>
       </c>
-      <c r="AX14" s="15" t="s">
+      <c r="AX14" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY14" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ14" s="14">
+      <c r="AY14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="13">
         <v>50</v>
       </c>
-      <c r="BA14" s="10">
+      <c r="BA14" s="9">
         <v>1</v>
       </c>
       <c r="BE14" s="4" t="s">
@@ -8547,144 +8634,147 @@
       <c r="BG14" s="4" t="s">
         <v>382</v>
       </c>
+      <c r="BH14" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="15" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>11</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="J15" s="10">
-        <v>1</v>
-      </c>
-      <c r="K15" s="11">
+      <c r="J15" s="9">
+        <v>1</v>
+      </c>
+      <c r="K15" s="10">
         <v>3</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M15" s="36" t="s">
+      <c r="M15" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="N15" s="36" t="s">
+      <c r="N15" s="33" t="s">
         <v>421</v>
       </c>
-      <c r="T15" s="12" t="s">
+      <c r="T15" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="U15" s="13">
-        <v>0</v>
-      </c>
-      <c r="V15" s="13">
+      <c r="U15" s="12">
+        <v>0</v>
+      </c>
+      <c r="V15" s="12">
         <v>295</v>
       </c>
-      <c r="W15" s="13">
+      <c r="W15" s="12">
         <v>1.2</v>
       </c>
-      <c r="X15" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="13">
+      <c r="X15" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="12">
         <v>2035</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AC15" s="12">
         <v>578</v>
       </c>
-      <c r="AD15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="11">
+      <c r="AD15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="10">
         <v>3</v>
       </c>
-      <c r="AH15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="10">
+      <c r="AH15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="9">
         <v>16</v>
       </c>
-      <c r="AT15" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU15" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="14">
+      <c r="AT15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="13">
         <v>60</v>
       </c>
-      <c r="AX15" s="15" t="s">
+      <c r="AX15" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY15" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ15" s="14">
+      <c r="AY15" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="13">
         <v>50</v>
       </c>
-      <c r="BA15" s="10">
+      <c r="BA15" s="9">
         <v>1</v>
       </c>
       <c r="BE15" s="4" t="s">
@@ -8696,144 +8786,147 @@
       <c r="BG15" s="4" t="s">
         <v>385</v>
       </c>
+      <c r="BH15" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="16" spans="1:60" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>12</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>356</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="J16" s="10">
-        <v>1</v>
-      </c>
-      <c r="K16" s="11">
+      <c r="J16" s="9">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10">
         <v>3</v>
       </c>
-      <c r="L16" s="36" t="s">
+      <c r="L16" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M16" s="36" t="s">
+      <c r="M16" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="N16" s="36" t="s">
+      <c r="N16" s="33" t="s">
         <v>422</v>
       </c>
-      <c r="T16" s="12" t="s">
+      <c r="T16" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="U16" s="13">
-        <v>0</v>
-      </c>
-      <c r="V16" s="13">
+      <c r="U16" s="12">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12">
         <v>699</v>
       </c>
-      <c r="W16" s="13">
+      <c r="W16" s="12">
         <v>2.8</v>
       </c>
-      <c r="X16" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="13">
+      <c r="X16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="12">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="12">
         <v>1150</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AC16" s="12">
         <v>85</v>
       </c>
-      <c r="AD16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS16" s="10">
+      <c r="AD16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="9">
         <v>21</v>
       </c>
-      <c r="AT16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW16" s="14">
+      <c r="AT16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW16" s="13">
         <v>60</v>
       </c>
-      <c r="AX16" s="15" t="s">
+      <c r="AX16" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="14">
+      <c r="AY16" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ16" s="13">
         <v>50</v>
       </c>
-      <c r="BA16" s="10">
+      <c r="BA16" s="9">
         <v>1</v>
       </c>
       <c r="BE16" s="4" t="s">
@@ -8845,144 +8938,147 @@
       <c r="BG16" s="4" t="s">
         <v>388</v>
       </c>
+      <c r="BH16" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
-    <row r="17" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+    <row r="17" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>13</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="J17" s="10">
-        <v>1</v>
-      </c>
-      <c r="K17" s="11">
+      <c r="J17" s="9">
+        <v>1</v>
+      </c>
+      <c r="K17" s="10">
         <v>3</v>
       </c>
-      <c r="L17" s="36" t="s">
+      <c r="L17" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M17" s="36" t="s">
+      <c r="M17" s="33" t="s">
         <v>412</v>
       </c>
-      <c r="N17" s="36" t="s">
+      <c r="N17" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="T17" s="12" t="s">
+      <c r="T17" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="U17" s="13">
-        <v>0</v>
-      </c>
-      <c r="V17" s="13">
+      <c r="U17" s="12">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12">
         <v>516</v>
       </c>
-      <c r="W17" s="13">
-        <v>1</v>
-      </c>
-      <c r="X17" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="13">
+      <c r="W17" s="12">
+        <v>1</v>
+      </c>
+      <c r="X17" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="12">
         <v>1226</v>
       </c>
-      <c r="AC17" s="13">
+      <c r="AC17" s="12">
         <v>279</v>
       </c>
-      <c r="AD17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR17" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS17" s="10">
+      <c r="AD17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS17" s="9">
         <v>8</v>
       </c>
-      <c r="AT17" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU17" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV17" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW17" s="14">
+      <c r="AT17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW17" s="13">
         <v>60</v>
       </c>
-      <c r="AX17" s="15" t="s">
+      <c r="AX17" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY17" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ17" s="14">
+      <c r="AY17" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ17" s="13">
         <v>50</v>
       </c>
-      <c r="BA17" s="10">
+      <c r="BA17" s="9">
         <v>1</v>
       </c>
       <c r="BE17" s="4" t="s">
@@ -8994,144 +9090,147 @@
       <c r="BG17" s="4" t="s">
         <v>391</v>
       </c>
+      <c r="BH17" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>14</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="J18" s="10">
-        <v>1</v>
-      </c>
-      <c r="K18" s="11">
+      <c r="J18" s="9">
+        <v>1</v>
+      </c>
+      <c r="K18" s="10">
         <v>3</v>
       </c>
-      <c r="L18" s="36" t="s">
+      <c r="L18" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M18" s="36" t="s">
+      <c r="M18" s="33" t="s">
         <v>412</v>
       </c>
-      <c r="N18" s="36" t="s">
+      <c r="N18" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="T18" s="12" t="s">
+      <c r="T18" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="U18" s="13">
-        <v>0</v>
-      </c>
-      <c r="V18" s="13">
+      <c r="U18" s="12">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12">
         <v>325</v>
       </c>
-      <c r="W18" s="13">
+      <c r="W18" s="12">
         <v>1.05</v>
       </c>
-      <c r="X18" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="13">
+      <c r="X18" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="12">
         <v>1325</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AC18" s="12">
         <v>330</v>
       </c>
-      <c r="AD18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="11">
+      <c r="AD18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="10">
         <v>2</v>
       </c>
-      <c r="AH18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS18" s="10">
+      <c r="AH18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="9">
         <v>9</v>
       </c>
-      <c r="AT18" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU18" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV18" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW18" s="14">
+      <c r="AT18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="13">
         <v>60</v>
       </c>
-      <c r="AX18" s="15" t="s">
+      <c r="AX18" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY18" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="14">
+      <c r="AY18" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ18" s="13">
         <v>50</v>
       </c>
-      <c r="BA18" s="10">
+      <c r="BA18" s="9">
         <v>1</v>
       </c>
       <c r="BE18" s="4" t="s">
@@ -9143,144 +9242,147 @@
       <c r="BG18" s="4" t="s">
         <v>394</v>
       </c>
+      <c r="BH18" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+    <row r="19" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>15</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="J19" s="10">
-        <v>1</v>
-      </c>
-      <c r="K19" s="11">
+      <c r="J19" s="9">
+        <v>1</v>
+      </c>
+      <c r="K19" s="10">
         <v>3</v>
       </c>
-      <c r="L19" s="36" t="s">
+      <c r="L19" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M19" s="36" t="s">
+      <c r="M19" s="33" t="s">
         <v>415</v>
       </c>
-      <c r="N19" s="36" t="s">
+      <c r="N19" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="T19" s="12" t="s">
+      <c r="T19" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="U19" s="13">
-        <v>0</v>
-      </c>
-      <c r="V19" s="13">
+      <c r="U19" s="12">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12">
         <v>642</v>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="12">
         <v>2.6850000000000001</v>
       </c>
-      <c r="X19" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="13">
+      <c r="X19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AB19" s="12">
         <v>1141</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AC19" s="12">
         <v>95</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AD19" s="12">
         <v>15</v>
       </c>
-      <c r="AE19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS19" s="10">
+      <c r="AE19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS19" s="9">
         <v>28</v>
       </c>
-      <c r="AT19" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU19" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV19" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW19" s="14">
+      <c r="AT19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="13">
         <v>66</v>
       </c>
-      <c r="AX19" s="15" t="s">
+      <c r="AX19" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY19" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ19" s="14">
+      <c r="AY19" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="13">
         <v>50</v>
       </c>
-      <c r="BA19" s="10">
+      <c r="BA19" s="9">
         <v>1</v>
       </c>
       <c r="BE19" s="4" t="s">
@@ -9292,144 +9394,147 @@
       <c r="BG19" s="4" t="s">
         <v>397</v>
       </c>
+      <c r="BH19" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>16</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="J20" s="10">
-        <v>1</v>
-      </c>
-      <c r="K20" s="11">
+      <c r="J20" s="9">
+        <v>1</v>
+      </c>
+      <c r="K20" s="10">
         <v>3</v>
       </c>
-      <c r="L20" s="36" t="s">
+      <c r="L20" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M20" s="36" t="s">
+      <c r="M20" s="33" t="s">
         <v>413</v>
       </c>
-      <c r="N20" s="36" t="s">
+      <c r="N20" s="33" t="s">
         <v>426</v>
       </c>
-      <c r="T20" s="12" t="s">
+      <c r="T20" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="U20" s="13">
-        <v>0</v>
-      </c>
-      <c r="V20" s="13">
+      <c r="U20" s="12">
+        <v>0</v>
+      </c>
+      <c r="V20" s="12">
         <v>569</v>
       </c>
-      <c r="W20" s="13">
+      <c r="W20" s="12">
         <v>1.3</v>
       </c>
-      <c r="X20" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="13">
+      <c r="X20" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="12">
         <v>1653</v>
       </c>
-      <c r="AC20" s="13">
+      <c r="AC20" s="12">
         <v>282</v>
       </c>
-      <c r="AD20" s="13">
+      <c r="AD20" s="12">
         <v>10</v>
       </c>
-      <c r="AE20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="11">
+      <c r="AE20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="10">
         <v>2</v>
       </c>
-      <c r="AH20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR20" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS20" s="10">
+      <c r="AH20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS20" s="9">
         <v>14</v>
       </c>
-      <c r="AT20" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU20" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV20" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW20" s="14">
+      <c r="AT20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="13">
         <v>66</v>
       </c>
-      <c r="AX20" s="15" t="s">
+      <c r="AX20" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY20" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ20" s="14">
+      <c r="AY20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ20" s="13">
         <v>50</v>
       </c>
-      <c r="BA20" s="10">
+      <c r="BA20" s="9">
         <v>1</v>
       </c>
       <c r="BE20" s="4" t="s">
@@ -9441,144 +9546,147 @@
       <c r="BG20" s="4" t="s">
         <v>400</v>
       </c>
+      <c r="BH20" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
+    <row r="21" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>17</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="18" t="s">
         <v>360</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="J21" s="10">
-        <v>1</v>
-      </c>
-      <c r="K21" s="11">
+      <c r="J21" s="9">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10">
         <v>3</v>
       </c>
-      <c r="L21" s="36" t="s">
+      <c r="L21" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M21" s="36" t="s">
+      <c r="M21" s="33" t="s">
         <v>414</v>
       </c>
-      <c r="N21" s="36" t="s">
+      <c r="N21" s="33" t="s">
         <v>427</v>
       </c>
-      <c r="T21" s="12" t="s">
+      <c r="T21" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="U21" s="13">
-        <v>0</v>
-      </c>
-      <c r="V21" s="13">
+      <c r="U21" s="12">
+        <v>0</v>
+      </c>
+      <c r="V21" s="12">
         <v>437</v>
       </c>
-      <c r="W21" s="13">
+      <c r="W21" s="12">
         <v>1.9</v>
       </c>
-      <c r="X21" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="13">
+      <c r="X21" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="12">
         <v>935</v>
       </c>
-      <c r="AC21" s="13">
+      <c r="AC21" s="12">
         <v>83</v>
       </c>
-      <c r="AD21" s="13">
+      <c r="AD21" s="12">
         <v>15</v>
       </c>
-      <c r="AE21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS21" s="10">
+      <c r="AE21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS21" s="9">
         <v>10</v>
       </c>
-      <c r="AT21" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU21" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV21" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW21" s="14">
+      <c r="AT21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AW21" s="13">
         <v>60</v>
       </c>
-      <c r="AX21" s="15" t="s">
+      <c r="AX21" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY21" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ21" s="14">
+      <c r="AY21" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="13">
         <v>50</v>
       </c>
-      <c r="BA21" s="10">
+      <c r="BA21" s="9">
         <v>1</v>
       </c>
       <c r="BE21" s="4" t="s">
@@ -9590,144 +9698,147 @@
       <c r="BG21" s="4" t="s">
         <v>403</v>
       </c>
+      <c r="BH21" s="4" t="s">
+        <v>449</v>
+      </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+    <row r="22" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>18</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="J22" s="10">
-        <v>1</v>
-      </c>
-      <c r="K22" s="11">
+      <c r="J22" s="9">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10">
         <v>3</v>
       </c>
-      <c r="L22" s="36" t="s">
+      <c r="L22" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M22" s="36" t="s">
+      <c r="M22" s="33" t="s">
         <v>413</v>
       </c>
-      <c r="N22" s="36" t="s">
+      <c r="N22" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="T22" s="12" t="s">
+      <c r="T22" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="U22" s="13">
-        <v>0</v>
-      </c>
-      <c r="V22" s="13">
+      <c r="U22" s="12">
+        <v>0</v>
+      </c>
+      <c r="V22" s="12">
         <v>568</v>
       </c>
-      <c r="W22" s="13">
+      <c r="W22" s="12">
         <v>1.2</v>
       </c>
-      <c r="X22" s="11">
+      <c r="X22" s="10">
         <v>2</v>
       </c>
-      <c r="Y22" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="13">
+      <c r="Y22" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="12">
         <v>1858</v>
       </c>
-      <c r="AC22" s="13">
+      <c r="AC22" s="12">
         <v>245</v>
       </c>
-      <c r="AD22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="11">
+      <c r="AD22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="10">
         <v>2</v>
       </c>
-      <c r="AH22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS22" s="10">
+      <c r="AH22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS22" s="9">
         <v>17</v>
       </c>
-      <c r="AT22" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU22" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV22" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW22" s="14">
+      <c r="AT22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV22" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW22" s="13">
         <v>66</v>
       </c>
-      <c r="AX22" s="15" t="s">
+      <c r="AX22" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY22" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ22" s="14">
+      <c r="AY22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ22" s="13">
         <v>50</v>
       </c>
-      <c r="BA22" s="10">
+      <c r="BA22" s="9">
         <v>1</v>
       </c>
       <c r="BE22" s="4" t="s">
@@ -9739,144 +9850,147 @@
       <c r="BG22" s="4" t="s">
         <v>406</v>
       </c>
+      <c r="BH22" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="23" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
+    <row r="23" spans="1:60" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>19</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="32" t="s">
         <v>410</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="I23" s="9" t="s">
+      <c r="I23" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="J23" s="10">
-        <v>1</v>
-      </c>
-      <c r="K23" s="11">
+      <c r="J23" s="9">
+        <v>1</v>
+      </c>
+      <c r="K23" s="10">
         <v>3</v>
       </c>
-      <c r="L23" s="36" t="s">
+      <c r="L23" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="M23" s="36" t="s">
+      <c r="M23" s="33" t="s">
         <v>412</v>
       </c>
-      <c r="N23" s="36" t="s">
+      <c r="N23" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="T23" s="12" t="s">
+      <c r="T23" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="U23" s="13">
-        <v>0</v>
-      </c>
-      <c r="V23" s="13">
+      <c r="U23" s="12">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12">
         <v>425</v>
       </c>
-      <c r="W23" s="13">
+      <c r="W23" s="12">
         <v>1.05</v>
       </c>
-      <c r="X23" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="13">
+      <c r="X23" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="12">
         <v>1270</v>
       </c>
-      <c r="AC23" s="13">
+      <c r="AC23" s="12">
         <v>240</v>
       </c>
-      <c r="AD23" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="11">
+      <c r="AD23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="10">
         <v>2</v>
       </c>
-      <c r="AH23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS23" s="10">
+      <c r="AH23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS23" s="9">
         <v>9</v>
       </c>
-      <c r="AT23" s="10">
-        <v>1</v>
-      </c>
-      <c r="AU23" s="10">
-        <v>1</v>
-      </c>
-      <c r="AV23" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW23" s="14">
+      <c r="AT23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AU23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AV23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW23" s="13">
         <v>60</v>
       </c>
-      <c r="AX23" s="15" t="s">
+      <c r="AX23" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY23" s="10">
-        <v>1</v>
-      </c>
-      <c r="AZ23" s="14">
+      <c r="AY23" s="9">
+        <v>1</v>
+      </c>
+      <c r="AZ23" s="13">
         <v>50</v>
       </c>
-      <c r="BA23" s="10">
+      <c r="BA23" s="9">
         <v>1</v>
       </c>
       <c r="BE23" s="4" t="s">
@@ -9888,124 +10002,127 @@
       <c r="BG23" s="4" t="s">
         <v>409</v>
       </c>
+      <c r="BH23" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="10">
-        <v>1</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="9">
+        <v>1</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="9">
         <v>2</v>
       </c>
-      <c r="L24" s="16"/>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
-      <c r="P24" s="9" t="s">
+      <c r="L24" s="15"/>
+      <c r="O24" s="9">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="Q24" s="10">
-        <v>1</v>
-      </c>
-      <c r="R24" s="10">
-        <v>1</v>
-      </c>
-      <c r="S24" s="10">
-        <v>1</v>
-      </c>
-      <c r="T24" s="12" t="s">
+      <c r="Q24" s="9">
+        <v>1</v>
+      </c>
+      <c r="R24" s="9">
+        <v>1</v>
+      </c>
+      <c r="S24" s="9">
+        <v>1</v>
+      </c>
+      <c r="T24" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U24" s="13">
-        <v>0</v>
-      </c>
-      <c r="V24" s="13">
+      <c r="U24" s="12">
+        <v>0</v>
+      </c>
+      <c r="V24" s="12">
         <v>400</v>
       </c>
-      <c r="W24" s="13">
+      <c r="W24" s="12">
         <v>2</v>
       </c>
-      <c r="X24" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="13">
+      <c r="X24" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="12">
         <v>5960</v>
       </c>
-      <c r="AC24" s="13">
+      <c r="AC24" s="12">
         <v>265</v>
       </c>
-      <c r="AD24" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR24" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB24" s="13">
+      <c r="AD24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="12">
         <v>0.5</v>
       </c>
-      <c r="BC24" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD24" s="11">
+      <c r="BC24" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="10">
         <v>0</v>
       </c>
       <c r="BE24" s="4" t="s">
@@ -10017,124 +10134,127 @@
       <c r="BG24" s="4" t="s">
         <v>263</v>
       </c>
+      <c r="BH24" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="25" spans="1:59" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
+    <row r="25" spans="1:60" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>2</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="35" t="s">
         <v>441</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="9">
         <v>2</v>
       </c>
-      <c r="L25" s="16"/>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
-      <c r="P25" s="9" t="s">
+      <c r="L25" s="15"/>
+      <c r="O25" s="9">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="Q25" s="10">
-        <v>1</v>
-      </c>
-      <c r="R25" s="10">
-        <v>1</v>
-      </c>
-      <c r="S25" s="10">
-        <v>1</v>
-      </c>
-      <c r="T25" s="12" t="s">
+      <c r="Q25" s="9">
+        <v>1</v>
+      </c>
+      <c r="R25" s="9">
+        <v>1</v>
+      </c>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
+      <c r="T25" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U25" s="13">
+      <c r="U25" s="12">
         <v>2.8284280000000002</v>
       </c>
-      <c r="V25" s="13">
+      <c r="V25" s="12">
         <v>395</v>
       </c>
-      <c r="W25" s="13">
+      <c r="W25" s="12">
         <v>5</v>
       </c>
-      <c r="X25" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="13">
+      <c r="X25" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="12">
         <v>5090</v>
       </c>
-      <c r="AC25" s="13">
+      <c r="AC25" s="12">
         <v>185</v>
       </c>
-      <c r="AD25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR25" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB25" s="13">
+      <c r="AD25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB25" s="12">
         <v>0.45</v>
       </c>
-      <c r="BC25" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD25" s="11">
+      <c r="BC25" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD25" s="10">
         <v>0</v>
       </c>
       <c r="BE25" s="4" t="s">
@@ -10146,121 +10266,124 @@
       <c r="BG25" s="4" t="s">
         <v>264</v>
       </c>
+      <c r="BH25" s="4" t="s">
+        <v>446</v>
+      </c>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>3</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="9">
         <v>2</v>
       </c>
-      <c r="L26" s="16"/>
-      <c r="O26" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="10">
-        <v>1</v>
-      </c>
-      <c r="R26" s="10">
-        <v>1</v>
-      </c>
-      <c r="S26" s="10">
-        <v>1</v>
-      </c>
-      <c r="T26" s="12" t="s">
+      <c r="L26" s="15"/>
+      <c r="O26" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>1</v>
+      </c>
+      <c r="R26" s="9">
+        <v>1</v>
+      </c>
+      <c r="S26" s="9">
+        <v>1</v>
+      </c>
+      <c r="T26" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U26" s="13">
+      <c r="U26" s="12">
         <v>1.4142140000000001</v>
       </c>
-      <c r="V26" s="13">
+      <c r="V26" s="12">
         <v>1050</v>
       </c>
-      <c r="W26" s="13">
+      <c r="W26" s="12">
         <v>3</v>
       </c>
-      <c r="X26" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="13">
+      <c r="X26" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="12">
         <v>12500</v>
       </c>
-      <c r="AC26" s="13">
+      <c r="AC26" s="12">
         <v>325</v>
       </c>
-      <c r="AD26" s="13">
+      <c r="AD26" s="12">
         <v>10</v>
       </c>
-      <c r="AE26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB26" s="13">
+      <c r="AE26" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB26" s="12">
         <v>0.4</v>
       </c>
-      <c r="BC26" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="11">
+      <c r="BC26" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="10">
         <v>0</v>
       </c>
       <c r="BE26" s="4" t="s">
@@ -10272,124 +10395,127 @@
       <c r="BG26" s="4" t="s">
         <v>294</v>
       </c>
+      <c r="BH26" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
+    <row r="27" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>4</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="9">
         <v>2</v>
       </c>
-      <c r="L27" s="16"/>
-      <c r="O27" s="10">
-        <v>1</v>
-      </c>
-      <c r="P27" s="9" t="s">
+      <c r="L27" s="15"/>
+      <c r="O27" s="9">
+        <v>1</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="Q27" s="10">
-        <v>1</v>
-      </c>
-      <c r="R27" s="10">
-        <v>1</v>
-      </c>
-      <c r="S27" s="10">
-        <v>1</v>
-      </c>
-      <c r="T27" s="12" t="s">
+      <c r="Q27" s="9">
+        <v>1</v>
+      </c>
+      <c r="R27" s="9">
+        <v>1</v>
+      </c>
+      <c r="S27" s="9">
+        <v>1</v>
+      </c>
+      <c r="T27" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U27" s="13">
+      <c r="U27" s="12">
         <v>3</v>
       </c>
-      <c r="V27" s="13">
+      <c r="V27" s="12">
         <v>200</v>
       </c>
-      <c r="W27" s="13">
+      <c r="W27" s="12">
         <v>5</v>
       </c>
-      <c r="X27" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="13">
+      <c r="X27" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="12">
         <v>13000</v>
       </c>
-      <c r="AC27" s="13">
+      <c r="AC27" s="12">
         <v>375</v>
       </c>
-      <c r="AD27" s="13">
+      <c r="AD27" s="12">
         <v>50</v>
       </c>
-      <c r="AE27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR27" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB27" s="13">
+      <c r="AE27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB27" s="12">
         <v>0.25</v>
       </c>
-      <c r="BC27" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="11">
+      <c r="BC27" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="10">
         <v>0</v>
       </c>
       <c r="BE27" s="4" t="s">
@@ -10398,121 +10524,124 @@
       <c r="BF27" s="5" t="s">
         <v>256</v>
       </c>
+      <c r="BH27" s="4" t="s">
+        <v>445</v>
+      </c>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
+    <row r="28" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>6</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="9">
         <v>2</v>
       </c>
-      <c r="L28" s="16"/>
-      <c r="O28" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="10">
-        <v>1</v>
-      </c>
-      <c r="R28" s="10">
-        <v>1</v>
-      </c>
-      <c r="S28" s="10">
-        <v>1</v>
-      </c>
-      <c r="T28" s="12" t="s">
+      <c r="L28" s="15"/>
+      <c r="O28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>1</v>
+      </c>
+      <c r="R28" s="9">
+        <v>1</v>
+      </c>
+      <c r="S28" s="9">
+        <v>1</v>
+      </c>
+      <c r="T28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U28" s="13">
-        <v>0</v>
-      </c>
-      <c r="V28" s="13">
+      <c r="U28" s="12">
+        <v>0</v>
+      </c>
+      <c r="V28" s="12">
         <v>290</v>
       </c>
-      <c r="W28" s="13">
+      <c r="W28" s="12">
         <v>2</v>
       </c>
-      <c r="X28" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB28" s="13">
+      <c r="X28" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="12">
         <v>1235</v>
       </c>
-      <c r="AC28" s="13">
+      <c r="AC28" s="12">
         <v>65</v>
       </c>
-      <c r="AD28" s="13">
+      <c r="AD28" s="12">
         <v>5</v>
       </c>
-      <c r="AE28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF28" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG28" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB28" s="13">
-        <v>0</v>
-      </c>
-      <c r="BC28" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD28" s="11">
+      <c r="AE28" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB28" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC28" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD28" s="10">
         <v>0</v>
       </c>
       <c r="BE28" s="4" t="s">
@@ -10524,127 +10653,130 @@
       <c r="BG28" s="4" t="s">
         <v>297</v>
       </c>
+      <c r="BH28" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+    <row r="29" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>7</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="9">
         <v>2</v>
       </c>
-      <c r="L29" s="16"/>
-      <c r="O29" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>1</v>
-      </c>
-      <c r="R29" s="10">
-        <v>1</v>
-      </c>
-      <c r="S29" s="10">
-        <v>1</v>
-      </c>
-      <c r="T29" s="12" t="s">
+      <c r="L29" s="15"/>
+      <c r="O29" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>1</v>
+      </c>
+      <c r="R29" s="9">
+        <v>1</v>
+      </c>
+      <c r="S29" s="9">
+        <v>1</v>
+      </c>
+      <c r="T29" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U29" s="13">
-        <v>0</v>
-      </c>
-      <c r="V29" s="13">
+      <c r="U29" s="12">
+        <v>0</v>
+      </c>
+      <c r="V29" s="12">
         <v>430</v>
       </c>
-      <c r="W29" s="13">
+      <c r="W29" s="12">
         <v>4</v>
       </c>
-      <c r="X29" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="13">
+      <c r="X29" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="12">
         <v>3600</v>
       </c>
-      <c r="AC29" s="13">
+      <c r="AC29" s="12">
         <v>150</v>
       </c>
-      <c r="AD29" s="13">
+      <c r="AD29" s="12">
         <v>5</v>
       </c>
-      <c r="AE29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP29" s="12" t="s">
+      <c r="AE29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="AQ29" s="11" t="s">
+      <c r="AQ29" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="AR29" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB29" s="13">
-        <v>0</v>
-      </c>
-      <c r="BC29" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD29" s="11">
+      <c r="AR29" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB29" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC29" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD29" s="10">
         <v>0</v>
       </c>
       <c r="BE29" s="4" t="s">
@@ -10656,127 +10788,130 @@
       <c r="BG29" s="4" t="s">
         <v>297</v>
       </c>
+      <c r="BH29" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>8</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="9">
         <v>2</v>
       </c>
-      <c r="L30" s="16"/>
-      <c r="O30" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>1</v>
-      </c>
-      <c r="R30" s="10">
-        <v>1</v>
-      </c>
-      <c r="S30" s="10">
-        <v>1</v>
-      </c>
-      <c r="T30" s="12" t="s">
+      <c r="L30" s="15"/>
+      <c r="O30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="9">
+        <v>1</v>
+      </c>
+      <c r="R30" s="9">
+        <v>1</v>
+      </c>
+      <c r="S30" s="9">
+        <v>1</v>
+      </c>
+      <c r="T30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U30" s="13">
-        <v>0</v>
-      </c>
-      <c r="V30" s="13">
+      <c r="U30" s="12">
+        <v>0</v>
+      </c>
+      <c r="V30" s="12">
         <v>670</v>
       </c>
-      <c r="W30" s="13">
+      <c r="W30" s="12">
         <v>5</v>
       </c>
-      <c r="X30" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB30" s="13">
+      <c r="X30" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="12">
         <v>6900</v>
       </c>
-      <c r="AC30" s="13">
+      <c r="AC30" s="12">
         <v>235</v>
       </c>
-      <c r="AD30" s="13">
+      <c r="AD30" s="12">
         <v>5</v>
       </c>
-      <c r="AE30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF30" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG30" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="12" t="s">
+      <c r="AE30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="AQ30" s="11" t="s">
+      <c r="AQ30" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="AR30" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB30" s="13">
-        <v>0</v>
-      </c>
-      <c r="BC30" s="11">
-        <v>1</v>
-      </c>
-      <c r="BD30" s="11">
+      <c r="AR30" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB30" s="12">
+        <v>0</v>
+      </c>
+      <c r="BC30" s="10">
+        <v>1</v>
+      </c>
+      <c r="BD30" s="10">
         <v>0</v>
       </c>
       <c r="BE30" s="4" t="s">
@@ -10788,118 +10923,121 @@
       <c r="BG30" s="4" t="s">
         <v>297</v>
       </c>
+      <c r="BH30" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+    <row r="31" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>9</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="E31" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="9">
         <v>2</v>
       </c>
-      <c r="L31" s="16"/>
-      <c r="O31" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>0</v>
-      </c>
-      <c r="R31" s="10">
-        <v>0</v>
-      </c>
-      <c r="S31" s="10">
-        <v>0</v>
-      </c>
-      <c r="T31" s="12" t="s">
+      <c r="L31" s="15"/>
+      <c r="O31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>0</v>
+      </c>
+      <c r="R31" s="9">
+        <v>0</v>
+      </c>
+      <c r="S31" s="9">
+        <v>0</v>
+      </c>
+      <c r="T31" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U31" s="13">
+      <c r="U31" s="12">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V31" s="13">
+      <c r="V31" s="12">
         <v>500</v>
       </c>
-      <c r="W31" s="13">
+      <c r="W31" s="12">
         <v>3</v>
       </c>
-      <c r="X31" s="11">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="13">
+      <c r="X31" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="12">
         <v>5000</v>
       </c>
-      <c r="AC31" s="13">
+      <c r="AC31" s="12">
         <v>500</v>
       </c>
-      <c r="AD31" s="13">
+      <c r="AD31" s="12">
         <v>50</v>
       </c>
-      <c r="AE31" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG31" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR31" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB31" s="13">
+      <c r="AE31" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR31" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB31" s="12">
         <v>0.45</v>
       </c>
-      <c r="BC31" s="11">
+      <c r="BC31" s="10">
         <v>2</v>
       </c>
-      <c r="BD31" s="11">
+      <c r="BD31" s="10">
         <v>0</v>
       </c>
       <c r="BE31" s="4" t="s">
@@ -10908,145 +11046,148 @@
       <c r="BF31" s="5" t="s">
         <v>256</v>
       </c>
+      <c r="BH31" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
+    <row r="32" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>10</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="9">
         <v>2</v>
       </c>
-      <c r="L32" s="16"/>
-      <c r="O32" s="10">
-        <v>0</v>
-      </c>
-      <c r="P32" s="19" t="s">
+      <c r="L32" s="15"/>
+      <c r="O32" s="9">
+        <v>0</v>
+      </c>
+      <c r="P32" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="Q32" s="10">
-        <v>0</v>
-      </c>
-      <c r="R32" s="10">
-        <v>0</v>
-      </c>
-      <c r="S32" s="10">
-        <v>0</v>
-      </c>
-      <c r="T32" s="12" t="s">
+      <c r="Q32" s="9">
+        <v>0</v>
+      </c>
+      <c r="R32" s="9">
+        <v>0</v>
+      </c>
+      <c r="S32" s="9">
+        <v>0</v>
+      </c>
+      <c r="T32" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U32" s="13">
-        <v>0</v>
-      </c>
-      <c r="V32" s="13">
+      <c r="U32" s="12">
+        <v>0</v>
+      </c>
+      <c r="V32" s="12">
         <v>100</v>
       </c>
-      <c r="W32" s="13">
+      <c r="W32" s="12">
         <v>2</v>
       </c>
-      <c r="X32" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="13">
+      <c r="X32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="12">
         <v>100</v>
       </c>
-      <c r="AC32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="11">
-        <v>0</v>
-      </c>
-      <c r="AP32" s="12" t="s">
+      <c r="AC32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP32" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="AQ32" s="11" t="s">
+      <c r="AQ32" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="AR32" s="11">
-        <v>1</v>
-      </c>
-      <c r="AS32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AT32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AU32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AV32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AW32" s="14">
-        <v>0</v>
-      </c>
-      <c r="AX32" s="15" t="s">
+      <c r="AR32" s="10">
+        <v>1</v>
+      </c>
+      <c r="AS32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AU32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AV32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AW32" s="13">
+        <v>0</v>
+      </c>
+      <c r="AX32" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="AY32" s="10">
-        <v>0</v>
-      </c>
-      <c r="AZ32" s="14">
-        <v>0</v>
-      </c>
-      <c r="BA32" s="10">
+      <c r="AY32" s="9">
+        <v>0</v>
+      </c>
+      <c r="AZ32" s="13">
+        <v>0</v>
+      </c>
+      <c r="BA32" s="9">
         <v>0</v>
       </c>
       <c r="BE32" s="4" t="s">
@@ -11055,124 +11196,127 @@
       <c r="BF32" s="5" t="s">
         <v>256</v>
       </c>
+      <c r="BH32" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A33" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>11</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="9">
         <v>2</v>
       </c>
-      <c r="L33" s="16"/>
-      <c r="O33" s="10">
+      <c r="L33" s="15"/>
+      <c r="O33" s="9">
         <v>2</v>
       </c>
-      <c r="P33" s="19" t="s">
+      <c r="P33" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="Q33" s="10">
-        <v>1</v>
-      </c>
-      <c r="R33" s="10">
-        <v>1</v>
-      </c>
-      <c r="S33" s="10">
+      <c r="Q33" s="9">
+        <v>1</v>
+      </c>
+      <c r="R33" s="9">
+        <v>1</v>
+      </c>
+      <c r="S33" s="9">
         <v>2</v>
       </c>
-      <c r="T33" s="12" t="s">
+      <c r="T33" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="U33" s="13">
+      <c r="U33" s="12">
         <v>3</v>
       </c>
-      <c r="V33" s="13">
+      <c r="V33" s="12">
         <v>650</v>
       </c>
-      <c r="W33" s="13">
+      <c r="W33" s="12">
         <v>5</v>
       </c>
-      <c r="X33" s="11">
+      <c r="X33" s="10">
         <v>3</v>
       </c>
-      <c r="Y33" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="13">
+      <c r="Y33" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="12">
         <v>32500</v>
       </c>
-      <c r="AC33" s="13">
+      <c r="AC33" s="12">
         <v>700</v>
       </c>
-      <c r="AD33" s="13">
+      <c r="AD33" s="12">
         <v>50</v>
       </c>
-      <c r="AE33" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AH33" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AJ33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AK33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AL33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AM33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AN33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AO33" s="11">
-        <v>1</v>
-      </c>
-      <c r="AR33" s="11">
-        <v>0</v>
-      </c>
-      <c r="BB33" s="13">
+      <c r="AE33" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AJ33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AK33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="10">
+        <v>1</v>
+      </c>
+      <c r="AR33" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB33" s="12">
         <v>0.3</v>
       </c>
-      <c r="BC33" s="11">
+      <c r="BC33" s="10">
         <v>7</v>
       </c>
-      <c r="BD33" s="11">
+      <c r="BD33" s="10">
         <v>0</v>
       </c>
       <c r="BE33" s="4" t="s">
@@ -11181,97 +11325,100 @@
       <c r="BF33" s="5" t="s">
         <v>256</v>
       </c>
+      <c r="BH33" s="4" t="s">
+        <v>444</v>
+      </c>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:60" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="10">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="B34" s="9">
+        <v>1</v>
+      </c>
+      <c r="C34" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="9">
         <v>2</v>
       </c>
-      <c r="L34" s="16"/>
-      <c r="T34" s="12" t="s">
+      <c r="L34" s="15"/>
+      <c r="T34" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="U34" s="13">
+      <c r="U34" s="12">
         <v>1.5</v>
       </c>
-      <c r="V34" s="13">
-        <v>0</v>
-      </c>
-      <c r="W34" s="13">
+      <c r="V34" s="12">
+        <v>0</v>
+      </c>
+      <c r="W34" s="12">
         <v>-1</v>
       </c>
-      <c r="X34" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="11">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="13">
+      <c r="X34" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="12">
         <v>100</v>
       </c>
-      <c r="AC34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AL34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="11">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="11">
+      <c r="AC34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="12">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="10">
         <v>0</v>
       </c>
       <c r="BE34" s="4" t="s">
@@ -11282,6 +11429,9 @@
       </c>
       <c r="BG34" s="4" t="s">
         <v>265</v>
+      </c>
+      <c r="BH34" s="4" t="s">
+        <v>444</v>
       </c>
     </row>
   </sheetData>
